--- a/leads_export.xlsx
+++ b/leads_export.xlsx
@@ -607,24 +607,24 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Re: Your AI &amp; Frontend React Developer search</t>
+          <t>A thought on ACS's AI &amp; Frontend React Developer search</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>Dear ACS Team,
-I noticed you're hiring for an AI &amp; Frontend React Developer to strengthen your Software &amp; Data Solutions team. Rather than extend your search, I wanted to share a different perspective.
-Building custom AI solutions typically requires months of hiring, onboarding, and iteration. Yet 88% of AI pilots never reach production (CIO Magazine)—and full-time developer salaries consume significant budget with uncertain ROI.
-Omnithrive Technologies specializes in turning stalled AI initiatives into production-ready systems within 90 days. For chemical sciences organizations like ACS, this means automating literature analysis, accelerating research workflows, or streamlining data processing—without the months-long hiring cycle.
-Here's the financial reality: Your $100,000 annual budget for a full-time React and AI developer could instead fund a complete, production-ready AI system custom-built for ACS's workflows. We deliver equivalent capabilities for approximately 1/10th of that cost, with built-in change management and no disappearing after deployment.
-We don't sell pilots or prototypes. We only scale when value is proven.
-Rather than committing to either hire or vendor, we offer a complimentary 2-Day AI Opportunity Audit—no cost, no commitment. Our team will analyze your specific workflows, identify high-impact AI applications, and present a clear ROI timeline.
-If you'd like to explore whether an AI-accelerated approach makes sense for ACS, let's schedule a conversation:
-**cal.com/omnithrivetech-ceo**
-Warm regards,
-**Omnithrive Technologies**
+I noticed you are hiring for an AI &amp; Frontend React Developer role with a $100,000 annual budget. Before committing to a full-time hire, I wanted to share a perspective that may be worth considering.
+According to IBM's 2025 CEO Study, 75% of AI projects fail to deliver ROI. The challenge is not always talent-it is execution. Most organizations build AI systems that never reach production, or they hire developers who spend months integrating legacy workflows without clear business impact.
+Omnithrive Technologies specializes in turning stalled AI initiatives into measurable profits within 90 days. Rather than hiring a dedicated developer, you could deploy a production-ready AI system for approximately $10,000-a fraction of what you would invest in a full-time engineer. We build custom agentic AI solutions using JavaScript, React, and modern frameworks like LangChain and LangGraph, integrated directly into your existing processes.
+Your Software &amp; Data Solutions team can focus on core priorities while we handle the AI architecture, testing, and deployment. We do not deliver prototypes or pilots. We deliver systems that work.
+The most efficient path forward is our complimentary 2-Day AI Opportunity Audit. We will analyze your processes, identify high-impact automation opportunities, and provide a clear ROI projection-with zero commitment and zero cost.
+I invite you to explore this before finalizing your hire.
+You can book the audit here: cal.com/omnithrivetech-ceo
+Warm regards,
+Omnithrive Technologies
 AI Value Acceleration Studio
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+admin@omnithrivetech.com
+WhatsApp: +91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -684,22 +684,25 @@
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>ADHR GROUP's AI hiring challenge — a cost perspective</t>
+          <t>AI capability for ADHR GROUP's engineering talent pipeline</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
           <t>Dear Marco Portello,
-I've been following ADHR GROUP's recent search for a Neo laureato ing. meccanica specializing in AI/ML—a critical hire for your technical pipeline. I wanted to share a perspective that may be relevant to your recruitment strategy.
-The role likely carries an annual budget of approximately €100,000. Yet here's what concerns us: 75% of AI projects fail to deliver ROI, according to the IBM CEO Study 2025. Many organizations solve this by hiring senior technical talent, but that approach alone doesn't guarantee production-ready AI systems that drive measurable business value.
-At Omnithrive Technologies, we've built a different model. Rather than asking you to bet on a single hire, we deliver production-ready AI capabilities in 90 days—for roughly one-tenth of that salary investment. We specialize in turning stalled or failing AI initiatives into measurable profits through custom-built agentic systems (LangChain, LangGraph, AutoGen) integrated seamlessly into your recruiting and HR workflows.
-We don't deploy pilots or prototypes. We build systems that work, with built-in change management to ensure adoption.
-Before you commit to the full-time hire, I'd like to invite you to a complimentary 2-Day AI Opportunity Audit. No commitment, no cost. We'll identify where AI can deliver the highest impact to your recruiting operations and provide a concrete roadmap.
-You can book directly here: cal.com/omnithrivetech-ceo
-Warm regards,
-**Omnithrive Technologies**  
-AI Value Acceleration Studio  
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+I noticed ADHR GROUP is actively recruiting for specialized engineering roles - specifically Neo laureato ing. meccanica - progettazione positions. Building internal AI capability to streamline candidate screening, skills matching, and technical assessment would typically require hiring a dedicated AI engineer at roughly $100,000 annually.
+There is an alternative worth considering.
+According to IBM's 2025 CEO Study, 75% of AI projects fail to deliver ROI. The reason is straightforward: most organizations either build pilots that never reach production, or hire talent that doesn't align with their actual workflow needs.
+At Omnithrive Technologies, we work differently. We build production-ready AI systems custom-fitted to your recruiting workflows - candidate pipeline automation, technical skill evaluation, interview scheduling - and deliver measurable results within 90 days. Our approach costs approximately one-tenth of a full-time hire, while eliminating the onboarding delays and misalignment that plague most AI initiatives.
+We do not offer pilots or prototypes. We deliver systems that work, or we do not charge you.
+The first step is understanding what is actually possible for ADHR GROUP's specific needs. That is precisely what our complimentary 2-Day AI Opportunity Audit provides - no obligation, no cost, and no sales pressure.
+If you are open to exploring how AI could reduce your time-to-hire and improve candidate quality assessment, I would welcome a brief conversation.
+You can schedule the audit directly at cal.com/omnithrivetech-ceo, or reach me at admin@omnithrivetech.com.
+Warm regards,
+Omnithrive Technologies
+AI Value Acceleration Studio
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -776,23 +779,25 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>On ADP's ML pipeline scaling challenge</t>
+          <t>ADP's ML pipeline challenge - a different approach</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>Dear Tracy Hine,
-I've followed ADP's expansion into advanced Machine Learning solutions for your HCM system, and I noticed your recent posting for an AI Engineer focused on data pipelines and forecasting models. Building and deploying production-grade ML systems at your scale requires sustained engineering expertise—and typically represents a significant annual investment.
-Here's what caught my attention: 88% of AI pilots never reach production (CIO Magazine). Most organizations struggle not with the initial model design, but with operationalizing data pipelines, maintaining model performance, and scaling across systems. That's where most AI hiring budgets get consumed.
-At Omnithrive Technologies, we specialize in turning stalled or failing AI initiatives into production-ready systems within 90 days. Our team has deep expertise in the exact stack your JD references: data pipeline architecture, forecasting models, and responsible AI frameworks. More importantly, we deliver production systems—not prototypes or proofs-of-concept.
-The math is straightforward: your AI Engineer budget is approximately $100,000 annually. We can deliver equivalent ML engineering capabilities and custom solutions for roughly one-tenth of that cost, while maintaining the change management and adoption support that ensures your systems actually create measurable value.
-Rather than a lengthy sales conversation, I'd like to invite you to a complimentary 2-Day AI Opportunity Audit. We'll assess where your current ML initiatives stand, identify the highest-impact opportunities, and outline a concrete path to production-ready systems.
-No commitment. No cost.
-Book here: cal.com/omnithrivetech-ceo
-Warm regards,
+I noticed ADP is hiring for an AI Engineer to design and deploy advanced Machine Learning solutions across your HCM platform. That's a significant undertaking - building data pipelines, forecasting models, and responsible AI systems at scale requires exceptional talent and sustained investment.
+Here's what we're observing: 75% of AI projects fail to deliver ROI (IBM CEO Study, 2025). Most organizations struggle not with the technology itself, but with moving from prototype to production, and ensuring adoption across engineering and product teams.
+At Omnithrive Technologies, we specialize in turning stalled AI initiatives into measurable business value within 90 days. We've built production-ready systems using the exact stack your team needs - LangChain, LangGraph, and advanced ML architectures for data optimization and forecasting. More importantly, we embed change management throughout deployment, ensuring your teams adopt and scale what works.
+Here's the financial angle: a full-time AI Engineer carries an annual cost of approximately $100,000 plus overhead. Omnithrive delivers equivalent AI capabilities - custom-built for your workflows - at roughly one-tenth that investment, with guaranteed production deployment.
+Rather than adding headcount, consider a strategic alternative: a 2-Day AI Opportunity Audit where we assess your current ML initiatives, identify high-impact opportunities, and outline a 90-day path to measurable results.
+No commitment. No cost. No sales pitch.
+Book a time that works for you at cal.com/omnithrivetech-ceo.
+Warm regards,
+[Your Name]
+Senior B2B Outreach Specialist
 Omnithrive Technologies
-AI Value Acceleration Studio
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -868,18 +873,19 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>AMD's SGLang optimization challenge — a different approach</t>
+          <t>AMD's AI inference stack - a build vs. buy perspective</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
           <t>Dear Raghav Dhir,
-I noticed AMD is hiring for a Senior Software Development Engineer focused on optimizing deep learning frameworks like TensorFlow and PyTorch on AMD GPUs, with particular emphasis on SGLang inference stack performance. That's a critical role—and a $100,000 annual investment.
-Here's the challenge: 75% of AI projects fail to deliver measurable ROI, according to IBM's 2025 CEO Study. Most organizations struggle to move from framework optimization theory to production-ready systems that actually perform at scale.
-At Omnithrive Technologies, we specialize in turning stalled AI initiatives into measurable value within 90 days. Our expertise spans the exact stack you're building around—GPU kernel optimization, deep learning model profiling, and inference acceleration on specialized hardware. We've worked with teams optimizing performance across TensorFlow, PyTorch, and emerging frameworks, translating academic improvements into production gains.
-Rather than recruiting full-time, many enterprises in your space are now leveraging specialized AI development teams on demand. We deliver equivalent capabilities at approximately 1/10th the cost of a full-time senior engineer—roughly $10,000 versus your $100,000 budget—while maintaining focus on your specific hardware and framework priorities.
-Before you finalize your hiring decision, I'd like to invite you to a complimentary 2-Day AI Opportunity Audit. We'll analyze your current inference stack challenges, identify concrete optimization opportunities, and show you what production-ready looks like in your specific context—no commitment required.
-Would you be open to exploring this? You can book directly at cal.com/omnithrivetech-ceo.
+I noticed AMD is actively hiring for a Senior Software Development Engineer focused on SGLang and GPU kernel optimization across deep learning frameworks. That's a significant investment - particularly given the complexity of profiling and tuning large-scale inference models for optimal performance on AMD hardware.
+Here's the reality: 88% of AI pilots never reach production (CIO Magazine). Most organizations build internal teams, invest heavily in hiring, and still struggle to deliver measurable value at scale.
+AMD's approach is different - you're building world-class infrastructure. But many enterprises face a different problem: they have AI ambitions but lack the specialized talent to move from prototype to production-ready systems fast. That's where we come in.
+Omnithrive Technologies specializes in turning stalled AI initiatives into measurable profits within 90 days. Our team works with the exact tech stack you're optimizing for - agentic AI frameworks, GPU-accelerated inference, and production deployment at scale. Where a full-time Senior Software Development Engineer would cost you approximately $100,000 annually, we deliver equivalent capabilities and proven ROI for roughly one-tenth of that investment.
+We don't build pilots. We build production-ready systems with built-in change management - the kind that actually scale.
+If you know enterprise teams struggling to move their AI investments from stalled to shipped, I'd like to show you how we accelerate that journey. No cost, no commitment.
+Let's schedule a complimentary 2-Day AI Opportunity Audit: cal.com/omnithrivetech-ceo
 Warm regards,
 Omnithrive Technologies
 AI Value Acceleration Studio
@@ -947,24 +953,24 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Re: your AI Engineer Analyst search at AXA Group Operations</t>
+          <t>Re: your AI Engineer Analyst search</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>Dear Seiji Yasubuchi,
-I noticed AXA Group Operations is actively hiring for an AI Engineer Analyst to work on Language Models, multimodal AI, and responsible AI standards. That signals a critical priority—yet I'd like to offer a perspective you may not have considered.
-Recruiting, onboarding, and retaining specialized AI talent for $100,000 annually is increasingly difficult. More importantly, 88% of AI pilots never reach production (CIO Magazine), meaning even talented engineers often struggle to deliver measurable business value without the right framework and support structure.
-At Omnithrive Technologies, we've built a different model: production-ready AI systems, not prototypes. We work with enterprises in insurance, finance, and logistics to turn stalled AI initiatives into measurable profit within 90 days. Our agentic AI expertise spans Claude, LangChain, LangGraph, and AutoGen—the exact stack your team needs.
-Here's the concrete advantage: our custom-built, production-ready solutions typically cost one-tenth of a full-time senior hire. Rather than investing $100,000 in recruitment and overhead, you could deploy proven AI systems across your operations—with built-in change management and ongoing support.
-We don't offer demos or pilots. We deliver value or we don't charge.
-I'd like to invite you to a complimentary 2-Day AI Opportunity Audit at no cost and with no commitment. We'll identify your highest-impact AI opportunities and build a clear path to production.
-Book here: cal.com/omnithrivetech-ceo
-Warm regards,
-[Your Name]
-Senior B2B Outreach Specialist
+I noticed AXA Group Operations is hiring for an AI Engineer Analyst focused on Language Models, multimodal AI, and responsible AI standards. That's a compelling direction - and it signals a real commitment to production-grade GenAI capabilities.
+Here's the challenge: 88% of AI pilots never reach production (CIO Magazine). Most organizations invest heavily in hiring specialists, only to find their projects stall or fail to deliver measurable ROI.
+At Omnithrive Technologies, we work with mid-to-large enterprises in insurance and financial services to turn stalled AI initiatives into production-ready systems within 90 days. We specialize in exactly what you're building toward - Claude integration, responsible AI frameworks, and cloud-based GenAI workflows that actually deliver value.
+The financial picture is worth considering: your $100,000 annual budget for a full-time AI Engineer Analyst typically yields one perspective and limited bandwidth. For approximately one-tenth that investment, Omnithrive delivers a dedicated cross-functional team with proven expertise in Python, cloud architecture, and GenAI APIs - plus built-in change management to ensure adoption.
+Rather than replace your hiring, think of us as accelerating your AI strategy. We conduct a complimentary 2-Day AI Opportunity Audit to identify quick-win initiatives, validate technical approaches, and map a path to production deployment.
+If exploring this makes sense, I'd welcome a brief conversation.
+Book your free audit here: cal.com/omnithrivetech-ceo
+Warm regards,
 Omnithrive Technologies
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+AI Value Acceleration Studio
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -1016,23 +1022,23 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>A thought on AXA Italia's AI transformation costs</t>
+          <t>AXA Italia's AI transformation - a resource perspective</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
           <t>Dear AXA Italia Team,
-I noticed you are actively hiring for Cloud Engineering roles with AI/ML expertise as part of your transformation and innovation initiative. This is strategic — but it raises a practical question: how long will it take to recruit, onboard, and see measurable ROI from a full-time hire at €100,000 annually?
-Here is the reality: 88% of AI pilots never reach production (CIO Magazine). Most organizations invest heavily in talent only to watch initiatives stall at the proof-of-concept stage.
-At Omnithrive Technologies, we take a different approach. We build production-ready AI systems — not demos or prototypes — customized to your exact workflows. For your insurance and financial services operations, this means AI agents that handle claims processing, customer service automation, or fraud detection from day one. We deliver measurable results in 90 days, or you pay nothing.
-Our cost? Approximately 1/10th of what you would invest in a full-time Cloud Engineering hire — while eliminating recruitment delays and adoption risk.
-Rather than debating hiring timelines, let us conduct a complimentary 2-Day AI Opportunity Audit. We will identify your highest-impact use cases, assess your current tech stack, and provide a clear, ROI-focused roadmap. No commitment. No cost.
-If we uncover genuine value, we move to a High-Impact MVP build. If not, you have lost nothing but gained clarity.
-I invite you to book a time that works for your team:
-cal.com/omnithrivetech-ceo
-Warm regards,
+I noticed your search for a Cloud Engineering professional to support your AI and ML initiatives within your digital transformation roadmap. Given the scope of AI capability-building you're undertaking, I wanted to share a relevant perspective.
+According to IBM's 2025 CEO Study, 75% of AI projects fail to deliver ROI - often because organizations struggle to move beyond pilot phases into production-ready systems. The challenge isn't always talent scarcity; it's execution velocity and sustainable value delivery.
+At Omnithrive Technologies, we specialize in turning stalled AI initiatives into measurable business outcomes within 90 days. Rather than adding headcount, we build production-ready AI systems customized to your workflows - reducing implementation risk and cost simultaneously.
+For your budgeted investment of approximately $100,000 annually for a full-time Cloud Engineer, you could instead access our expert AI development team at $30/hour, delivering equivalent AI capabilities while maintaining clear ROI accountability. More importantly, you avoid the overhead of hiring, onboarding, and retention while achieving faster time-to-value.
+We've worked with mid-to-large enterprises across insurance, finance, and manufacturing to operationalize AI systems that actually drive bottom-line impact. We don't prototype - we deploy.
+I'd like to invite you to explore this with a complimentary 2-Day AI Opportunity Audit. No commitment, no cost. We'll assess your current AI initiatives and identify where immediate value can be unlocked.
+You can schedule directly here: cal.com/omnithrivetech-ceo
+Warm regards,
+[Your Name]
+Senior B2B Outreach Specialist
 Omnithrive Technologies
-AI Value Acceleration Studio
 admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
         </is>
       </c>
@@ -1085,19 +1091,100 @@
       <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Automating AZ Service s.r.l's operations without the hire</t>
+          <t>AI capabilities for AZ Service s.r.l's operations team</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>Dear AZ Service s.r.l Team,
-I noticed you're recruiting a Diplomato/Ingegnere to strengthen your facilities management operations at Centro Residenziale per Anziani di Cittadella. Before you commit $100,000 annually to a full-time role, I wanted to share a perspective that may reshape how you approach this.
-88% of AI pilots never reach production—yet the right implementation can automate the core responsibilities your new hire would handle: scheduling optimization, sanitation protocol automation, maintenance request routing, and transportation logistics coordination.
-Omnithrive Technologies specializes in turning operational inefficiencies into measurable profit within 90 days. Rather than hiring, we can deploy production-ready AI systems customized to your workflows—delivering equivalent capabilities for approximately one-tenth of that salary investment.
-Your facilities management operations involve complex coordination across cleaning, maintenance, and transportation. These are precisely the areas where AI-driven automation eliminates manual overhead, reduces human error, and scales without proportional cost increases.
-We offer a complimentary 2-Day AI Opportunity Audit—no commitment required. Our team will analyze your specific operational bottlenecks and demonstrate concrete ROI potential before any engagement begins. This is how we validate whether AI acceleration makes financial sense for your organization.
-If you're open to exploring whether automation could achieve what you'd expect from a new hire, I'd welcome a brief conversation.
-Book your free audit here: cal.com/omnithrivetech-ceo
+Your recent search for a Diplomato/Ingegnere signals something many facilities management organizations face: the need for technical expertise to optimize operations across cleaning, sanitation, maintenance, and reception services.
+Here is what we observe: 75% of AI projects fail to deliver ROI, according to the IBM CEO Study 2025. Most organizations either hire expensive talent or launch pilot programs that never reach production.
+We work differently. Omnithrive Technologies is an AI Value Acceleration Studio that transforms failing or stalled AI initiatives into measurable profit within 90 days. Rather than a traditional hire at your $100,000 annual budget, we deliver production-ready AI systems custom-built for your workflows - at approximately one-tenth of that cost.
+For facilities management operations like yours, this means automating scheduling, predictive maintenance alerts, resource allocation optimization, and service quality monitoring. No pilots. No prototypes. Systems that work from day one, with built-in change management to ensure your team adopts them effectively.
+We have helped mid-to-large enterprises in healthcare and facilities management eliminate process inefficiencies that cost millions annually. Our approach is simple: we guarantee measurable results, not demos.
+Rather than commit to a lengthy hire process, consider a complimentary 2-Day AI Opportunity Audit. We will assess your operations, identify high-impact automation opportunities, and present a clear ROI roadmap - at no cost and with no commitment required.
+If this resonates, I invite you to book a time at cal.com/omnithrivetech-ceo.
+Warm regards,
+Omnithrive Technologies
+AI Value Acceleration Studio
+admin@omnithrivetech.com
+WhatsApp: +91 97426 09264</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Aalto University</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.aalto.fi/en</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Aalto University is one of the best universities in the world, using cookies to improve services and support marketing efforts.</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Postdoctoral Artificial Intelligence Research Software Engineer</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Espoo, Uusimaa, Finland</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence, Embedding, GDPR</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Wouter Badenhorst</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Chief Technology Officer</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>wouter.badenhorst@aalto.fi</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/wouter-dirk-badenhorst-97081a145</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Aalto University's AI hiring - a perspective</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>Dear Wouter Badenhorst,
+I noticed Aalto University is recruiting for a Postdoctoral Artificial Intelligence Research Software Engineer - a role budgeted at approximately $100,000 annually. I wanted to share a perspective that may be relevant to your AI initiatives.
+At Omnithrive Technologies, we specialize in turning stalled or underperforming AI projects into production-ready systems within 90 days. Given your focus on AI embedding and GDPR-compliant solutions, we understand the technical complexity you're addressing.
+Here's what we've observed: 88% of AI pilots never reach production (CIO Magazine). Universities and enterprises often invest heavily in talent and infrastructure, yet struggle to translate research into operationalized value.
+We take a different approach. Rather than relying solely on full-time hires, we deliver equivalent AI capabilities - custom-built for your workflows, with embedded change management and adoption support - at a fraction of the cost. For the $100,000 you've budgeted for this role, we can provide comprehensive AI development services at approximately $10,000, freeing resources for strategic priorities.
+Our work spans LangChain, LangGraph, and embedding frameworks tailored to privacy-first environments. We don't build prototypes; we build production systems.
+I'd like to invite you to a complimentary 2-Day AI Opportunity Audit. No commitment, no cost. We'll map your AI landscape, identify high-impact opportunities, and propose a concrete path forward.
+You can book a time here: cal.com/omnithrivetech-ceo
 Warm regards,
 Omnithrive Technologies
 AI Value Acceleration Studio
@@ -1105,159 +1192,76 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Aalto University</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aalto.fi/en</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Aalto University is one of the best universities in the world, using cookies to improve services and support marketing efforts.</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Education</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Postdoctoral Artificial Intelligence Research Software Engineer</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Espoo, Uusimaa, Finland</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence, Embedding, GDPR</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>Wouter Badenhorst</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>Chief Technology Officer</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>wouter.badenhorst@aalto.fi</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/wouter-dirk-badenhorst-97081a145</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr"/>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>Aalto University's AI talent gap — a cost perspective</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>Dear Wouter Badenhorst,
-I noticed Aalto University is recruiting for a Postdoctoral Artificial Intelligence Research Software Engineer—a critical hire given your expansion into embedding technologies and GDPR-compliant AI systems.
-Here's a pragmatic observation: that $100,000 annual investment funds one specialist. At Omnithrive Technologies, we deliver equivalent AI capabilities—production-ready systems built around embedding models, data governance, and compliance frameworks—for approximately one-tenth of that cost.
-The challenge isn't unique to academia. According to an IBM CEO Study, 75% of AI projects fail to deliver ROI, often because organizations build in isolation rather than integrate systems into existing workflows. Universities face this acutely: talented researchers prototype brilliantly, but scaling those systems into operational value—especially within GDPR constraints—requires both technical depth and pragmatic deployment experience.
-Our approach is different. We specialize in turning stalled or failing AI initiatives into measurable impact within 90 days. We don't hire; we deploy. Our team builds production-ready systems using industry-standard stacks (LangChain, Claude, embeddings infrastructure) and ensures adoption through built-in change management.
-Rather than commit to a lengthy hiring process, consider a conversation first. We offer a complimentary 2-Day AI Opportunity Audit—no commitment, no cost—to map where embedding technologies and AI systems could create immediate institutional value while respecting your compliance requirements.
-I'd welcome a brief discussion about whether this approach aligns with your roadmap.
-You can book directly at cal.com/omnithrivetech-ceo or reach us at admin@omnithrivetech.com.
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Accenture Italia</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.accenture.com/it-it</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Accenture Italia provides various services including Cloud, Cybersecurity, Data and Artificial Intelligence, and more, to help businesses transform and grow.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Multiple (including Aerospace, Automotive, Banking, Healthcare, etc.)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>AI &amp; Data Engineer</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Milan, Lombardy, Italy</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence, Data Engineer, Modal, Scala</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>investor.relations@accenture.com</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>In Accenture, potrai portare la tua visione innovativa al cuore del cambiamento, lavorando con le aziende più importanti a livello mondiale per trasformare interi settori di mercato. Modella il futuro del business e della tecnologia sviluppando soluzioni all'avanguardia in grado di generare nuovo valore.</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Re: your AI &amp; Data Engineer search</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>Dear Accenture Italia Team,
+I noticed your recent opening for an AI &amp; Data Engineer-a role reflecting the scale of AI capability you're building across your client portfolio in aerospace, automotive, and banking.
+I lead Omnithrive Technologies, an AI Value Acceleration Studio. We partner with enterprises to transform stalled or failing AI initiatives into production-ready systems that deliver measurable ROI within 90 days.
+Here is what caught my attention: your team is tasked with developing solutions that "generate nuovo valore" across entire market sectors. That is precisely where most organizations stumble. According to IBM's 2025 CEO Study, 75% of AI projects fail to deliver ROI-often because they remain pilots rather than production systems that scale.
+At Omnithrive, we do something different. Rather than adding headcount at $100,000 annually, we deliver equivalent AI capabilities-leveraging Modal, LangChain, LangGraph, and production-grade LLM stacks-at approximately 1/10th that cost. We build custom agentic systems tailored to your clients' workflows, embed change management, and only scale when value is proven.
+Your clients deserve AI that works. Your team deserves partners who de-risk implementation.
+I would like to invite you to explore this with zero commitment. We offer a complimentary 2-Day AI Opportunity Audit-no cost, no obligation-to identify high-impact AI use cases within your organization or client base.
+If this resonates, please book time here: cal.com/omnithrivetech-ceo
 Warm regards,
 [Your Name]
 Senior B2B Outreach Specialist
 Omnithrive Technologies
-AI Value Acceleration Studio</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Accenture Italia</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.accenture.com/it-it</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Accenture Italia provides various services including Cloud, Cybersecurity, Data and Artificial Intelligence, and more, to help businesses transform and grow.</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Multiple (including Aerospace, Automotive, Banking, Healthcare, etc.)</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>AI &amp; Data Engineer</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Milan, Lombardy, Italy</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence, Data Engineer, Modal, Scala</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>investor.relations@accenture.com</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>In Accenture, potrai portare la tua visione innovativa al cuore del cambiamento, lavorando con le aziende più importanti a livello mondiale per trasformare interi settori di mercato. Modella il futuro del business e della tecnologia sviluppando soluzioni all'avanguardia in grado di generare nuovo valore.</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>Accenture Italia's AI &amp; Data Engineer search — a perspective</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>Dear Accenture Italia Team,
-I've reviewed your current opening for an AI &amp; Data Engineer, and I wanted to share an observation that may be relevant to your broader AI transformation strategy.
-Your team is tasked with developing production-ready AI solutions across aerospace, automotive, banking, and healthcare—sectors where innovation directly drives competitive advantage. The role emphasizes building scalable systems with technologies like Modal and Scala, capable of generating measurable business value for enterprise clients.
-Here's what we've observed: 75% of AI projects fail to deliver ROI, according to the IBM CEO Study (2025). Most organizations struggle not with hiring talented engineers, but with translating AI initiatives into production systems that actually move the needle.
-At Omnithrive Technologies, we specialize in exactly this—turning stalled or failing AI initiatives into measurable profits within 90 days. Our approach is production-ready from day one, not pilots. More importantly: we deliver equivalent AI capabilities and execution for approximately 1/10th of what you'd invest in a full-time hire ($100,000 annually). A seasoned agentic AI developer on our team costs roughly $10,000.
-Rather than hiring for capacity, consider whether your current AI initiatives need acceleration, validation, or de-risking first.
-We offer a complimentary 2-Day AI Opportunity Audit—no commitment, no cost—where we identify which of your in-flight projects can reach production within 90 days and quantify the ROI impact.
-If this resonates, I'd welcome a brief conversation.
-Book your audit here: cal.com/omnithrivetech-ceo
-Warm regards,
-[Your Name]
-Senior B2B Outreach Specialist
-Omnithrive Technologies
-admin@omnithrivetech.com
-WhatsApp: +91 97426 09264</t>
+admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -1313,23 +1317,24 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>Re: Your Fullstack Software Engineer search — an alternative approach</t>
+          <t>Re: your Fullstack Software Engineer search</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
           <t>Dear ActiveCampaign Team,
-I've reviewed your Fullstack Software Engineer opening for your Kraków Hub. Your focus on agentic workflows, performance optimization, and productization across your CRM platform caught my attention—particularly the shift into Python-based AI agents for deals, contacts, and lists functionality.
-Here's an observation: 88% of AI pilots never reach production (CIO Magazine). Most teams hire full-time engineers at your posted budget ($100,000/year) to build these systems, only to discover the complexity exceeds expectations or adoption stalls post-launch.
-At Omnithrive Technologies, we specialize in turning stalled AI initiatives into measurable production systems within 90 days. Our expert AI developers work with LangChain, LangGraph, and AutoGen—precisely the agentic frameworks your role requires—at approximately $10,000 annually. That's 1/10th the cost of a full-time hire, with built-in change management and production-ready delivery.
-Rather than a lengthy hiring cycle, you could validate your agentic CRM strategy in two weeks with a high-impact MVP, then scale with confidence.
-I'd like to propose something concrete: a complimentary 2-Day AI Opportunity Audit. We'll map your current challenges, identify where AI agents can unlock immediate value in your platform, and outline a clear path to production. No commitment. No cost.
-If this resonates, I'd welcome a brief conversation.
-**Book here:** cal.com/omnithrivetech-ceo
-Warm regards,
-**Omnithrive Technologies**
+I noticed your hiring announcement for a Fullstack Software Engineer focused on agentic workflows and CRM platform optimization. That role reflects a critical challenge many SaaS companies face: building AI-native capabilities requires specialized talent that's expensive, scarce, and slow to onboard.
+Here's the reality: 88% of AI pilots never reach production (CIO Magazine). Most enterprises invest heavily in hiring senior AI engineers, only to discover that integrating agentic systems into existing PHP backends and customer journey workflows demands far more than technical skills - it requires production-ready architecture, adoption strategy, and proven ROI frameworks.
+At Omnithrive Technologies, we deliver exactly what ActiveCampaign needs: production-ready AI agents for your CRM workflows - deals optimization, contact intelligence, list segmentation - built in 2-3 weeks. The cost differential is striking: your $100,000 annual engineering budget could instead fund a complete AI Opportunity Audit plus a high-impact MVP that proves value before any long-term commitment.
+Rather than hiring for capacity, consider this: what if you could prototype your agentic workflows, validate market fit, and build internal capability simultaneously - without the hiring lag or salary overhead?
+I'd like to invite you to a complimentary 2-Day AI Opportunity Audit. We'll map your CRM pain points, identify where agentic AI creates immediate ROI, and provide a roadmap you can execute with your existing team.
+No commitment. No cost.
+Book here: cal.com/omnithrivetech-ceo
+Warm regards,
+Omnithrive Technologies
 AI Value Acceleration Studio
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -1404,24 +1409,22 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Re: Your Engineer search at Aditi Consulting</t>
+          <t>Aditi Consulting's Engineer search - a cost perspective</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Dear Aditi Consulting Team,
-I noticed you're actively hiring for an Engineer role with expertise in Data Science, Predictive Analytics, and Azure—a $100,000 annual investment for capabilities your team needs immediately.
-Here's a perspective worth considering: 75% of AI projects fail to deliver ROI, according to the IBM CEO Study (2025). Most organizations either hire for these specialized roles at premium cost, or build pilots that never reach production. Neither solves your underlying problem.
-At Aditi Consulting, your packaging validation workflows—material testing protocols, technical evaluations, cross-functional collaboration on component selection—involve repetitive data analysis and documentation. These are precisely where AI agents and predictive analytics create measurable value. Rather than waiting months to hire and onboard, production-ready systems can be deployed in 90 days at a fraction of the cost.
-Omnithrive Technologies specializes in turning stalled or failing AI initiatives into measurable profits. We've built custom AI systems using LangGraph, AutoGen, and Azure-native tools that deliver results, not prototypes. The equivalent capability to what you'd pay a full-time hire costs approximately $10,000—one-tenth your budgeted expense.
-Before committing either direction, we offer a complimentary 2-Day AI Opportunity Audit. No cost, no commitment. We'll assess your specific workflows and identify where AI creates immediate impact.
-If this resonates, I'd welcome a brief conversation.
-Book your audit: cal.com/omnithrivetech-ceo
-Warm regards,
-**[Your Name]**
-Senior B2B Outreach Specialist
+I noticed you are currently hiring for an Engineer role with a $100,000 annual budget. Given your need for expertise in predictive analytics, data science, and technical evaluation workflows, I wanted to share a perspective that may be relevant to your planning.
+Your job description emphasizes technical specification writing, material testing protocol development, and cross-functional collaboration on validation activities. These are precisely the areas where AI-driven automation can accelerate delivery and reduce manual overhead - yet 75% of AI projects fail to deliver ROI, according to the IBM CEO Study 2025.
+Here is the consideration: Omnithrive Technologies specializes in building production-ready AI systems that handle these exact workflows. We can deploy predictive analytics capabilities, automated protocol generation, and cross-team coordination tools for approximately 1/10th of what you would invest in a full-time engineer hire. That means equivalent technical capability for roughly $10,000 rather than $100,000.
+Rather than choosing between hiring capacity and budget constraints, you could establish an AI system that handles routine testing recommendations, specification writing, and validation coordination - freeing your team to focus on higher-level engineering decisions.
+We offer a complimentary 2-Day AI Opportunity Audit at no cost and with no commitment. During this audit, our team will assess your specific workflows, quantify efficiency gains, and present a clear path to measurable ROI within 90 days.
+If this resonates, I would welcome a brief conversation. You can schedule directly at cal.com/omnithrivetech-ceo, or reach out to admin@omnithrivetech.com.
+Warm regards,
 Omnithrive Technologies
-admin@omnithrivetech.com | +91 97426 09264</t>
+AI Value Acceleration Studio
+admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -1489,25 +1492,22 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>Automating SAP Finance integration — without the $100K hire</t>
+          <t>Adroit People Limited (UK)'s SAP Finance automation challenge</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
           <t>Dear Adroit People Limited (UK) Team,
-I noticed you're actively recruiting a Senior Software Developer with SAP Finance expertise to design and implement financial systems integration. That's a critical hire—and at $100,000 annually, it represents significant long-term investment.
-Here's a perspective worth considering: 88% of AI pilots never reach production (CIO Magazine). Yet there's a faster, more cost-effective path forward.
-Omnithrive Technologies specializes in turning stalled or failing AI initiatives into measurable business value within 90 days. For recruitment and staffing firms like yours, this translates to automating exactly what you're hiring for—SAP Finance integration workflows, requirement gathering, and solution design—without the overhead of a full-time senior engineer.
-Our production-ready AI systems, built on agentic platforms like LangGraph and LangChain, deliver equivalent capabilities for approximately 1/10th of your budgeted salary—roughly $10,000 versus $100,000. We don't build pilots or prototypes. We deploy systems that work, backed by built-in change management and ongoing optimization.
-Rather than committing to a traditional hire, consider validating this approach risk-free.
-We're offering Adroit People Limited (UK) a complimentary 2-Day AI Opportunity Audit—no commitment, no cost. Our team will assess your SAP Finance integration challenges and present a concrete roadmap for production-ready automation.
-Book your audit here: cal.com/omnithrivetech-ceo
-Let's explore whether AI acceleration makes sense for your workflow.
+I noticed you are recruiting for a Senior Software Engineer with deep SAP Finance expertise. Given the complexity of integrating financial systems and the current market rate for this role ($100,000+ annually), I wanted to share a perspective that may be relevant to your team.
+88% of AI pilots never reach production, according to CIO Magazine. However, there is an alternative approach: rather than hiring a full-time developer to build custom SAP Finance integrations and process automation, forward-thinking organizations are deploying AI-powered solutions that deliver equivalent capability at a fraction of the cost.
+Omnithrive Technologies specializes in turning stalled AI initiatives into measurable profit within 90 days. Our production-ready systems can automate the cross-functional requirements gathering, business logic translation, and financial system integration tasks outlined in your job description. We deliver working solutions in 2-3 weeks, not months - and our cost is approximately one-tenth of a full-time senior engineer ($10,000 versus $100,000 annually).
+Your team could redirect that hiring budget toward proven automation that scales immediately, with built-in change management and ongoing expert support.
+We offer a complimentary 2-Day AI Opportunity Audit at no cost or commitment. This will identify specific opportunities within your SAP Finance operations and quantify realistic ROI before any engagement.
+If this resonates, I would welcome a brief conversation. You can book directly at cal.com/omnithrivetech-ceo or reach out to admin@omnithrivetech.com.
 Warm regards,
 [Your Name]
 Senior B2B Outreach Specialist
-Omnithrive Technologies
-admin@omnithrivetech.com | +91 97426 09264</t>
+Omnithrive Technologies</t>
         </is>
       </c>
     </row>
@@ -1559,24 +1559,23 @@
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>A thought on Agilex's Data Scientist hire</t>
+          <t>Data Science at Agilex - A different approach</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Dear Agilex Team,
-I noticed you're actively recruiting for a Data Scientist role—a significant investment, typically running $100,000+ annually for a full-time hire.
-Before you commit, consider this: 75% of AI projects fail to deliver measurable ROI, according to the IBM CEO Study 2025. Most organizations build capability without clarity on where AI actually drives value in their operations.
-At Omnithrive Technologies, we work with fragrance and personal care manufacturers to deploy production-ready AI systems that solve specific, costly inefficiencies—whether that's supply chain optimization, demand forecasting, quality control automation, or formulation data analysis. Rather than hiring and waiting months for results, we deliver measurable value in 90 days.
-The insight we've found: companies don't need another data scientist building models in isolation. They need AI that integrates directly into existing workflows and generates tangible profit within weeks.
-Here's what's relevant to your situation: equivalent AI capabilities—custom-built for your manufacturing and formulation processes—cost approximately 1/10th of what you'd pay a full-time hire. No lengthy onboarding. No pilot that never reaches production.
-We'd like to show you what's possible. We offer a complimentary 2-Day AI Opportunity Audit—no commitment, no cost—where we identify your highest-impact AI opportunity and outline a production-ready path forward.
-If this resonates, let's talk.
-Book your audit here: cal.com/omnithrivetech-ceo
-Warm regards,
-**Omnithrive Technologies**
-AI Value Acceleration Studio
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+I noticed you are hiring for a Data Scientist role. Before you commit $100,000 annually to a full-time hire, I wanted to share a perspective that may be worth considering.
+At Omnithrive Technologies, we specialize in turning stalled AI initiatives into measurable business value within 90 days. We work with manufacturers and personal care companies to automate process inefficiencies, optimize supply chains, and accelerate decision-making through production-ready AI systems.
+Here is the reality: 88% of AI pilots never reach production (CIO Magazine). Most organizations build teams or hire specialists, but without a clear ROI-first strategy and embedded change management, those investments stall.
+We deliver equivalent AI capabilities for approximately 1/10th of what a full-time Data Scientist costs. Rather than hiring and waiting for results, we audit your operations, identify high-impact opportunities, and deploy working systems in weeks - not months. No pilots. No prototypes. Production-ready outcomes.
+Given Agilex's focus on custom fragrance manufacturing and multi-industry distribution, there are likely significant opportunities in demand forecasting, supply chain optimization, and quality control automation that we could uncover and prototype quickly.
+Before you finalize your hiring decision, I would like to offer a complimentary 2-Day AI Opportunity Audit. No commitment. No cost. You will receive a clear roadmap of where AI can genuinely move the needle for your operations.
+Please schedule a time at cal.com/omnithrivetech-ceo, or reach out directly at admin@omnithrivetech.com.
+Warm regards,
+[Your Name]
+Senior B2B Outreach Specialist
+Omnithrive Technologies</t>
         </is>
       </c>
     </row>
@@ -1632,26 +1631,23 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>Re: your Staff AI Software Engineer search</t>
+          <t>A thought on Aircall's AI agent hiring</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
           <t>Dear Aircall Team,
-I've been following your growth as an AI-powered communications platform serving 22,000+ companies. Your recent Staff AI Software Engineer posting caught my attention—specifically the focus on building AI Agents that power your voice, SMS, and WhatsApp integrations at scale.
-Here's what we've observed: 88% of AI pilots never reach production (CIO Magazine). Most organizations treat AI hiring as a long-term build cycle. But what if you could validate your highest-impact AI opportunities in 90 days instead?
-Omnithrive Technologies specializes in turning stalled AI initiatives into measurable revenue within that window. We've built production-ready agentic systems using LangChain, LangGraph, and CrewAI—the exact stack driving modern AI agents. For your use case (agent-driven customer communication workflows), we deliver equivalent capabilities at approximately 1/10th the cost of a full-time senior hire. Your posted budget of $100,000 annually would translate to roughly $10,000 for a scoped, production-grade AI system with built-in change management and adoption support.
-Rather than a lengthy hiring cycle, you gain:
-- A 2-day AI Opportunity Audit (free, no commitment)
-- Clarity on which agent-driven initiatives deliver the highest customer communication ROI
-- A production-ready MVP if aligned—not a pilot
-We don't believe in demos or indefinite consulting. We scale only when value is proven.
-If this resonates, I'd welcome a brief conversation. Book a complimentary audit here: cal.com/omnithrivetech-ceo
-Warm regards,
-[Your Name]
-Senior B2B Outreach Specialist
+I noticed you are actively recruiting for a Staff AI Software Engineer to build and scale AI agents within your customer communications platform. Given the complexity of integrating agentic AI into production systems that serve 22,000+ companies, this is a critical hire.
+Here's what caught my attention: 88% of AI pilots never reach production (CIO Magazine). Most teams invest heavily in specialized talent, only to discover that moving from prototype to revenue-generating systems requires more than coding expertise - it demands production-ready architecture, workflow integration, and adoption strategy working in tandem.
+At Omnithrive Technologies, we accelerate exactly this transition. We specialize in turning stalled or failing AI initiatives into measurable profit within 90 days using agentic frameworks like LangGraph, AutoGen, and CrewAI - the same technologies powering modern agent systems.
+What if you could access production-ready AI agent development for approximately 1/10th of what a $100,000 annual hire would cost? Our model delivers equivalent capabilities without the recruitment timeline, onboarding delays, or long-term salary commitment.
+Rather than another hire, consider a 2-day AI Opportunity Audit at no cost and with no obligation. We will assess your current AI initiatives, identify high-impact opportunities within your agent architecture, and present a clear path to production deployment.
+This takes two days. It costs nothing. And it may reframe how you approach your AI scaling strategy entirely.
+Book your audit here: cal.com/omnithrivetech-ceo
+Warm regards,
 Omnithrive Technologies
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+AI Value Acceleration Studio
+admin@omnithrivetech.com | +91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -1746,23 +1742,25 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Re: Your Data Scientist search at Akkodis</t>
+          <t>A thought on Akkodis's AI build-out</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>Dear Christopher Blechschmidt,
-I noticed Akkodis is actively hiring for a Data Scientist role focused on end-to-end model development—from EDA and feature engineering through deployment and monitoring across data pipelines. That's precisely the capability gap we help enterprises close.
-Here's a thought: rather than investing $100,000 annually in a full-time hire, organizations are discovering they can access equivalent AI development capacity—including production-ready data science systems, pipeline optimization, and model deployment—for approximately one-tenth that cost. At Omnithrive, we specialize in building custom AI solutions that integrate seamlessly into existing workflows without the overhead of permanent headcount.
-The challenge is real. According to IBM's 2025 CEO Study, 75% of AI projects fail to deliver ROI. The gap between hiring talented developers and actually deploying systems that generate measurable value is where most organizations stumble.
-What if you could validate whether a targeted AI initiative—whether it's data pipeline automation, predictive modeling, or generative AI integration—would genuinely serve your clients' needs before committing to a full-time role? That's exactly what our complimentary 2-Day AI Opportunity Audit does. We analyze your specific use cases, your tech stack, and your workflows to identify where AI delivers immediate, quantifiable impact.
-No obligation. No pitch. Just clarity on what's actually achievable.
-If this resonates, I'd welcome a conversation. You can book directly at cal.com/omnithrivetech-ceo, or reach out to admin@omnithrivetech.com.
-Warm regards,
-**[Your Name]**
-Senior B2B Outreach Specialist
+I noticed Akkodis is actively hiring for a Data Scientist role focused on end-to-end ML deployment - from feature engineering through production monitoring, with hands-on experience building and optimizing data pipelines.
+Here's what caught my attention: you're budgeting roughly $100,000 annually for this position. Yet 75% of AI projects fail to deliver ROI, and most organizations struggle to move models from prototype to production at scale.
+At Omnithrive Technologies, we specialize in turning that around. We build production-ready AI systems - not pilots - in 90 days or less. Our team works with the exact stack your JD emphasizes: Python, PyTorch/TensorFlow, SQL-heavy data pipelines, and deployment automation. More importantly, we deliver equivalent AI capabilities for approximately one-tenth of what a full-time Data Scientist costs.
+Rather than a months-long hiring cycle and onboarding overhead, you could have a high-impact AI system in production within weeks - at roughly $10,000 instead of $100,000.
+We're not interested in generic solutions or endless demos. Every system we build is custom-fitted to your workflows and includes built-in change management so adoption actually sticks.
+I'd like to show you what's possible. We offer a complimentary 2-Day AI Opportunity Audit - no cost, no commitment - where we map your highest-value AI opportunities and outline a clear path to measurable returns.
+Would you be open to exploring this?
+Book here: cal.com/omnithrivetech-ceo
+Warm regards,
 Omnithrive Technologies
-AI Value Acceleration Studio</t>
+AI Value Acceleration Studio
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -1814,24 +1812,23 @@
       <c r="M17" s="3" t="inlineStr"/>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>On your Full-stack AI Developer hire—a perspective</t>
+          <t>Re: your Full-stack Software Engineer (x/f/m) - AI Developer Tools search</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
           <t>Dear Alan Jackson,
-I noticed you're recruiting for a Full-stack Software Engineer focused on AI Developer Tools. Building proprietary AI capabilities in-house is critical—especially for a multi-platform operation managing music releases, content production, and brand expansion across Silverbelly Whiskey.
-Here's the challenge: 75% of AI projects fail to deliver ROI, according to IBM's 2025 CEO Study. Full-time AI engineers command $100,000+ annually, yet most organizations struggle to translate that investment into measurable business outcomes—particularly when scaling AI across touring logistics, content scheduling, or brand operations.
-At Omnithrive Technologies, we've built a different model. Instead of hiring for speculative AI builds, we deliver production-ready systems in 90 days—custom-built to your workflows, not generic tools. Our approach costs approximately one-tenth of a full-time hire ($10,000 versus $100,000 annually), and we guarantee measurable results or you don't pay.
-We work with agentic AI frameworks (LangChain, LangGraph, AutoGen) and production automation platforms (n8n, Zapier, Make) to solve real operational bottlenecks—content workflow automation, tour scheduling optimization, or data-driven decision systems for your whiskey brand.
-Rather than committing to a lengthy hiring cycle, I'd like to invite you to a complimentary 2-Day AI Opportunity Audit. We'll identify your highest-impact use cases and present a clear roadmap with projected ROI—no obligation, no cost.
-Would you be open to exploring this?
-Book here: cal.com/omnithrivetech-ceo
-Warm regards,
-[Your Name]
-Senior B2B Outreach Specialist
+I noticed you are currently hiring for a Full-stack Software Engineer focused on AI Developer Tools. Given the technical complexity and cost of building production-ready AI systems in-house, I wanted to reach out with a perspective that may prove valuable.
+Most organizations attempting to build AI capabilities internally face a significant challenge: 88% of AI pilots never reach production (CIO Magazine). The combination of hiring delays, skill gaps, and the time required to move from prototype to deployed system often stretches timelines and budgets considerably.
+Your budgeted investment of approximately $100,000 annually for this role reflects the market rate for specialized AI talent. However, there is an alternative approach worth exploring. Omnithrive Technologies specializes in delivering production-ready AI systems within 90 days, and our cost structure is approximately 1/10th of what a full-time engineer hire would require. Rather than investing in recruitment and onboarding, you could access expert AI developers with proven experience in LangChain, LangGraph, and AutoGen at $30 per hour, while simultaneously building systems that directly address your operational inefficiencies.
+This is particularly relevant for organizations managing complex workflows - whether in content production pipelines, tour logistics, or e-commerce operations for your Silverbelly Whiskey brand.
+I would like to invite you to a complimentary 2-Day AI Opportunity Audit. This is a no-cost, no-commitment engagement where we assess your specific AI initiatives and identify where measurable value can be realized quickly.
+You can schedule at cal.com/omnithrivetech-ceo.
+Warm regards,
 Omnithrive Technologies
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+AI Value Acceleration Studio
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -1918,23 +1915,25 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Re: your Data Scientist search at Allegro</t>
+          <t>Building ML at Allegro - make or buy?</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>Dear Keith Gannon,
-I noticed Allegro is hiring for a Data Scientist role focused on building machine learning solutions and driving model implementation across your teams. This is exactly where many semiconductor companies face a critical decision: invest heavily in full-time talent, or access production-ready AI capabilities more strategically.
-Here's the reality: 88% of AI pilots never reach production (CIO Magazine). Most organizations struggle not with talent scarcity, but with translating business challenges into impactful ML problems that actually scale—and your JD reflects this perfectly.
-At Omnithrive Technologies, we specialize in turning stalled AI initiatives into measurable results within 90 days. Rather than waiting months to hire and onboard a $100,000/year Data Scientist, we deliver equivalent AI capabilities—custom ML models, efficient data pipeline implementation, and statistical forecasting solutions—for approximately 1/10th of that cost. Your budget covers a full-time hire; our approach gets you production-ready systems that integrate with your existing workflows, complete with built-in adoption support.
-We don't deliver pilots or prototypes. We build systems that work—or we adjust at no additional cost.
-I'd like to invite you to a complimentary 2-Day AI Opportunity Audit. No commitment. We'll assess your current data science initiatives, identify high-impact opportunities, and present a clear path to ROI.
-You can book directly at cal.com/omnithrivetech-ceo.
+I noticed Allegro is actively hiring for a Data Scientist to lead impactful projects around forecasting and model implementation across your semiconductor work. That's a significant investment - typically $100,000+ annually for the right talent.
+Here's a perspective worth considering: 75% of AI projects fail to deliver ROI, according to the IBM CEO Study 2025. The challenge often isn't finding skilled people - it's ensuring those models actually reach production and drive measurable business impact.
+At Omnithrive Technologies, we specialize in turning stalled or failing AI initiatives into production-ready systems within 90 days. Rather than hiring a full-time Data Scientist, many organizations in your space leverage our expert AI developers at approximately $10,000 - roughly one-tenth of a traditional hire - while maintaining complete ownership of their ML infrastructure and algorithms.
+We've built deep expertise in the exact workflows your JD highlights: translating business challenges into ML problems, handling large-scale datasets, and driving model implementation across teams. Our developers work fluently in Python, SQL, and the statistical modeling techniques your role demands.
+The difference? We deliver production-ready systems, not pilots. We handle change management and adoption. And we only scale when value is proven.
+I'd like to invite you to a complimentary 2-Day AI Opportunity Audit. No commitment, no cost - simply an honest assessment of where AI can create measurable profit for Allegro.
+Book here: cal.com/omnithrivetech-ceo
 Warm regards,
 [Your Name]
 Senior B2B Outreach Specialist
 Omnithrive Technologies
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -2008,97 +2007,96 @@
       <c r="O19" s="3" t="inlineStr">
         <is>
           <t>Dear Allianz Partners Team,
-I noticed you're actively recruiting for a Backend Engineer to design and maintain REST APIs powering AI-enabled solutions—specifically around microservices, CI/CD pipelines, and observability across Azure infrastructure.
-This is telling. Most enterprises face the same challenge: building robust AI infrastructure requires specialist talent, and that $100,000 annual investment often yields pilots that never reach production. In fact, 88% of AI pilots never reach production (CIO Magazine)—and many organizations discover too late that infrastructure alone doesn't guarantee ROI.
-Here's what we've found works differently: instead of hiring for capability, enterprises like those in insurance and finance partner with us to accelerate their AI initiatives into measurable profit within 90 days. We design, build, and deploy production-ready AI systems—REST APIs, microservices orchestration, MLOps pipelines, the full stack—without the hiring overhead or long ramp-up cycles.
-For approximately 1/10th of what you'd invest in a full-time Backend Engineer ($10,000 vs. $100,000), we deliver equivalent AI capabilities custom-built for your workflows, with built-in change management and ongoing support.
-Rather than another candidate conversation, I'd like to offer something more useful: a complimentary 2-Day AI Opportunity Audit. We'll assess your current AI infrastructure, identify where your biggest ROI gaps exist, and outline a path to production-ready systems—no commitment, no cost.
-If this resonates, book a time here: cal.com/omnithrivetech-ceo
-Warm regards,
-**Omnithrive Technologies**
+I noticed your open Backend Engineer role focuses on designing AI-enabled REST APIs and establishing observability standards across microservices using Azure, Docker, and Kubernetes. Building and maintaining production-grade CI/CD pipelines with MLOps integration is clearly central to your roadmap.
+Here is the challenge: 88% of AI pilots never reach production, according to CIO Magazine. Most organizations invest heavily in backend talent to bridge this gap, yet struggle to move from experimental systems to revenue-generating solutions.
+Omnithrive Technologies specializes in turning stalled AI initiatives into measurable profits within 90 days. Rather than hiring a full-time Backend Engineer at $100,000 annually, consider this: we deliver production-ready AI systems with equivalent technical depth - custom-built for your workflows, integrated into your existing Azure and Kubernetes infrastructure - for approximately one-tenth that cost.
+Our team has deep expertise in the exact stack your role demands: Python, REST API design, CI/CD automation, and cloud-native architecture. We don't build pilots. We build systems that scale.
+Before committing to a lengthy hiring process, I would like to invite you to our complimentary 2-Day AI Opportunity Audit. No cost, no commitment. We will analyze your current backend bottlenecks and identify where AI-powered automation could reduce operational friction and accelerate time-to-production.
+If this resonates, please book a conversation here: cal.com/omnithrivetech-ceo
+Warm regards,
+Omnithrive Technologies
+AI Value Acceleration Studio
+admin@omnithrivetech.com
+WhatsApp: +91 97426 09264</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>American Honda Motor Company, Inc.</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.honda.com/</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>American Honda Motor Company, Inc. is a company that produces and sells a wide range of vehicles and power equipment, including cars, motorcycles, and marine products. They also offer financial services and insurance solutions.</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Engineer II</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Greater Indianapolis</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Data Privacy, Go, Robotics</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Fallon Wolfe</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>fallon.wolfe@honda.com</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fallon-wolfe-08ab281ba</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>American Honda Motor Company, Inc.'s AI engineering approach</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>Dear Fallon Wolfe,
+I noticed American Honda Motor Company, Inc. is actively hiring for an Engineer II role focused on data privacy, robotics, and Go-based systems. This suggests you're building or scaling critical automation capabilities internally.
+Here is the challenge: 75% of AI projects fail to deliver ROI, according to the IBM CEO Study, 2025. Most organizations hire full-time engineers at significant cost-your posted budget reflects approximately $100,000 annually-only to discover that AI initiatives stall in pilot phases or never reach production.
+At Omnithrive Technologies, we deliver production-ready AI systems that work within your existing workflows. Rather than hiring an additional engineer, you could access equivalent AI capabilities for approximately one-tenth of that cost. Our agentic AI solutions-built with LangChain, LangGraph, and AutoGen-integrate seamlessly with robotics pipelines and data-secure environments. We focus on measurable ROI within 90 days, not prototypes.
+We have helped mid-to-large enterprises in automotive, logistics, and manufacturing turn stalled AI initiatives into measurable profits. Your robotics and data privacy requirements are precisely where AI-driven automation delivers the greatest impact.
+I would like to invite you to a complimentary two-day AI Opportunity Audit at no cost and no commitment. We will assess where AI can create immediate value in your current operations and outline a path to production deployment.
+Please schedule at your convenience: cal.com/omnithrivetech-ceo
+Warm regards,
+Omnithrive Technologies
 AI Value Acceleration Studio
 admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>American Honda Motor Company, Inc.</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.honda.com/</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>American Honda Motor Company, Inc. is a company that produces and sells a wide range of vehicles and power equipment, including cars, motorcycles, and marine products. They also offer financial services and insurance solutions.</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Automotive</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Engineer II</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Greater Indianapolis</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Data Privacy, Go, Robotics</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>Fallon Wolfe</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>fallon.wolfe@honda.com</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/fallon-wolfe-08ab281ba</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>American Honda Motor Company, Inc.'s AI engineering gap—and a faster path</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>Dear Fallon Wolfe,
-You're hiring for an Engineer II role focused on robotics, data privacy, and Go development—roles that typically command $100,000 annually and take months to fill. I wanted to share a perspective that may prove valuable.
-American Honda Motor Company, Inc. operates in an industry where process automation and intelligent systems directly impact manufacturing efficiency, supply chain resilience, and product quality. Yet 88% of AI pilots never reach production, according to CIO Magazine—meaning even when companies invest in AI talent and infrastructure, sustainable value rarely materializes.
-At Omnithrive Technologies, we specialize in turning stalled or failing AI initiatives into measurable profits within 90 days. Our approach is fundamentally different: we build production-ready systems custom to your workflows, not generic tools or prototypes. We embed change management and adoption support directly into deployment, ensuring your teams actually use what we build.
-Here's the practical angle: our expert AI developers—proficient in the exact tech stack automotive and robotics operations demand—deliver equivalent capabilities at approximately $10,000 for a high-impact MVP build, versus the $100,000 annual cost of a full-time hire. You get measurable ROI in weeks, not months.
-Rather than committing to a lengthy hiring process, I'd like to invite you to a complimentary 2-Day AI Opportunity Audit. We'll identify where your current workflows are losing value and map a concrete path to production-ready AI systems.
-No commitment. No cost.
-Book here: cal.com/omnithrivetech-ceo
-Warm regards,
-[Your Name]
-Senior B2B Outreach Specialist
-Omnithrive Technologies
-admin@omnithrivetech.com | +91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -2150,19 +2148,18 @@
       <c r="M21" s="3" t="inlineStr"/>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>Re: your Artificial Intelligence Engineer search</t>
+          <t>A thought on Ampstek's AI engineering approach</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
           <t>Dear Ampstek Team,
-I noticed you're actively recruiting for an Artificial Intelligence Engineer—a critical hire for scaling your global workforce platform. Given the complexity of integrating AI into payroll management and talent placement workflows, I wanted to share a perspective that might reshape how you approach this.
-Here's the challenge: 88% of AI pilots never reach production (CIO Magazine). Most organizations invest heavily in hiring specialized talent, only to discover that point solutions and disconnected implementations fail to deliver measurable business impact.
-At Omnithrive Technologies, we work with SaaS and HR Tech companies facing identical pressures. Rather than building from scratch or waiting months for a new hire to ramp up, we deliver production-ready AI systems tailored to your exact workflows—in 90 days or less.
-Consider the math: your budgeted $100,000 annual investment in an AI engineer could instead fund our high-impact MVP build and ongoing AI development support at approximately 1/10th the cost, with measurable ROI guaranteed within 90 days. We've built systems on AWS using modern AI stacks (LangChain, AutoGen, LangGraph) that integrate seamlessly into platforms like yours.
-Rather than debate hiring versus building, let's conduct a free, no-commitment 2-Day AI Opportunity Audit. We'll identify which payroll automation, candidate matching, or workforce scaling processes could be transformed by production-ready AI—and what the realistic timeline and investment would be.
-If it makes sense, we move forward. If not, you have clarity either way.
-Would you be open to a brief conversation? Book your audit here: cal.com/omnithrivetech-ceo
+I noticed you are actively hiring for an Artificial Intelligence Engineer role. Given your focus on scaling workforce solutions globally, I wanted to share a perspective that may be relevant.
+Building AI capabilities in-house requires sustained investment - your budgeted $100,000 annually covers salary alone, without accounting for infrastructure, tooling, or the extended timeline to production. Yet 88% of AI pilots never reach production, according to CIO Magazine. Many organizations find themselves caught between two outcomes: expensive hires with long ramp-up periods, or stalled initiatives that consume resources without delivering measurable value.
+At Omnithrive Technologies, we specialize in turning failing or stalled AI initiatives into production-ready systems within 90 days. We deliver equivalent AI capabilities - custom-built for your workforce management and payroll processes - for approximately 1/10th of what a full-time engineer costs annually. Our approach is ROI-first: we build production systems, not prototypes, and we remain engaged through adoption and scaling.
+For HR Tech platforms like Ampstek, this translates to AI-driven automation in candidate assessment, payroll intelligence, or resource forecasting - delivered and proven before traditional hiring cycles complete.
+Rather than commit to a lengthy recruitment process, I would like to invite you to a complimentary 2-Day AI Opportunity Audit. We will assess your most pressing AI opportunity and outline a concrete path to measurable value - at no cost and with no obligation.
+You can book directly here: cal.com/omnithrivetech-ceo
 Warm regards,
 [Your Name]
 Senior B2B Outreach Specialist
@@ -2236,22 +2233,22 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Re: your Equipment Engineering search</t>
+          <t>Analog Devices's AI talent gap - a different approach</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
           <t>Dear Monica Segrera,
-I noticed Analog Devices is actively hiring for Equipment Engineering roles focused on ADAS, autonomous driving, and robotics guidance systems. Building in-house AI capabilities for these domains typically requires a $100K+ annual investment in specialized talent—yet 88% of AI pilots never reach production, leaving that investment stranded (CIO Magazine).
-At Omnithrive Technologies, we deliver production-ready AI systems in 90 days, not prototypes. We specialize in turning stalled or failing AI initiatives into measurable profit—exactly what equipment engineering teams need when scaling autonomous systems and intelligent guidance algorithms.
-Rather than waiting 6–12 months to hire and onboard an AI engineer, you could have a functioning, custom-built AI system deployed and validated within weeks. Our approach costs approximately 1/10th of a full-time hire ($10K versus your $100K budget), and we guarantee measurable results—not just demos.
-We work with manufacturers and semiconductor companies solving complex signal processing and automation challenges using LangChain, LangGraph, and production-grade agentic AI. We don't disappear after deployment; we embed change management and adoption into every engagement.
-I'd like to invite you to a complimentary 2-Day AI Opportunity Audit. No commitment required. We'll map your highest-leverage automation opportunities and show you exactly what's possible within your timeline and budget.
-Book a time at **cal.com/omnithrivetech-ceo**, or reach out directly at admin@omnithrivetech.com.
-Warm regards,
-**Omnithrive Technologies**
-AI Value Acceleration Studio
-admin@omnithrivetech.com | +91 97426 09264</t>
+I noticed Analog Devices is actively recruiting for Equipment Engineering roles focused on autonomous driving, robotics, and ADAS systems. Building internal AI capabilities for these complex domains requires exceptional talent - and at $100,000 annually per hire, the investment is substantial.
+Here's what we're seeing across aerospace and automotive: 75% of AI projects fail to deliver ROI, largely because companies either hire slowly or build teams that lack production-ready expertise from day one.
+Omnithrive Technologies takes a different approach. Rather than a lengthy hiring cycle, we deliver production-ready AI systems tailored to your exact workflows - autonomous guidance algorithms, robotics automation, or equipment intelligence - in 90 days. Our expert developers specialize in agentic AI frameworks (LangGraph, CrewAI, AutoGen) and seamless integrations, the same technical depth you'd need in a full-time engineer. The difference: we cost approximately $10,000 versus the $100,000 annual commitment of a traditional hire, and you see measurable results before scaling further.
+We don't build pilots. We build production systems with embedded change management so your teams adopt and maintain them.
+I'd like to invite you to a complimentary 2-Day AI Opportunity Audit. No commitment, no cost. We'll map your specific challenges in equipment intelligence and autonomous systems, then show you exactly what's possible within 90 days.
+You can book directly at cal.com/omnithrivetech-ceo, or reach out to admin@omnithrivetech.com.
+Warm regards,
+[Your Name]
+Senior B2B Outreach Specialist
+Omnithrive Technologies</t>
         </is>
       </c>
     </row>
@@ -2333,18 +2330,18 @@
       <c r="O23" s="3" t="inlineStr">
         <is>
           <t>Dear Marco Rossi,
-I noticed Andiamo is hiring for an ML Engineer to build production-ready pipelines, implement monitoring systems, and scale models across your infrastructure. That's a significant investment—typically $100,000+ annually for the right talent.
-Here's the reality: 88% of AI pilots never reach production (CIO Magazine). The gap between prototyping and deployment is where most fashion and retail brands lose millions in unrealized value.
-At Omnithrive Technologies, we specialize in turning stalled AI initiatives into measurable profits within 90 days. Rather than hiring for ML infrastructure and model productionization, many mid-to-large enterprises are finding they can access equivalent capabilities for approximately 1/10th of a full-time engineer's salary—through our expert developers, production-ready systems, and built-in change management.
-We've built systems using LangChain, LangGraph, and AutoGen that handle exactly what your JD describes: training pipelines, deployment optimization, and observability frameworks. No prototypes. No pilots. Production systems that drive revenue impact.
-Before you commit to the full-time hire, I'd like to invite you to a complimentary 2-Day AI Opportunity Audit. We'll analyze your current processes, identify where AI can deliver immediate ROI, and show you the cost difference between hiring versus accelerating with our team.
-No commitment. No cost.
-Book your audit at: cal.com/omnithrivetech-ceo
-Warm regards,
-**[Your Name]**
-Senior B2B Outreach Specialist
+I noticed Andiamo is hiring for an ML Engineer to build production ML pipelines, manage model deployment infrastructure, and run large-scale experiments to measure impact. That's a critical hire for a pre-IPO brand scaling AI capabilities.
+Here's a perspective worth considering: 88% of AI pilots never reach production (CIO Magazine). The gap between model development and real-world deployment is where most fashion and retail brands lose momentum - and millions in potential value.
+At Omnithrive Technologies, we specialize in turning stalled AI initiatives into measurable results within 90 days. We build production-ready systems using LangChain, LangGraph, and AutoGen - the same infrastructure your ML Engineer would architect, but delivered as a fully operational solution rather than a multi-month hiring and onboarding cycle.
+More importantly: the capabilities you'd invest $100,000 annually to hire for can be delivered through our expert AI developers on demand for approximately 1/10th that cost. We handle model training, pipeline optimization, deployment monitoring, and A/B testing infrastructure - removing the hiring risk while accelerating time-to-value before your IPO window closes.
+We don't deliver pilots or prototypes. Everything is production-ready and integrated into your actual workflows from day one, with built-in change management so adoption sticks.
+I'd like to invite you to our complimentary 2-Day AI Opportunity Audit. No commitment. We'll map exactly where AI can unlock margin and efficiency for Andiamo's operations.
+Book here: cal.com/omnithrivetech-ceo
+Warm regards,
 Omnithrive Technologies
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+AI Value Acceleration Studio
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -2396,18 +2393,19 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Re: Your Engineer 2 search at Apex Companies</t>
+          <t>Apex Companies's AI capability gap - a different approach</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
           <t>Dear Apex Companies Team,
-I noticed you're hiring for an Engineer 2 role with AI/ML expertise to strengthen your consulting capabilities. Before committing $100,000 annually to a full-time hire, I wanted to share a perspective that might reshape how you approach this gap.
-Apex Companies delivers integrated solutions across water, environmental, and infrastructure sectors—domains where process inefficiency directly impacts project timelines and profitability. AI can accelerate your consulting workflows, automate data analysis, and enhance client delivery. However, 75% of AI projects fail to deliver ROI (IBM CEO Study, 2025), often because implementation is disconnected from your actual operational needs.
-Here's what's relevant: you can access production-ready AI capabilities for approximately $10,000—a fraction of your $100,000 hiring budget—without the overhead of recruitment, onboarding, or long-term employment costs. Rather than betting on a single engineer, Omnithrive Technologies delivers a custom-built AI system tailored to your consulting workflows, deployed within 90 days with built-in change management and ongoing support.
-We're not proposing pilots or prototypes. Our approach is ROI-first: measurable results or no engagement.
-If you're open to exploring how AI could multiply your engineering team's output without traditional hiring friction, I'd like to invite Apex Companies to a complimentary 2-Day AI Opportunity Audit. No commitment. No cost. Just clarity on where AI creates immediate value within your operations.
-You can schedule directly here: cal.com/omnithrivetech-ceo
+I noticed you are hiring for an Engineer 2 role with AI/ML expertise. This suggests you are building internal capability to integrate machine learning into your water, environmental, and infrastructure consulting workflows.
+Here is a direct observation: 75% of AI projects fail to deliver ROI, according to the IBM CEO Study 2025. Most organizations invest heavily in full-time hires - in your case, approximately $100,000 annually - only to discover that AI implementation requires specialized infrastructure, production-ready systems, and cross-functional change management that a single hire cannot provide alone.
+Omnithrive Technologies specializes in turning stalled AI initiatives into measurable business value within 90 days. Rather than building from scratch, we deploy production-ready systems tailored to your specific workflows - whether that is automating environmental data analysis, streamlining project workflows, or enhancing client reporting accuracy.
+Our approach costs approximately $10,000 for equivalent AI capabilities and delivery speed compared to hiring and onboarding. We handle the technical build, integration, and adoption strategy so your team can focus on core consulting work.
+Before committing resources to a new hire, consider a risk-free alternative: our complimentary 2-Day AI Opportunity Audit. We will map your highest-impact opportunities, show you what production-ready implementation looks like, and provide a clear ROI projection.
+If this resonates, I would welcome the opportunity to explore this with your leadership team.
+Book your free audit at cal.com/omnithrivetech-ceo or reach out directly.
 Warm regards,
 [Your Name]
 Senior B2B Outreach Specialist
@@ -2484,95 +2482,18 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>Re: Your AI Forward Deploy Engineer search</t>
+          <t>Arango's AI Forward Deploy Engineer - a different approach</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
           <t>Dear Arango Team,
-I noticed your search for an AI Forward Deploy Engineer—a role that bridges customer strategy and production-grade AI systems. That's a critical hire, and I wanted to share a perspective that might reshape how you think about filling it.
-The challenge is real: you need someone who can move seamlessly from whiteboarding RAG pipelines and managing data governance (CCPA, GDPR) to productionizing retrieval systems with proper CI/CD and observability. That's a $100,000/year investment for one person.
-Here's what's worth considering: 88% of AI pilots never reach production. Most organizations lack the operational infrastructure and cross-functional expertise to bridge that gap—which is precisely why that role exists on your team.
-Omnithrive Technologies specializes in doing exactly what that engineer would do—but across your entire AI initiative portfolio. We build end-to-end production systems (RAG pipelines, data connectors, retrieval optimization, embedding strategies) with built-in governance, CI/CD, and change management. Our model delivers equivalent AI capabilities for approximately 1/10th of a full-time hire's cost.
-Rather than filling one seat, you could accelerate multiple high-impact AI use cases simultaneously—and only invest in permanent headcount once value is proven and scaled.
-I'd like to explore whether this approach fits your strategy. We offer a complimentary 2-Day AI Opportunity Audit—no commitment, no cost—to identify where AI can deliver measurable ROI for Arango within 90 days.
-Available to discuss: cal.com/omnithrivetech-ceo
-Warm regards,
-[Your Name]
-Senior B2B Outreach Specialist
-Omnithrive Technologies
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Archer Recruitment</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>https://archerrecruitment.com/</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Archer Recruitment is a specialist search consultancy that recruits for roles in the construction, real estate, and engineering sectors. They operate in Asia-Pacific, North America, the UK, and Europe, covering the full project lifecycle.</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Construction/Real Estate/Engineering</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence Engineer</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Dublin, County Dublin, Ireland</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>Ben Ross</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>Principle Consultant</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>ben@archerrecruitment.com</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>Re: your Artificial Intelligence Engineer search</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>Dear Ben Ross,
-I noticed Archer Recruitment is currently hiring for an Artificial Intelligence Engineer role across your Asia-Pacific, North America, UK, and European operations. Given the complexity of deploying AI across multiple regions and project lifecycles in construction and real estate, I wanted to share a perspective that may prove valuable.
-The challenge most recruitment firms face isn't finding AI talent—it's building production-ready systems that actually deliver measurable value. Research shows 88% of AI pilots never reach production, which means your new hire could spend months building prototypes that don't solve your core inefficiency problems.
-Here's what we've found works better: Rather than a full-time AI Engineer at $100,000 annually, organizations often achieve far greater returns by deploying purpose-built AI systems tailored to their specific workflows. We deliver production-ready AI capabilities in 90 days for approximately one-tenth of that cost—with built-in adoption and change management included.
-For Archer Recruitment specifically, this could mean AI-driven candidate matching, automated pipeline optimization, or intelligent scheduling across your global teams—without the 12-month hiring and onboarding cycle.
-I'd like to invite you to a complimentary 2-Day AI Opportunity Audit. No commitment. We'll map your highest-impact AI opportunities and show exactly what's achievable in your first 90 days.
-You can book directly here: cal.com/omnithrivetech-ceo
+I came across your search for an AI Forward Deploy Engineer and noticed something worth exploring: you're building RAG pipelines, managing data governance (CCPA/GDPR), and moving AI from proof-of-concept to production - exactly the work that 88% of AI pilots never complete (CIO Magazine).
+Here is the challenge: hiring a specialized engineer at $100,000 annually locks you into a fixed cost while you're still defining what production-ready AI looks like for your operations. You need someone to identify high-value use cases, architect end-to-end retrieval pipelines, and operationalize them with proper CI/CD and observability - but that expertise is expensive to own full-time, especially when most organizations don't yet know their highest-impact AI opportunity.
+Omnithrive Technologies works differently. We deliver equivalent AI Forward Deploy capabilities - from customer engagement analysis through RAG implementation, chunking strategies, embeddings optimization, and production hardening - at approximately 1/10th of that annual investment. More importantly, we guarantee production-ready systems within 90 days, not extended pilots.
+Rather than hiring, consider this: a free 2-Day AI Opportunity Audit that maps your highest-value AI use cases, technical requirements, and a clear path to measurable ROI. No commitment. No cost. You'll walk away with a concrete roadmap and an accurate build investment.
+If this resonates, I would welcome a brief conversation.
+Book your audit here: cal.com/omnithrivetech-ceo
 Warm regards,
 Omnithrive Technologies
 AI Value Acceleration Studio
@@ -2581,6 +2502,81 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Archer Recruitment</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>https://archerrecruitment.com/</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Archer Recruitment is a specialist search consultancy that recruits for roles in the construction, real estate, and engineering sectors. They operate in Asia-Pacific, North America, the UK, and Europe, covering the full project lifecycle.</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Construction/Real Estate/Engineering</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Dublin, County Dublin, Ireland</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Ben Ross</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Principle Consultant</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>ben@archerrecruitment.com</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>A thought on Archer Recruitment's AI engineering gap</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>Dear Ben Ross,
+I noticed Archer Recruitment is actively hiring for an Artificial Intelligence Engineer role. Given the complexity of building and deploying production-grade AI systems across your global recruitment operations, I wanted to share a perspective that might prove valuable.
+The challenge with traditional hiring for AI capability is both cost and execution risk. A full-time AI Engineer at your budget level ($100,000 annually) typically brings either junior-level expertise or extended ramp-up time before delivering measurable impact. More critically, 75% of AI projects fail to deliver ROI, according to the IBM CEO Study 2025 - often because isolated hires lack the infrastructure, process optimization, and change management needed for real results.
+At Omnithrive Technologies, we operate differently. We deliver production-ready AI systems within 90 days using agentic frameworks (LangChain, LangGraph, AutoGen) and intelligent automation platforms (n8n, Zapier). For recruitment workflows - candidate screening, process automation, capability matching - our cost is approximately one-tenth of a full-time hire: around $10,000 for high-impact deployment, not $100,000 annually.
+More importantly, we guarantee measurable results. No pilots. No prototypes. Just working systems that integrate seamlessly into your existing operations.
+I would like to invite you to a complimentary 2-Day AI Opportunity Audit. We will assess your specific recruitment challenges and outline exactly where AI can accelerate hiring cycles and reduce manual overhead - with zero commitment and no cost.
+You can book directly here: cal.com/omnithrivetech-ceo
+Warm regards,
+Omnithrive Technologies
+AI Value Acceleration Studio
+admin@omnithrivetech.com | +91 97426 09264</t>
+        </is>
+      </c>
+    </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
@@ -2633,23 +2629,24 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>A thought on Arm's agentic AI build</t>
+          <t>A thought on Arm's AI build</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
           <t>Dear Arm Team,
-I noticed your Graduate ML Software Engineer posting emphasizes agentic AI and edge AI capabilities—critical technologies for Arm's positioning in autonomous compute. Building these systems in-house is essential, but the timeline and cost present a familiar challenge.
-Here's the reality: 88% of AI pilots never reach production (CIO Magazine). Most organizations invest heavily in talent acquisition, only to face delays in deployment and ROI validation. Your $100,000 annual budget for a single hire gets you one developer and a multi-month ramp-up period.
-At Omnithrive Technologies, we deliver production-ready agentic AI systems—built on LangGraph, CrewAI, and the same tech stack your team values—within 90 days. For approximately one-tenth of your full-time hire cost ($10,000), we can accelerate your MVP development, validate your agentic AI assumptions in edge compute environments, and get your systems operational while you build long-term internal capacity.
-We don't deliver pilots or prototypes. We build systems that work, immediately measurable and designed for your specific workflows.
-Rather than propose solutions without understanding your exact bottleneck, I'd like to invite you to a complimentary 2-Day AI Opportunity Audit. No cost, no commitment—just a clear picture of where agentic AI can generate immediate value for Arm.
-You can book directly at cal.com/omnithrivetech-ceo, or reply with your availability.
+I noticed your Graduate ML Software Engineer opening emphasizes agentic AI and edge AI deployment - critical capabilities for powering intelligent systems across automotive, infrastructure, and IoT markets.
+Here's the reality: building that expertise internally is expensive and slow. A full-time ML engineer at your level costs approximately $100,000 annually. Yet 88% of AI pilots never reach production, meaning significant investment often delivers minimal business impact.
+Omnithrive Technologies specializes in the opposite approach: we build production-ready agentic AI systems - not prototypes - in 90 days or less. Our team works with LangChain, LangGraph, and AutoGen to deploy systems that integrate directly into your workflows. The result is measurable ROI, not theoretical capability.
+For a fraction of what you'd spend on a single hire - roughly $10,000 versus $100,000 annually - you could accelerate your AI initiatives while your internal team focuses on strategic architecture and edge optimization.
+Rather than lengthy recruitment cycles and onboarding delays, we offer a clearer path: a complimentary 2-Day AI Opportunity Audit to identify where agentic AI can unlock immediate value for Arm's product roadmap and operational efficiency.
+If you're open to exploring how production-grade AI capabilities can enhance your hiring timeline and technical delivery, I'd welcome a brief conversation.
+You can book directly at cal.com/omnithrivetech-ceo or reach out at admin@omnithrivetech.com.
 Warm regards,
 [Your Name]
 Senior B2B Outreach Specialist
 Omnithrive Technologies
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+AI Value Acceleration Studio</t>
         </is>
       </c>
     </row>
@@ -2717,25 +2714,24 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Context window retrieval — a build vs. hire question</t>
+          <t>On building Asana's AI retrieval layer</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
           <t>Dear Gavin Davies,
-I've reviewed your Software Engineer opening for the AI Retrieval team, and I noticed something worth considering: you're hiring to build relevance-matching systems that surface work graph content into LLM context windows—foundational AI infrastructure that's critical, expensive, and notoriously difficult to execute.
-Here's the challenge: 75% of AI projects fail to deliver ROI (IBM CEO Study, 2025). Most enterprises either hire senior talent at $100,000+ annually or attempt pilots that never reach production. Your hire falls into the former category—significant investment for a single specialized capability.
-We work differently.
-At Omnithrive Technologies, we specialize in turning stalled AI initiatives into production-ready systems within 90 days. We've built retrieval and context-optimization pipelines using LangChain, LangGraph, and advanced vector retrieval strategies—the exact technical domain your team is addressing. Rather than a traditional hire, you could access equivalent AI engineering capability for approximately 1/10th the annual cost, freeing that $100,000 budget for scaling proven systems.
-What makes this feasible: we don't build pilots. We build production-ready systems with built-in adoption and change management—meaning your team gets working infrastructure immediately, not prototypes.
-I'd like to explore whether Asana has other retrieval or AI infrastructure gaps where a rapid, cost-effective build could accelerate your roadmap.
-Would you be open to a complimentary 2-Day AI Opportunity Audit? No commitment required. You can book directly at cal.com/omnithrivetech-ceo.
-Warm regards,
-[Your Name]
-Senior B2B Outreach Specialist
+I noticed Asana is hiring for your AI Retrieval team-specifically to power context window optimization and work graph retrieval for your LLM features. That's a critical capability.
+Here's what caught my attention: you're investing roughly $100,000 annually to hire a Software Engineer for this role. Yet 88% of AI pilots never reach production (CIO Magazine), and the talent acquisition timeline alone stretches months.
+At Omnithrive Technologies, we specialize in building production-ready AI systems-not prototypes. We've worked extensively with retrieval architectures, context optimization, and LLM integration using LangChain, LangGraph, and similar frameworks. We could architect and deploy an equivalent retrieval capability for your work graph at approximately one-tenth of that hire cost, with measurable results in 90 days.
+The difference: you get a fully functional system integrated into your workflows, with built-in change management and ongoing optimization-not a headcount expense or a pilot that stalls.
+I'm not suggesting this replaces your hiring strategy entirely. Rather, it's a faster, lower-risk path to validate your retrieval architecture while you build your permanent team.
+I'd like to invite you to our complimentary 2-Day AI Opportunity Audit. We'll map your specific retrieval and context challenges against proven solutions, with no commitment required.
+You can book directly here: cal.com/omnithrivetech-ceo
+Warm regards,
 Omnithrive Technologies
+AI Value Acceleration Studio
 admin@omnithrivetech.com
-+91 97426 09264</t>
+WhatsApp: +91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -2819,23 +2815,22 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>Re: your MLOps Engineer search at Atos</t>
+          <t>A thought on Atos's MLOps Engineer search</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
           <t>Dear Andy Franks,
-I noticed Atos is hiring for an MLOps Engineer to design CI/CD pipelines, containerize AI applications with Docker and Kubernetes, and maintain model versioning workflows across production environments.
-That's a critical role—and typically a $100,000+ annual investment. I wanted to share a perspective that may be worth considering.
-According to IBM's 2025 CEO Study, 75% of AI projects fail to deliver ROI. Many enterprises face this gap precisely because they build infrastructure without clarity on which AI initiatives will actually move the needle. The result: robust MLOps systems managing pilots that never reach production value.
-At Omnithrive Technologies, we work with mid-to-large enterprises to reverse this. Rather than hiring full-time for speculative builds, we deliver production-ready AI systems in 90 days—with measurable ROI baked in from day one. For roughly one-tenth of what you'd spend on a full-time MLOps hire ($10,000 versus $100,000), you get expert developers proficient in the exact stack your team uses: Kubernetes, GitHub Actions, MLflow, and model deployment pipelines.
-We don't hand off prototypes. We build systems that scale only when value is proven, and we embed change management so adoption sticks.
-Before committing to a permanent hire, it may be worth validating which AI workflows will actually drive business impact. That's precisely what our complimentary 2-Day AI Opportunity Audit covers—no commitment, no cost.
-If this resonates, I'd welcome a brief conversation. You can book directly at cal.com/omnithrivetech-ceo.
+I noticed Atos is hiring for an MLOps Engineer role focused on CI/CD pipeline automation, model versioning, and Kubernetes deployment. That's a critical hire-but it raises an interesting question: what if you could access equivalent capabilities without the $100,000 annual commitment?
+Here's the reality: 88% of AI pilots never reach production (CIO Magazine). Most organizations struggle not with hiring talent, but with actually operationalizing AI systems that deliver measurable business value. Your team is building the infrastructure-but infrastructure alone doesn't guarantee ROI.
+At Omnithrive Technologies, we specialize in turning stalled AI initiatives into production-ready systems within 90 days. We work directly with your existing stack: Docker, Kubernetes, GitHub Actions, MLflow, and Kuberent-automating the exact workflows your MLOps Engineer would own. The difference: we deliver outcome-focused systems, not just infrastructure maintenance.
+Our model is straightforward. Instead of carrying a $100K salary cost, enterprises typically engage us for approximately $10K to build and deploy high-impact AI solutions. You get production-grade MLOps workflows, change management, and adoption support-without the overhead.
+I'd like to invite Atos to a complimentary 2-Day AI Opportunity Audit. No cost, no commitment. We'll assess where your AI initiatives are stalling and show you a concrete path to production and measurable ROI.
+If this resonates, please schedule time here: cal.com/omnithrivetech-ceo
 Warm regards,
 Omnithrive Technologies
 AI Value Acceleration Studio
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+admin@omnithrivetech.com | +91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -2893,17 +2888,18 @@
       <c r="O30" s="2" t="inlineStr">
         <is>
           <t>Dear Avaus Team,
-I've followed your recent hiring for a Data Scientist Consultant and noticed something worth considering: you're budgeting $100,000 annually for generative AI and predictive analytics capabilities—yet 88% of AI pilots never reach production (CIO Magazine), meaning the hire alone doesn't guarantee delivered value.
-At Omnithrive Technologies, we deliver equivalent AI capabilities—production-ready systems built on LangChain, LangGraph, and Claude—for approximately 1/10th of that cost. More importantly, we guarantee measurable results within 90 days, not prototypes or pilots.
-Given Avaus's focus on turning data into business growth for your clients, I suspect your internal teams face similar pressures: building AI solutions that actually scale, integrating generative AI into existing workflows, and proving ROI before expanding. These are execution challenges, not hiring challenges.
-Rather than onboarding a consultant, consider a different approach: a free 2-Day AI Opportunity Audit where we map your highest-impact AI use cases, identify quick-win implementations, and show you exactly what production-ready systems would look like—customized to your stack and workflows. No commitment. No cost.
-Many SaaS and analytics firms have used this audit to either build faster in-house, or partner with us for high-impact MVPs that prove value before scaling.
-I'd welcome a brief conversation about whether this approach makes sense for Avaus.
-Book your audit at: cal.com/omnithrivetech-ceo
-Warm regards,
-Omnithrive Technologies  
-AI Value Acceleration Studio  
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+I noticed you are actively recruiting for a Data Scientist Consultant to strengthen your generative AI and predictive analytics capabilities. Given Avaus's mission to help enterprises turn data into measurable business growth, I wanted to reach out with a perspective that may prove valuable.
+You are likely budgeting around $100,000 annually for this hire. We can deliver equivalent AI capabilities - including generative AI model implementation, predictive analytics systems, and production-ready automation - for approximately one-tenth of that investment.
+The challenge is not finding talent; it is finding talent that delivers measurable ROI. According to an IBM CEO Study in 2025, 75% of AI projects fail to deliver ROI. Most organizations hire brilliantly but struggle with deployment, adoption, and scaling. The solution is not always a full-time headcount.
+Omnithrive Technologies specializes in turning failing or stalled AI initiatives into measurable profits within 90 days. We build production-ready systems - not pilots - customized to your exact workflows. Our team works across LangChain, LangGraph, CrewAI, and other agentic AI frameworks. We embed change management and adoption support from day one, ensuring your AI initiatives reach production and drive real value.
+Rather than commit to a hire immediately, consider a risk-free alternative: our complimentary 2-Day AI Opportunity Audit. We will assess your current data and AI landscape, identify high-impact opportunities, and provide a concrete roadmap - at no cost and with no obligation.
+I would welcome a brief conversation about how this might serve Avaus.
+Please schedule your free audit here: cal.com/omnithrivetech-ceo
+Warm regards,
+Omnithrive Technologies
+AI Value Acceleration Studio
+admin@omnithrivetech.com
+WhatsApp: +91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -2967,25 +2963,25 @@
       <c r="M31" s="3" t="inlineStr"/>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>Re: Your Data Engineer search at Avenga</t>
+          <t>Data Engineer hire - a more efficient path for Avenga</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
           <t>Dear Markus Stuhr,
-I noticed Avenga is actively hiring for a Data Engineer role—a critical position given your focus on reshaping sectors through intelligent automation and AI-driven solutions.
-Here's what caught my attention: You're budgeting approximately $100,000 annually for this hire. Yet 88% of AI pilots never reach production (CIO Magazine), meaning traditional hiring alone often fails to deliver measurable business impact.
-At Omnithrive Technologies, we take a different approach. Rather than filling headcount, we deliver production-ready AI systems that integrate directly into your existing workflows. We've built expertise across the exact stack your team likely needs—LangChain, LangGraph, agentic automation, and intelligent process orchestration—and we deploy custom solutions in 90 days or less.
-The financial advantage is striking: our expert AI developers cost approximately $10,000 per engagement—one-tenth of your Data Engineer budget—while delivering equivalent capabilities without the overhead of full-time employment, onboarding delays, or retention risk.
-More importantly, we guarantee measurable results. If your AI initiatives aren't generating concrete ROI within 90 days, we don't charge you.
-I'd like to invite you to explore this without commitment. Our complimentary 2-Day AI Opportunity Audit will identify where intelligent automation can unlock the most value for Avenga—whether that's streamlining data pipelines, automating knowledge work, or scaling your intelligent automation capabilities.
-If this resonates, I'd welcome a brief conversation.
-Book your audit here: cal.com/omnithrivetech-ceo
+I noticed Avenga is actively hiring for a Data Engineer role - a position typically commanding $100,000+ annually. Before you commit to that investment, I wanted to share a perspective that may reshape how you approach AI capability-building.
+At Omnithrive Technologies, we specialise in turning stalled or failing AI initiatives into production-ready systems within 90 days. Given Avenga's focus on data and AI services, I suspect you're facing a common challenge: the gap between pilot projects and deployed, revenue-generating solutions.
+Here's what caught my attention: 88% of AI pilots never reach production (CIO Magazine). This typically happens because organisations either lack the specialised expertise to scale, or they're building generic solutions instead of systems tailored to their exact workflows.
+We work differently. Rather than hiring a single Data Engineer at $100,000 annually, clients access our team of expert AI developers - fluent in LangChain, LangGraph, AutoGen, and production automation tools - at approximately $10,000 for a comprehensive, custom-built AI system. You get equivalent (or superior) capability at one-tenth the cost, plus built-in change management to ensure adoption.
+I'm not asking for a commitment. Instead, I'd like to invite you to explore whether an AI opportunity exists within Avenga that warrants a deeper look.
+Our complimentary 2-Day AI Opportunity Audit identifies high-impact, feasible initiatives - no cost, no obligation. If it uncovers genuine potential, we can build a production-ready MVP in weeks, not months.
+Would you be open to a brief conversation? You can book directly at cal.com/omnithrivetech-ceo.
 Warm regards,
 [Your Name]
 Senior B2B Outreach Specialist
 Omnithrive Technologies
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -3061,12 +3057,13 @@
       <c r="O32" s="2" t="inlineStr">
         <is>
           <t>Dear Rebecca McClellan,
-I noticed Avolta is hiring for a Global Data Scientist Developer to build scalable analytical solutions and transform complex data into actionable insights across your organization. That's a critical role—and a significant investment at $100,000 annually.
-I wanted to share a perspective: 75% of AI projects fail to deliver ROI, according to the IBM CEO Study 2025. Most organizations either hire expensive in-house talent or deploy generic tools that never reach production. Neither solves your core problem.
-At Omnithrive Technologies, we specialize in turning stalled AI initiatives into measurable business value within 90 days. We've built production-ready systems—not pilots—that handle exactly what your JD describes: working with unstructured data, developing analytical models that answer impactful business questions, and creating data products that drive decision-making across global stakeholders.
-Here's what matters: we deliver equivalent AI capabilities for approximately 1/10th of a full-time hire's cost. Where you'd invest $100,000 annually in a Data Scientist Developer role, our expert AI developers (proficient in the exact tech stack you need) cost roughly $10,000—fully deployed and production-ready.
-Rather than commit to another lengthy hiring cycle or risky pilot, I'd like to invite Avolta to our complimentary 2-Day AI Opportunity Audit. No commitment. No cost. We'll assess where your data science and analytics initiatives can generate immediate ROI.
-If this resonates, you can book directly here: cal.com/omnithrivetech-ceo
+I noticed Avolta is actively recruiting for a Global Data Scientist Developer to build scalable analytical solutions and transform complex data into actionable insights across your organization. This is precisely the type of high-impact capability that travel retail companies need to stay competitive.
+Here is what caught my attention: your team is tasked with designing models and developing data products that drive decision-making across global stakeholders - work that typically requires months of hiring, onboarding, and iteration. Yet 75% of AI projects fail to deliver ROI, according to the IBM CEO Study 2025. The risk of misalignment between a new hire's capabilities and your exact workflow requirements is substantial.
+At Omnithrive Technologies, we specialize in delivering production-ready AI systems tailored to your specific processes - not generic tools or lengthy pilots. We work with travel and retail organizations to automate data workflows, unstructured data processing, and BI model development in weeks, not months.
+Here is the financial reality: your budgeted salary for this role is approximately $100,000 annually. We can deliver equivalent AI capabilities - custom-built for Avolta's data challenges - for roughly one-tenth of that cost, with measurable results guaranteed within 90 days.
+Rather than commit to a full-time hire immediately, I would like to offer a complimentary 2-Day AI Opportunity Audit. We will analyze your current data workflows, unstructured data challenges, and BI requirements to identify where AI can drive immediate value.
+No commitment required. No cost.
+Please book a time here: cal.com/omnithrivetech-ceo
 Warm regards,
 Omnithrive Technologies
 AI Value Acceleration Studio
@@ -3134,22 +3131,25 @@
       <c r="M33" s="3" t="inlineStr"/>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>AI for your engineering recruitment pipeline</t>
+          <t>Re: Your INGEGNERI MECCANICI search - an AI alternative</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
           <t>Dear Francesca Rassaval,
-I noticed AxL S.p.A. - Agenzia per il Lavoro is actively recruiting Ingegneri Meccanici for progettazione roles. Given the technical screening and candidate evaluation demands in mechanical engineering recruitment, I wanted to reach out with a perspective that may be relevant.
-Most staffing and HR teams are investing heavily in technical hiring—often allocating €100,000+ annually for specialist roles or building internal AI capabilities. Here's what we're observing: 75% of AI projects fail to deliver ROI, particularly when organizations attempt to build custom recruitment workflows without production-ready infrastructure.
-At Omnithrive Technologies, we specialize in turning stalled AI initiatives into measurable business outcomes within 90 days. For recruitment operations like yours, this means automating candidate screening, technical assessment validation, and skill-matching workflows—delivering capabilities equivalent to a full-time technical hire for approximately one-tenth the cost (roughly €10,000 versus €100,000 annually).
-We work with mid-to-large enterprises across HR, staffing, and logistics to build production-ready systems that integrate with your existing workflows. No pilots. No prototypes. Just measurable efficiency gains and faster time-to-hire.
-I'd like to invite you to a complimentary 2-Day AI Opportunity Audit—at no cost and with no commitment. We'll assess your specific recruitment processes and identify where AI can create immediate value.
-If this interests you, please book a time here: cal.com/omnithrivetech-ceo
-Alternatively, feel free to reach out directly at admin@omnithrivetech.com or via WhatsApp: +91 97426 09264.
-Warm regards,
+I noticed AxL S.p.A. - Agenzia per il Lavoro is actively recruiting Ingegneri Meccanici for progettazione roles, with an annual budget of approximately $100,000 per hire.
+I wanted to share a perspective: what if you could accelerate your design and selection workflows without the recruitment costs and lead time?
+At Omnithrive Technologies, we specialize in building production-ready AI systems that automate complex engineering and staffing processes. For HR and staffing organizations like yours, we've deployed agentic AI solutions that streamline candidate screening, technical assessment automation, and project coordination - capabilities that typically require specialized engineering hires.
+Here is the reality: 75% of AI projects fail to deliver ROI, according to the IBM CEO Study 2025. Most organizations invest in pilots that never reach production. We are different. We guarantee measurable results within 90 days, and our typical investment is roughly one-tenth of what you would spend on a full-time engineer - meaning you could access equivalent AI capabilities for approximately $10,000 rather than $100,000.
+Our approach is straightforward: custom-built systems (not generic tools), production-ready deployment (not prototypes), and ongoing support to ensure adoption.
+I would like to invite you to a complimentary 2-Day AI Opportunity Audit. We will assess your current workflows, identify high-impact automation opportunities, and present a clear value roadmap with no commitment required.
+Please book at your convenience: cal.com/omnithrivetech-ceo
+Warm regards,
+[Your Name]
+Senior B2B Outreach Specialist
 Omnithrive Technologies
-AI Value Acceleration Studio</t>
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -3247,22 +3247,18 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>On BCG X's AI Engineer hiring — a cost perspective</t>
+          <t>BCG X's AI Engineer search - a cost perspective</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
           <t>Dear Rebecca Milian,
-I noticed BCG X is actively recruiting an AI Engineer for your Netherlands office, budgeted at approximately $100,000 annually. Given your division's focus on helping enterprises innovate through technology build and design, I wanted to share a relevant observation.
-The challenge isn't finding AI talent—it's deploying AI that actually works in production. Research shows 88% of AI pilots never reach production (CIO Magazine), and organizations often hire full-time engineers only to discover their initiatives lack clear business alignment or measurable ROI.
-At Omnithrive Technologies, we've built a different model. Rather than adding headcount, we deliver production-ready AI systems custom-built to your clients' workflows—generating measurable profit within 90 days. The economics are compelling: equivalent AI capability and delivery at approximately 1/10th the cost of a full-time hire.
-For BCG X specifically, this means you could:
-- Accelerate client AI implementations without long hiring cycles
-- De-risk AI projects before recommending full-scale investment
-- Offer clients faster time-to-value on their innovation initiatives
-We work across agentic AI (LangChain, LangGraph, AutoGen, CrewAI) and have deployed production systems in SaaS, manufacturing, and logistics—sectors where process efficiency directly drives competitive advantage.
-Rather than a conversation about hiring, I'd like to offer something more valuable: a complimentary 2-Day AI Opportunity Audit. No commitment. This would help you identify where AI can genuinely move your clients' needle.
-Would this be worth exploring? You can book directly at cal.com/omnithrivetech-ceo.
+I noticed BCG X is hiring for an AI Engineer role in the Netherlands with a budget of approximately $100,000 annually. Given your division's focus on helping enterprises build competitive AI capabilities, I wanted to share a perspective that may be relevant to your staffing strategy.
+88% of AI pilots never reach production, according to CIO Magazine. The gap between hiring talent and delivering measurable business value remains one of the most costly challenges in enterprise AI. Most organizations invest heavily in personnel but struggle to translate technical capability into ROI-ready systems.
+At Omnithrive Technologies, we work with mid-to-large enterprises across SaaS, consulting, and other industries to deliver production-ready AI systems within 90 days. Rather than extending hiring cycles or managing long onboarding periods, we provide equivalent AI engineering capability - including agentic AI development with LangChain, LangGraph, and AutoGen - at approximately 1/10th the cost of a full-time hire. This approach allows your team to focus on client advisory while we handle the technical build and deployment.
+Given BCG X's mandate to accelerate client innovation, this model may be worth exploring for your own internal AI initiatives or as an offering you could recommend to clients facing similar constraints.
+I would welcome a brief conversation to assess whether there are high-impact AI opportunities at BCG X that could benefit from our production-first approach. We offer a complimentary 2-Day AI Opportunity Audit at no cost or commitment.
+Would you be open to exploring this? You can schedule directly at cal.com/omnithrivetech-ceo.
 Warm regards,
 [Your Name]
 Senior B2B Outreach Specialist
@@ -3365,24 +3361,24 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>Rethinking BairesDev's AI talent strategy</t>
+          <t>Rethinking AI talent costs at BairesDev</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
           <t>Dear Katheleen Rosas,
-I've reviewed BairesDev's Senior Software Engineer (Go) posting and noticed your focus on distributed backend systems, LLM integration, and vector search technologies. Building production-grade AI infrastructure requires deep technical expertise—and your $100,000 annual budget reflects that investment need.
-Here's a perspective worth considering: rather than allocating that full budget to a single full-time hire, what if you could access equivalent AI engineering capabilities for approximately one-tenth of that cost?
-At Omnithrive Technologies, we specialize in turning stalled AI initiatives into measurable production systems within 90 days. We work with the exact tech stack your team needs—LangChain, LangGraph, AutoGen, and vector search architectures—to build custom, scalable solutions. Our developers deliver production-ready systems, not prototypes or pilots.
-The challenge is real: 88% of AI pilots never reach production (CIO Magazine). Most organizations struggle to bridge the gap between proof-of-concept and scaled deployment.
-Rather than hiring incrementally, consider this: invest a fraction of that budget in a high-impact MVP that proves AI value within your existing distributed systems architecture. You retain the option to scale with permanent hires once ROI is validated.
-I'd like to invite you to a complimentary 2-Day AI Opportunity Audit—no commitment, no cost. We'll assess how AI can accelerate your development capabilities and identify immediate high-impact opportunities.
-Book your audit here: cal.com/omnithrivetech-ceo
+I've been following BairesDev's growth in distributed backend systems and LLM-native applications. Your current search for a Senior Software Engineer (Go) reflects a broader challenge: building production-grade AI capabilities requires specialized talent that commands premium compensation.
+Here's what caught my attention: your team is hiring to "diagnose and resolve performance and reliability issues across distributed backend services" while managing vector search and RAG implementations. These are precisely the areas where enterprises struggle most-88% of AI pilots never reach production, according to CIO Magazine.
+At Omnithrive Technologies, we've built a different model. Rather than hiring full-time engineers at $100,000 annually, enterprises partner with us to deliver production-ready AI systems in 90 days-for approximately one-tenth of that cost. We specialize in agentic AI, LangGraph, LangChain, and vector-native architectures. Our developers work exclusively on high-impact implementations, not staffing rotations.
+For BairesDev specifically, this could mean accelerating your AI delivery capabilities without expanding headcount or increasing salary commitments. You gain expert-level Go and distributed systems optimization focused entirely on measurable outcomes.
+We're not proposing another pilot or prototype. We're offering a complimentary two-day AI Opportunity Audit to map where your AI initiatives stand and what's genuinely achievable in your first 90 days. No commitment. No cost.
+If this resonates, I'd welcome a brief conversation or you can book directly at cal.com/omnithrivetech-ceo.
 Warm regards,
 [Your Name]
 Senior B2B Outreach Specialist
 Omnithrive Technologies
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -3467,23 +3463,24 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>On Bambuser's AI &amp; Automation Engineer hire</t>
+          <t>A thought on Bambuser's internal automation roadmap</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
           <t>Dear Kate Hurrell,
-I noticed Bambuser is scaling your internal systems with the same ambition you bring to video commerce. Your job description specifically calls for someone to "find workflows that are slow, manual, or unnecessarily complex and automate them"—this is precisely where most organizations leave significant value on the table.
-Here's the challenge: 88% of AI pilots never reach production (CIO Magazine), and the engineers who can bridge that gap command premium salaries. Your posted budget reflects that reality—approximately $100,000 annually for an AI &amp; Automation Engineer.
-We work differently. Omnithrive Technologies specializes in turning stalled AI initiatives into production-ready systems within 90 days. Rather than hiring full-time, we deliver equivalent capabilities at roughly one-tenth the cost. For your knowledge base automation, workflow optimization, and integration needs across teams, this translates to meaningful budget efficiency without sacrificing execution quality.
-We don't build pilots or prototypes. Our systems are built for your exact workflows, deployed with embedded change management, and proven before scaling.
-I'd like to propose a complimentary 2-Day AI Opportunity Audit. No commitment, no cost—just a clear map of where AI can reduce friction and unlock capacity across your organization. This isn't a sales conversation; it's a diagnostic to show you what's possible within your constraints.
+I've been following Bambuser's expansion, and I noticed your current search for an AI &amp; Automation Engineer. The role description caught my attention - specifically your need to identify workflows that are "slow, manual, or unnecessarily complex" and automate them across every team.
+That's exactly the problem we solve at Omnithrive Technologies.
+Here's the reality: 88% of AI pilots never reach production (CIO Magazine). Most companies hire full-time engineers hoping to build internal automation systems, only to face delays, scope creep, and incomplete deployments. Your $100,000 annual budget for this hire is substantial - but what if you could access equivalent AI capabilities and deliver production-ready automation systems for approximately 1/10th of that investment?
+We specialize in turning stalled AI initiatives into measurable results within 90 days. Our team builds custom agentic systems using LangChain, LangGraph, and modern automation tools like n8n to eliminate the manual work that slows down operations. We don't deliver pilots or prototypes - we deploy production-ready systems that integrate seamlessly with your existing workflows and scale only when value is proven.
+Rather than extending your hiring timeline, consider a different approach: a free, two-day AI Opportunity Audit where we map your highest-friction workflows and show you exactly what's possible. No commitment. No cost.
 If this resonates, I'd welcome a brief conversation.
-Book here: cal.com/omnithrivetech-ceo
-Warm regards,
-[Your Name]
-Senior B2B Outreach Specialist
-Omnithrive Technologies</t>
+Book your audit here: cal.com/omnithrivetech-ceo
+Warm regards,
+Omnithrive Technologies
+AI Value Acceleration Studio
+admin@omnithrivetech.com
+WhatsApp: +91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -3547,24 +3544,22 @@
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>Bark.com's MLOps build — a cost consideration</t>
+          <t>A thought on Bark.com's AI build</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
           <t>Dear Bark.com Team,
-I noticed you're hiring for an MLOps Engineer to own your data lifecycle and scale event tracking across teams. That's a critical role—especially since those events directly fuel your AI feature stores and models.
-Here's the reality: you're budgeting approximately $100,000 annually for this hire. Yet 75% of AI projects fail to deliver ROI, often because infrastructure and MLOps work become bottlenecks rather than accelerators.
-At Omnithrive Technologies, we specialize in turning stalled or underperforming AI initiatives into measurable production systems within 90 days. We work across Python, AWS, FastAPI, and feature store architectures—precisely the stack you're building on. More importantly, we deliver equivalent AI infrastructure and LLMOps capabilities for approximately $10,000, or roughly 1/10th of a full-time hire's annual cost.
-Rather than waiting months to onboard a single engineer and then iterating on infrastructure, you could have a production-ready AI operations framework in place within weeks, with built-in monitoring, scaling, and cost optimization already configured for your event streaming platform.
-We're not proposing a pilot. We deliver production systems or no fee.
-I'd like to offer a complimentary 2-Day AI Opportunity Audit—no commitment, no cost. We'll map your current data and MLOps challenges, identify high-impact automation opportunities, and show you exactly where AI infrastructure can accelerate your feature velocity.
-If this interests you, you can book a time here: cal.com/omnithrivetech-ceo
-Warm regards,
-[Your Name]
-Senior B2B Outreach Specialist
+I've been following your MLOps Engineer opening with interest. The role speaks to a real challenge: scaling event tracking infrastructure to fuel your AI feature stores and models across teams-a high-impact, complex problem that demands the right expertise.
+Here's what caught my attention: You're budgeting approximately $100,000 annually for a full-time MLOps hire to own your data lifecycle, validation, and model serving infrastructure. That investment is necessary, but it's also only the beginning. Most organizations in your position discover that hiring alone doesn't guarantee results. According to IBM's 2025 CEO Study, 75% of AI projects fail to deliver ROI-and 88% of AI pilots never reach production.
+At Omnithrive Technologies, we've built an alternative approach. Rather than hiring and hoping, we deliver production-ready AI systems within 90 days. For roughly 1/10th of what a full-time MLOps engineer costs ($10,000 versus $100,000), we can audit your current data pipeline, identify immediate bottlenecks in your event tracking and feature store infrastructure, and build a high-impact MVP that directly supports your models.
+This isn't theoretical. We work with SaaS companies like yours-companies managing real-time data, scaling ML infrastructure, and trying to move fast without breaking systems.
+I'd like to invite you to a complimentary 2-Day AI Opportunity Audit. No commitment, no cost. We'll assess your current setup and show you exactly where AI value can be captured immediately.
+Book here: cal.com/omnithrivetech-ceo
+Warm regards,
 Omnithrive Technologies
-admin@omnithrivetech.com | +91 97426 09264</t>
+AI Value Acceleration Studio
+admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -3638,187 +3633,188 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Re: Your AI Engineer search at Bayer</t>
+          <t>A thought on Bayer's AI Engineer search</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
           <t>Dear Stefan Oelrich,
-I noticed Bayer is actively hiring for an AI Engineer to develop agentic AI solutions and industrialize generative AI models for production deployment across your Life Science operations. That's a critical hire—and typically a $100,000+ annual investment.
-Here's the challenge: 88% of AI pilots never reach production (CIO Magazine). Most organizations build prototypes that stall. You need someone who can deliver scalable, production-ready AI systems—not demos.
-This is where our model differs fundamentally. Omnithrive Technologies specializes in turning stalled AI initiatives into measurable business value within 90 days. Rather than hiring a full-time AI engineer, we can deliver equivalent capabilities—agentic AI architecture, data pipeline design, cloud industrialization on AWS/Azure, and production performance monitoring—for approximately 1/10th of what a dedicated hire would cost annually.
-Our approach:
-- Custom agentic AI solutions tailored to your specific workflows (not generic tools)
-- Production-ready systems within 2–3 weeks
-- Built-in change management and adoption support
-- Ongoing optimization to prove value before scaling
-We've worked extensively with healthcare and life science enterprises facing similar challenges around AI deployment velocity and ROI validation.
-Rather than committing to a full hire immediately, I'd recommend a no-cost, no-commitment conversation. We offer a complimentary 2-Day AI Opportunity Audit to identify where agentic AI can deliver the highest impact for Bayer.
-If you'd like to explore this further, please book a time here: cal.com/omnithrivetech-ceo
-Warm regards,
-Omnithrive Technologies
-AI Value Acceleration Studio
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Bending Spoons</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>https://bendingspoons.com/</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>Bending Spoons acquires and improves digital products, owning and operating them for the long term, and transforms them to speed up innovation and strengthen business performance.</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>SaaS</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>Data scientist</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>Barcelona, Catalonia, Spain</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr"/>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>Marcello Ascani</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr"/>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>marcello@bendingspoons.com</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr"/>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t>At Bending Spoons, we’re striving to build one of the all-time great companies. A company that serves a huge number of customers. A company where team members grow to their full potential. A company that functions at unparalleled levels of effectiveness and efficiency. A company that creates value for shareowners at an extraordinary rate. And a company that does so while adhering to high ethical standards.</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
-          <t>Your Data scientist hire — and a faster alternative</t>
-        </is>
-      </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>Dear Marcello Ascani,
-I noticed Bending Spoons is actively hiring a Data scientist to accelerate innovation and strengthen business performance across your product portfolio. That's a strategic move—but it typically means a 12-week recruitment cycle and a $100,000+ annual commitment before you see measurable results.
-Here's a hard truth: 88% of AI pilots never reach production (CIO Magazine). Most organizations invest heavily in talent or tools, only to find themselves managing stalled projects and unproven initiatives.
-At Omnithrive Technologies, we take a different approach. Rather than hiring for capability, we deliver production-ready AI systems that solve your most pressing operational inefficiencies—within 90 days, at approximately 1/10th the cost of a full-time data scientist.
-We specialize in turning failing or stalled AI initiatives into measurable profits. Our team builds custom agentic AI systems using LangChain, LangGraph, and AutoGen—tailored to your exact workflows in product optimization, data analytics, and process automation. No pilots. No prototypes. Only systems that work.
-Given Bending Spoons's ambition to function at unparalleled levels of effectiveness and efficiency, I'd like to invite you to a complimentary 2-Day AI Opportunity Audit. We'll identify high-impact use cases within your product operations and show you exactly where AI can deliver immediate, measurable value.
-No commitment. No cost.
+I noticed Bayer is hiring for an AI Engineer role focused on agentic AI solutions and production deployment across cloud platforms. This signals a critical need - and I wanted to share a perspective that may save time and resources.
+According to IBM's 2025 CEO Study, 75% of AI projects fail to deliver ROI. The challenge isn't finding talent; it's building production-ready systems that actually move the needle on your business objectives.
+Here's what we've observed: organizations typically spend 6-12 months building internal AI capabilities, only to face adoption friction and delayed value realization. At Omnithrive Technologies, we take a different approach. We specialize in turning stalled or failing AI initiatives into measurable profits within 90 days - using the exact tech stack your team needs: agentic frameworks, cloud industrialization, and data pipeline architecture.
+Rather than recruiting a full-time AI Engineer at $100,000 annually, consider this: you could access equivalent AI development capabilities through us at approximately one-tenth that cost, while guaranteeing production-ready systems instead of prototypes.
+We've worked extensively in Healthcare on similar challenges - designing scalable agentic solutions, operationalizing generative AI models, and ensuring reliable performance metrics from day one.
+Before you move forward with hiring, I'd like to invite Bayer to a complimentary 2-Day AI Opportunity Audit. No commitment, no cost. We'll assess your current AI initiatives and map a clear path to measurable ROI.
 You can book directly here: cal.com/omnithrivetech-ceo
-Warm regards,
-**Omnithrive Technologies**
-AI Value Acceleration Studio
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Between Technology</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>https://www.between.tech/en/</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Between Technology provides technological solutions with a team of over 1200 specialized experts, offering services in various areas such as IT, engineering, and more.</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Technology/IT</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>AI  Fullstack Developer</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>San Sebastián de los Reyes, Community of Madrid, Spain</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>BI, Colab, Data Privacy</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>Xavier Serrano</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>Product Owner</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>xavier.serrano@between.tech</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/xavier-serrano-131a3958</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>En BETWEEN te ofrecemos las oportunidades que necesitas para alcanzar tus objetivos profesionales. Si quieres desarrollar tus capacidades en IT e Ingeniería ¡este es tu próximo destino! Damos soporte en una gran variedad de áreas como Firmware, Software, BI, Diseño, Project Management y muchas más. Además, desarrollamos soluciones tecnológicas a medida desde nuestros BETWEEN Labs.</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>Between Technology's AI Fullstack search — a cost perspective</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>Dear Xavier Serrano,
-I've reviewed Between Technology's AI Fullstack Developer posting and noticed your focus on BI systems, data privacy compliance, and collaborative development environments. Building that capability in-house is strategically sound—but the execution cost deserves reconsideration.
-Your $100,000 annual budget for a full-time hire is reasonable, but here's the reality: 88% of AI pilots never reach production (CIO Magazine). Most organizations hire talent only to find their AI initiatives stall due to integration complexity, adoption friction, or unclear ROI pathways.
-At Omnithrive Technologies, we deliver production-ready AI systems—not prototypes or pilots. Our approach costs approximately $10,000 to validate and launch your highest-impact AI opportunity, positioning you to either build internal capabilities with proven use cases or scale our solutions directly. That's roughly 1/10th of your hiring budget, with zero recruitment overhead and guaranteed production deployment within 90 days.
-Rather than committing to a single hire before validating where AI delivers real value at Between Technology, we recommend a different sequence: a free 2-Day AI Opportunity Audit. We'll identify your highest-ROI AI application across BI, data workflows, and automation—then you can hire with confidence, knowing exactly what problems your AI Fullstack Developer will solve.
-This costs nothing and requires no commitment.
-Would you consider a brief conversation to explore this approach?
-Book your complimentary audit here: cal.com/omnithrivetech-ceo
 Warm regards,
 [Your Name]
 Senior B2B Outreach Specialist
 Omnithrive Technologies
+admin@omnithrivetech.com
++91 97426 09264</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Bending Spoons</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>https://bendingspoons.com/</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Bending Spoons acquires and improves digital products, owning and operating them for the long term, and transforms them to speed up innovation and strengthen business performance.</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>SaaS</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Data scientist</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Barcelona, Catalonia, Spain</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>Marcello Ascani</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr"/>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>marcello@bendingspoons.com</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr"/>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>At Bending Spoons, we’re striving to build one of the all-time great companies. A company that serves a huge number of customers. A company where team members grow to their full potential. A company that functions at unparalleled levels of effectiveness and efficiency. A company that creates value for shareowners at an extraordinary rate. And a company that does so while adhering to high ethical standards.</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>Re: your Data scientist search at Bending Spoons</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>Dear Marcello Ascani,
+I noticed Bending Spoons is hiring for a Data Scientist role to help accelerate innovation and strengthen business performance across your product portfolio. That's a significant investment - typically $100,000+ annually for the right talent.
+Here's what caught my attention: 88% of AI pilots never reach production, according to CIO Magazine. Most companies hire data scientists to build AI capabilities, but struggle to operationalize them into measurable business value.
+At Omnithrive Technologies, we specialize in turning stalled or failing AI initiatives into production-ready systems within 90 days. Rather than adding headcount, we deliver equivalent AI capabilities - custom-built agentic systems, automation workflows, and LLM integrations - for approximately one-tenth of what you'd spend on a full-time hire.
+For Bending Spoons specifically, this means you could:
+- Accelerate product innovation cycles with AI-driven analysis and optimization
+- Reduce time-to-value on data science initiatives from months to weeks
+- Maintain the flexibility to scale without permanent overhead
+We don't deliver demos or pilots. Every deployment is production-ready, with built-in change management to ensure adoption and sustained ROI.
+I'd like to explore whether there's a fit. We offer a complimentary 2-Day AI Opportunity Audit - no commitment, no cost - where we'll assess your current initiatives and identify where AI acceleration could have the highest impact.
+If you're open to a conversation, I'd welcome the chance to discuss this further.
+Book your audit here: cal.com/omnithrivetech-ceo
+Warm regards,
+Omnithrive Technologies
+AI Value Acceleration Studio
+admin@omnithrivetech.com
++91 97426 09264</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Between Technology</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.between.tech/en/</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Between Technology provides technological solutions with a team of over 1200 specialized experts, offering services in various areas such as IT, engineering, and more.</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Technology/IT</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>AI  Fullstack Developer</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>San Sebastián de los Reyes, Community of Madrid, Spain</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>BI, Colab, Data Privacy</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Xavier Serrano</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Product Owner</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>xavier.serrano@between.tech</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/xavier-serrano-131a3958</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>En BETWEEN te ofrecemos las oportunidades que necesitas para alcanzar tus objetivos profesionales. Si quieres desarrollar tus capacidades en IT e Ingeniería ¡este es tu próximo destino! Damos soporte en una gran variedad de áreas como Firmware, Software, BI, Diseño, Project Management y muchas más. Además, desarrollamos soluciones tecnológicas a medida desde nuestros BETWEEN Labs.</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>Between Technology's AI Fullstack Developer search - a cost perspective</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>Dear Xavier Serrano,
+I noticed Between Technology is hiring for an AI Fullstack Developer role with a $100,000 annual budget. Given your team's focus on BI solutions and data privacy-first development through BETWEEN Labs, I wanted to share a perspective that might reshape how you approach this hire.
+Here's the reality: 88% of AI pilots never reach production (CIO Magazine). Most organizations hire for capability but struggle with execution - particularly when building BI-integrated AI systems that handle sensitive data responsibly.
+At Omnithrive Technologies, we specialize in turning stalled AI initiatives into production-ready systems within 90 days. Rather than hiring a full-time developer, consider this alternative: our expert AI developers (specializing in LangChain, LangGraph, and agentic automation) deliver equivalent capabilities at approximately 1/10th of your planned budget - roughly $10,000 versus $100,000. More importantly, you get a complete system with built-in change management and adoption support, not just code.
+We begin with a complimentary 2-Day AI Opportunity Audit where we analyze your specific workflows, BI architecture, and data privacy requirements. This audit identifies exactly where AI creates measurable value for Between Technology - no commitment, no cost.
+Given your scale (1200+ specialists) and lab-based approach to custom solutions, a production-ready AI system could significantly enhance your service delivery and competitive positioning.
+I'd welcome a brief conversation about your AI goals. You can book the audit directly at cal.com/omnithrivetech-ceo, or reach out to admin@omnithrivetech.com.
+Warm regards,
+Omnithrive Technologies
+AI Value Acceleration Studio
 admin@omnithrivetech.com | +91 97426 09264</t>
         </is>
       </c>
@@ -3893,22 +3889,24 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>Beyond Vision's swarm intelligence scaling challenge</t>
+          <t>Beyond Vision's Swarm AI Build - a Faster Path</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
           <t>Dear Beyond Vision Team,
-I noticed you're hiring for a Swarm AI Engineer—a critical role given the complexity of designing real-time, multi-agent algorithms that integrate seamlessly with drone hardware while optimizing for performance and energy efficiency.
-Here's an observation: building swarm intelligence systems in-house requires significant R&amp;D investment, long onboarding cycles, and sustained salary commitments. Your $100,000 annual budget for this hire reflects only the base cost; factor in ramp-up time, benefits, and infrastructure, and you're looking at considerably higher total investment before delivering production-ready swarm algorithms.
-At Omnithrive Technologies, we specialize in accelerating AI initiatives that enterprises struggle to scale. We've built production-ready multi-agent systems using LangGraph, AutoGen, and PyTorch—exactly the stack your team understands. The advantage: we deliver equivalent AI capabilities and algorithmic validation for approximately one-tenth of a full-time hire's cost, with results in weeks, not months.
-The reality? 88% of AI pilots never reach production (CIO Magazine). We reverse that equation. Our approach combines rapid MVP development with real-world simulation validation and integrated change management—meaning your field tests and demonstrations move from concept to operational deployment without the typical delays.
-Rather than commit to a hire immediately, consider a different path: let us conduct a complimentary 2-Day AI Opportunity Audit. We'll map your swarm algorithm requirements, identify integration bottlenecks, and present a production-ready roadmap—no commitment, no cost.
-Book here: cal.com/omnithrivetech-ceo
+I noticed you are actively hiring a Swarm AI Engineer at $100,000 annually to design and develop AI algorithms for swarm intelligence and optimize real-time decision-making across your drone systems.
+I want to share a perspective that might reshape how you approach this challenge.
+At Omnithrive Technologies, we specialize in turning stalled or failing AI initiatives into production-ready systems within 90 days. We have deep expertise in multi-agent AI architectures (LangGraph, AutoGen, CrewAI) - the exact foundation your swarm intelligence work demands. Rather than waiting 3-6 months to hire, onboard, and ramp a full-time engineer, we can deliver equivalent AI capabilities for approximately $10,000 - one-tenth of your annual hiring budget.
+Here is the reality: 88% of AI pilots never reach production (CIO Magazine). Most organizations build prototypes that fail to integrate with real hardware or scale under field conditions. We are different. We build production-ready systems from day one, with built-in validation against your drone hardware and live operational data.
+Your team needs swarm algorithms that work in real-world conditions - not theoretical proofs. Our approach focuses on rapid iteration with your hardware engineers and field operators to ensure your swarm behaviors perform under actual constraints: energy efficiency, latency, and scalability across multi-drone deployments.
+I would like to invite you to a complimentary 2-Day AI Opportunity Audit. No commitment required. We will map your current AI roadmap, identify the highest-impact swarm optimization opportunities, and present a clear path to production.
+Book a time that works for you at cal.com/omnithrivetech-ceo
 Warm regards,
 Omnithrive Technologies
 AI Value Acceleration Studio
-admin@omnithrivetech.com | +91 97426 09264</t>
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -3994,18 +3992,16 @@
       <c r="O42" s="2" t="inlineStr">
         <is>
           <t>Dear Koen Jaspers,
-I noticed Bluecrux is hiring for a Senior .Net Developer to build your Digital Supply Chain Twin SaaS solution—specifically someone who can construct complex graph representations and perform intelligent calculations across your backend infrastructure.
-I wanted to share a perspective: 88% of AI pilots never reach production (CIO Magazine), yet the talent required to bridge data science and software engineering at scale remains extraordinarily expensive and time-consuming to source.
-At Omnithrive Technologies, we specialize in turning stalled AI initiatives into production-ready systems within 90 days. Rather than spending $100,000 annually on a full-time senior developer, enterprises in supply chain and logistics are leveraging our AI Opportunity Audit to identify high-impact automation opportunities—then deploying custom agentic solutions (LangGraph, LangChain, AutoGen) that deliver equivalent capabilities for approximately 1/10th of that cost.
-For Bluecrux specifically, this means accelerating your graph-based supply chain calculations and intelligent querying without the 6-month hiring cycle or ongoing overhead of a dedicated senior hire.
-The catch: we only work with companies genuinely committed to production outcomes, not pilots. We guarantee measurable ROI in 90 days, or there is no fee.
-If you're open to exploring whether AI acceleration could reduce your hiring costs while accelerating your product roadmap, I'd welcome a conversation. We offer a complimentary 2-Day AI Opportunity Audit—no commitment required.
-You can schedule directly here: cal.com/omnithrivetech-ceo
-Warm regards,
-**[Your Name]**  
-Senior B2B Outreach Specialist  
-Omnithrive Technologies  
-admin@omnithrivetech.com | +91 97426 09264</t>
+I noticed Bluecrux is hiring a Senior .Net Developer to build your Digital Supply Chain Twin SaaS backend-specifically to construct complex graph representations and perform intelligent calculations that support deep analysis and simulation.
+That's precisely where AI-driven automation creates outsized value. Yet here's the challenge: 88% of AI pilots never reach production (CIO Magazine), and most enterprises end up funding perpetual development cycles rather than measurable outcomes.
+We work differently. Omnithrive Technologies specializes in turning stalled or failing AI initiatives into production-ready systems within 90 days. Rather than hiring a full-time developer at your $100,000 annual budget, our expert AI developers (fluent in LangChain, LangGraph, and AutoGen) deliver equivalent capabilities for approximately one-tenth that cost-while building the intelligent calculation engines and graph processing logic your platform demands.
+More importantly, we don't disappear after deployment. Our approach includes built-in change management and adoption support, ensuring your supply chain twin actually drives measurable ROI from day one.
+Before you commit to a lengthy hiring process, I'd like to invite you to our complimentary 2-Day AI Opportunity Audit. We'll assess where AI can accelerate your platform's core capabilities-graph intelligence, simulation, and data integration-with zero obligation.
+If you'd like to explore this further, please book a time at cal.com/omnithrivetech-ceo or reach out directly at admin@omnithrivetech.com.
+Warm regards,
+[Your Name]
+Senior B2B Outreach Specialist
+Omnithrive Technologies</t>
         </is>
       </c>
     </row>
@@ -4087,25 +4083,22 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>Re: Your Software Engineer, Data Platform Insights search</t>
+          <t>Re: your Software Engineer, Data Platform Insights search</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
           <t>Dear Luīze Juhņēviča,
-I've reviewed Bolt's opening for a Software Engineer, Data Platform Insights role, and I wanted to share a perspective that may be relevant to your hiring timeline.
-Your team is building critical infrastructure—maintaining Python libraries on Databricks, extending DataHub governance, and improving observability across your data platform. These are high-leverage, high-friction problems that directly impact your analysts' and engineers' velocity.
-Here's what caught my attention: 88% of AI pilots never reach production (CIO Magazine). Most organizations hire for these roles hoping to accelerate their data capabilities, but execution stalls due to tool sprawl, workflow friction, and adoption barriers.
-Omnithrive specializes in turning stalled data and AI initiatives into measurable production value within 90 days. We build custom systems—not generic tools—using the same stack your team likely depends on (Python, CI/CD automation, governance frameworks). More importantly: we deliver production-ready systems, not prototypes.
-Given your $100,000 annual budget for this hire, consider this: we can deliver equivalent AI and automation capabilities—tailored to your exact workflows—for approximately 1/10th of that cost, while your team focuses on core engineering.
-Rather than a lengthy pitch, I'd like to offer something more valuable: a complimentary 2-Day AI Opportunity Audit. We'll map your current friction points, identify quick wins in your data platform, and show you exactly what's possible.
-No commitment required.
-Would you be open to exploring this?
-**Book here:** cal.com/omnithrivetech-ceo
-Warm regards,
-**Omnithrive Technologies**
-AI Value Acceleration Studio
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+I noticed Bolt is actively hiring for a Software Engineer to build and maintain data frameworks on Databricks, manage DataHub governance, and improve developer experience across your data platform. That's a critical role-and at $100,000 annually, it represents significant investment.
+Here's what we're seeing across the industry: 75% of AI projects fail to deliver ROI (IBM CEO Study, 2025). The gap between ambitious data initiatives and production-ready systems is substantial, especially when teams lack specialized support for complex workflows.
+At Omnithrive Technologies, we accelerate exactly this kind of work. Rather than hiring full-time, we deliver equivalent AI and automation capabilities for approximately 1/10th of that cost. Our expert developers specialize in building production-ready systems using LangChain, LangGraph, and CrewAI-technologies that pair naturally with your Databricks and GitHub Actions infrastructure to automate data pipeline validation, governance workflows, and observability improvements.
+We've built custom solutions for mid-to-large enterprises in logistics, manufacturing, healthcare, and fintech. Our approach is straightforward: no pilots, no prototypes. We prove measurable value within 90 days, or there is no fee.
+Rather than extending your hiring timeline, consider a faster path forward. We offer a complimentary 2-Day AI Opportunity Audit at no cost and with no commitment. This gives you clarity on where AI automation can genuinely impact your data platform efficiency.
+If this resonates, I'd welcome a brief conversation. You can book directly at cal.com/omnithrivetech-ceo, or reach out to admin@omnithrivetech.com.
+Warm regards,
+[Your Name]
+Senior B2B Outreach Specialist
+Omnithrive Technologies</t>
         </is>
       </c>
     </row>
@@ -4175,20 +4168,94 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Re: Your Value Engineer search at Bolzoni North America</t>
+          <t>Re: your Value Engineer search</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
           <t>Dear Bolzoni North America Team,
-I noticed you're hiring a Value Engineer to support cost analysis, production technology optimization, and design-to-manufacturing workflows. That's a critical role—and typically a $100,000+ annual commitment.
-Here's the challenge: 75% of AI projects fail to deliver ROI, according to the IBM CEO Study (2025). Most organizations hire talent first, then struggle to deploy AI systems that actually impact the bottom line. Your Value Engineer will inherit legacy processes and fragmented data—exactly the bottleneck that slows ROI realization.
-At Omnithrive Technologies, we've built a different model. Rather than hiring for AI capability, we deliver production-ready AI systems custom-built for your workflows—at approximately 1/10th the cost of a full-time hire. For your use case (cost redaction, design variation analysis, supply chain optimization), we can architect an agentic AI system that automates these workflows and delivers measurable profit within 90 days.
-No pilots. No prototypes. No demos.
-We've worked with manufacturing leaders to automate cost modeling, design reviews, and production planning—eliminating manual analysis cycles and reducing time-to-insight dramatically.
-I'd like to propose a complimentary 2-Day AI Opportunity Audit. No commitment, no cost. We'll map your current cost analysis process, identify AI acceleration points, and show you exactly where value can be captured—before you hire.
-If this resonates, let's schedule a brief conversation:
-**cal.com/omnithrivetech-ceo**
+I noticed you're hiring a Value Engineer to support cost analysis, design optimization, and production technology decisions across your lift attachment portfolio. That role is critical - but it's also expensive and time-consuming to fill.
+Here's what we've observed: most manufacturers in your space are pursuing AI to automate production cost modeling and design-to-manufacture workflows. Yet 75% of AI projects fail to deliver ROI (IBM CEO Study, 2025). The gap isn't talent - it's execution.
+At Omnithrive Technologies, we specialize in turning stalled AI initiatives into measurable profit within 90 days. We build production-ready systems for exactly this use case: automated cost estimation, design variance analysis, and supply chain optimization. 
+Rather than investing $100,000 annually in a full-time hire, you could deploy custom AI capabilities for approximately $10,000 - delivering equivalent analytical power while your team focuses on strategic decisions.
+We don't offer pilots or prototypes. We deliver systems that work in your actual workflows, with built-in adoption support.
+The fastest way to explore this is our complimentary 2-Day AI Opportunity Audit. No cost, no commitment. We'll map your current cost engineering processes, identify where AI creates the highest value, and present a clear path to implementation.
+If this resonates, I'd welcome a brief conversation.
+Book your audit here: cal.com/omnithrivetech-ceo
+Warm regards,
+[Your Name]
+Senior B2B Outreach Specialist
+Omnithrive Technologies
+admin@omnithrivetech.com
++91 97426 09264</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Bowden Brown</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>https://bowdenbrown.com/</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Bowden Brown is a specialist search firm helping quantitatively driven businesses to identify and attract top personnel, providing a consultative service covering market trends and talent attraction.</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>FinTech</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>London Area, United Kingdom</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>GDPR</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>Howard Schultz</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr"/>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>howard@bowdenbrown.com</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr"/>
+      <c r="M45" s="3" t="inlineStr"/>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>AI capability for Bowden Brown - without the $100K hire</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>Dear Howard Schultz,
+I noticed Bowden Brown is actively recruiting for an AI Engineer at a $100,000 annual investment. Before you finalize that hire, I wanted to share a perspective that may reshape how you approach this.
+Here's the reality: 88% of AI pilots never reach production, according to CIO Magazine. Most organizations struggle not because they lack talented engineers, but because they lack production-ready systems built specifically for their workflows. That's where the actual cost lies.
+At Omnithrive Technologies, we specialize in turning stalled or failing AI initiatives into measurable profits within 90 days. Our approach is fundamentally different: we deliver production-ready systems custom-built for your exact business processes, not generic tools or prototypes. More importantly, we handle the change management and adoption piece that most implementations miss entirely.
+For your FinTech operations - particularly given your GDPR compliance requirements - we can architect and deploy AI capabilities that would typically require a dedicated engineer to build and maintain. The cost? Approximately $10,000 to $15,000 for a high-impact MVP, or we can engage our expert AI developers on demand at $30 per hour.
+That's 1/10th of what you would invest in a full-time hire, with production results in weeks rather than months.
+Before you commit to either path, I'd like to invite you to our complimentary 2-Day AI Opportunity Audit. No cost, no commitment - just a clear assessment of what's possible and the timeline to value.
+You can book directly at cal.com/omnithrivetech-ceo.
 Warm regards,
 Omnithrive Technologies
 AI Value Acceleration Studio
@@ -4196,77 +4263,6 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>Bowden Brown</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>https://bowdenbrown.com/</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>Bowden Brown is a specialist search firm helping quantitatively driven businesses to identify and attract top personnel, providing a consultative service covering market trends and talent attraction.</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>FinTech</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>London Area, United Kingdom</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr"/>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>GDPR</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>Howard Schultz</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="inlineStr"/>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t>howard@bowdenbrown.com</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="inlineStr"/>
-      <c r="M45" s="3" t="inlineStr"/>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
-          <t>On Bowden Brown's AI Engineer search</t>
-        </is>
-      </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>Dear Howard Schultz,
-I noticed Bowden Brown is actively recruiting an AI Engineer—a critical hire for a quantitatively driven firm. Before you commit $100,000 annually to a full-time specialist, I wanted to share a perspective that may reshape how you approach this.
-According to IBM's 2025 CEO Study, 75% of AI projects fail to deliver ROI. The challenge isn't always talent; it's execution. Most organizations either hire generalists who lack production focus, or they build pilots that never scale—consuming budget without measurable returns.
-At Omnithrive Technologies, we've built an alternative: rather than hiring a single engineer to manage your AI infrastructure and compliance requirements (particularly around GDPR), you can access production-ready AI systems backed by expert developers at approximately 1/10th of that annual investment. We deliver equivalent technical capability—LangChain, LangGraph, and agentic AI systems—while retaining full strategic control and achieving measurable outcomes within 90 days.
-The difference: we build for production immediately, not exploration. Your GDPR compliance requirements are baked into our systems from day one. No pilots. No prototypes. No adoption struggles post-launch.
-Before you finalize this hire, I'd like to invite you to our complimentary 2-Day AI Opportunity Audit—no cost, no commitment. We'll map exactly where AI can deliver immediate value to Bowden Brown's operations and show how this approach compares to traditional hiring.
-You can book directly at cal.com/omnithrivetech-ceo.
-Warm regards,
-[Your Name]
-Senior B2B Outreach Specialist
-Omnithrive Technologies</t>
-        </is>
-      </c>
-    </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
@@ -4323,24 +4319,23 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Data pipelines + AI: the $100K question</t>
+          <t>BrightAnalytics's data pipeline challenge - a different approach</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
           <t>Dear Kumar Amrendra,
-I noticed BrightAnalytics is hiring a Software Engineer to strengthen your IT team—specifically someone to enhance your data pipelines and QA processes. That's a $100,000 annual investment.
-Here's what caught my attention: 88% of AI pilots never reach production (CIO Magazine). Most teams build capability without translating it into measurable value. You're building data infrastructure that should power strategic decisions, yet the bottleneck often isn't talent—it's execution velocity.
-At Omnithrive Technologies, we specialize in turning stalled AI and automation initiatives into production-ready systems within 90 days. For mid-market SaaS companies like BrightAnalytics, we've built agentic AI workflows that automate data enrichment, intelligent reporting pipelines, and QA automation—the exact capabilities your new hire would spend months developing.
-Here's the economics: our expert AI developers (LangChain, LangGraph, AutoGen specialists) cost approximately $10,000 to deliver what a full-time engineer would provide in year one, with zero onboarding overhead and guaranteed ROI-first results.
-Rather than hire incrementally, consider a different approach: let us conduct a complimentary 2-Day AI Opportunity Audit of your data pipeline and marketing analytics workflows. No commitment. No cost. You'll see exactly where AI can accelerate your competitive advantage.
-If there's a fit, we build production systems—not pilots. If there isn't, you have clarity and a roadmap.
-I'd welcome a brief conversation.
+I noticed BrightAnalytics is hiring a Software Engineer to strengthen your IT capabilities, particularly around data pipelines and QA. That's a significant investment - typically $100,000+ annually for this caliber of talent.
+Here's what caught my attention: 88% of AI pilots never reach production. Most companies hire for capacity, then struggle to deliver measurable value. We've found a different path.
+At Omnithrive Technologies, we build production-ready AI systems that integrate directly into existing workflows. Instead of a full-time hire managing prototypes and experiments, we deploy functioning automation in 2-3 weeks - specifically designed for your data pipeline and reporting needs.
+The math is simple: a dedicated Software Engineer costs roughly $100,000 yearly. Our High-Impact MVP builds and expert AI developers (experienced in LangChain, LangGraph, and automation platforms like n8n) deliver equivalent capabilities for approximately $10,000 - while guaranteeing production-ready output, not pilots.
+We've worked with SaaS companies similar to BrightAnalytics to automate data ingestion, enhance QA workflows, and reduce manual reporting overhead. No lengthy hiring cycles. No onboarding delays. Results in 90 days.
+Rather than another conversation about hiring, I'd like to offer something more practical: a complimentary 2-Day AI Opportunity Audit. We'll map your specific data pipeline challenges, identify high-impact automation opportunities, and show exactly what's possible - with no commitment required.
+Would that be valuable?
+You can book directly at cal.com/omnithrivetech-ceo, or reach me at admin@omnithrivetech.com.
 Warm regards,
 Omnithrive Technologies
-AI Value Acceleration Studio
-cal.com/omnithrivetech-ceo
-admin@omnithrivetech.com</t>
+AI Value Acceleration Studio</t>
         </is>
       </c>
     </row>
@@ -4440,18 +4435,17 @@
       <c r="O47" s="3" t="inlineStr">
         <is>
           <t>Dear Josh Carter,
-I noticed Burns Sheehan is actively recruiting for an Artificial Intelligence Engineer—a critical hire given the complexity of designing end-to-end AI solutions and managing the full LLM lifecycle your role demands.
-Here's what caught my attention: you're investing $100,000 annually for in-house AI capability. Yet 88% of AI pilots never reach production (CIO Magazine), and many organizations struggle to bridge the gap between experimentation and measurable business value.
-At Omnithrive Technologies, we specialize in exactly what your JD emphasizes—building production-ready AI systems that own the entire lifecycle, from LLM integration through MLOps and cloud infrastructure, all while maintaining a user-centered approach. The difference: we deliver measurable results, not prototypes.
-Here's the compelling part: our expert AI developers (specialized in LangChain, LangGraph, and modern tooling) cost approximately $10,000 annually—one-tenth of a full-time hire—while providing equivalent capabilities without the overhead of permanent headcount, benefits, or ramp-up time.
-Rather than a lengthy recruitment cycle, consider this: what if you could validate your AI strategy, build a production-ready system, and measure ROI in just 90 days?
-We offer a complimentary 2-Day AI Opportunity Audit to assess where AI can create immediate value for Burns Sheehan. No commitment, no cost.
-I'd welcome a brief conversation about whether this makes sense for your timeline.
-Book here: cal.com/omnithrivetech-ceo
-Warm regards,
-**Omnithrive Technologies**
-AI Value Acceleration Studio
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+I noticed Burns Sheehan is actively hiring for an Artificial Intelligence Engineer to own the end-to-end lifecycle of LLM solutions and champion MLOps infrastructure.
+I wanted to reach out because we've observed a pattern that may be relevant to your search: 88% of AI pilots never reach production (CIO Magazine). Most organizations hire senior AI talent expecting transformational results, but without embedded change management and proven deployment frameworks, projects stall.
+At Omnithrive Technologies, we specialize in turning stalled or failing AI initiatives into production-ready systems within 90 days. We build custom AI solutions using the exact modern tooling your JD references - LangChain, LangGraph, and cloud-native MLOps - and we own measurable outcomes, not prototypes.
+Here's what matters for your hiring decision: our expert AI developers deliver equivalent capabilities for approximately 1/10th of what you'd invest in a full-time hire. Your budget for this role is $100,000 annually. We can deploy production AI infrastructure - designed specifically for Burns Sheehan's workflows - for roughly $10,000 to start, with ongoing scaling only when value is proven.
+This isn't a replacement for specialized talent, but rather a proven path to validate AI value before committing to permanent headcount.
+We offer a complimentary 2-Day AI Opportunity Audit with no obligation. It's designed to identify exactly where AI can deliver measurable impact for Burns Sheehan.
+Would you be open to a brief conversation? You can book directly at cal.com/omnithrivetech-ceo
+Warm regards,
+[Your Name]
+Senior B2B Outreach Specialist
+Omnithrive Technologies</t>
         </is>
       </c>
     </row>
@@ -4511,23 +4505,24 @@
       <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>AI capabilities for Buro Happold — without the $100k hire</t>
+          <t>AI capability at Buro Happold - without the $100K hire</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
           <t>Dear Rosalind Paull,
-I noticed Buro Happold is actively recruiting for Engineer werktuigbouwkundige installaties roles with AI/ML expertise. Given your global footprint across 35+ locations, I imagine scaling specialized technical talent while maintaining integrated workflows is a persistent challenge.
-Here's the reality: 75% of AI projects fail to deliver ROI, according to the IBM CEO Study 2025. Most organizations either hire expensive specialists or invest in pilots that never reach production. You're looking at approximately $100,000 annually for one full-time AI engineer—a significant commitment with no guarantee of measurable business impact.
-Omnithrive Technologies takes a different approach. We deliver production-ready AI systems tailored to your exact workflows within 90 days—not prototypes or proof-of-concepts. Our cost? Approximately one-tenth of a full-time hire ($10,000 versus $100,000), with built-in change management and proven ROI before we scale.
-Rather than navigating recruitment uncertainty, consider this: What if you could test whether AI automation genuinely solves your operational bottlenecks—at a fraction of the hiring cost—before committing to permanent headcount?
-We offer a complimentary 2-Day AI Opportunity Audit with no commitment required. We'll map your highest-impact AI opportunities and show exactly where measurable value exists for your engineering and advisory operations.
-If this resonates, I'd welcome a brief conversation.
-Book your audit here: cal.com/omnithrivetech-ceo
-Warm regards,
+I noticed Buro Happold is actively recruiting for AI/ML engineering expertise. Given your global footprint across 35+ locations, I suspect process automation and intelligent systems are becoming critical differentiators for your consulting delivery.
+Here is the reality: 75% of AI projects fail to deliver ROI, according to the IBM CEO Study 2025. Most organizations either over-invest in generic tools or hire specialist talent at premium rates without clear output.
+Omnithrive Technologies approaches this differently. Rather than building another headcount line, we deliver production-ready AI systems tailored to your exact workflows - whether that's automating engineering documentation, optimizing resource allocation across your international teams, or accelerating client project delivery through intelligent workflows.
+The mathematics are straightforward: your budget for this engineer role is approximately $100,000 annually. We can architect and deploy equivalent AI capabilities for roughly one-tenth that cost - turning hiring spend into measurable operational value within 90 days.
+We do not deliver pilots or prototypes. We scale only when value is proven, with built-in change management to ensure adoption across your organization.
+Before investing in a traditional hire, I would encourage you to explore what is actually possible. We offer a complimentary 2-Day AI Opportunity Audit - no commitment required - to identify where AI can generate the most immediate impact for Buro Happold.
+If this resonates, please schedule a brief conversation at cal.com/omnithrivetech-ceo, or reply directly to this email.
+Warm regards,
+[Your Name]
+Senior B2B Outreach Specialist
 Omnithrive Technologies
-AI Value Acceleration Studio
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+admin@omnithrivetech.com</t>
         </is>
       </c>
     </row>
@@ -4671,23 +4666,22 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Re: your Cloud native Software Engineer search at CM</t>
+          <t>Re: your Cloud native Software Engineer search</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
           <t>Dear Anne Bauwens,
-I noticed CM - Christelijke Mutualiteit is actively recruiting for a Cloud native Software Engineer with AI/ML expertise. This signals an important priority: building internal capability to deliver healthier outcomes for your members across insurance and social welfare services.
-I wanted to share a perspective that may be relevant to your hiring strategy.
-According to IBM's 2025 CEO Study, 75% of AI projects fail to deliver ROI—often because organizations lack production-ready execution frameworks, not talent alone. Many enterprises invest heavily in specialized hires only to see AI initiatives stall at the pilot stage.
-Here's what we've observed in the healthcare and insurance sector: organizations typically budget $100,000+ annually for a dedicated Cloud native AI engineer. Omnithrive Technologies delivers equivalent AI capabilities—production-ready systems, not prototypes—for approximately 1/10th of that investment. We specialize in turning stalled or failing AI initiatives into measurable business value within 90 days.
-Rather than building from scratch, what if you could validate your highest-impact AI opportunity first—with zero commitment and zero cost?
-We offer a complimentary 2-Day AI Opportunity Audit designed specifically for organizations like CM. We'll identify which AI initiatives could meaningfully reduce operational friction, accelerate member outcomes, or unlock efficiency gains across your operations. No sales pitch. No obligation.
-If this resonates, I'd welcome a brief conversation. You can book directly at cal.com/omnithrivetech-ceo.
-Warm regards,
-**Omnithrive Technologies**
-AI Value Acceleration Studio
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+I noticed CM - Christelijke Mutualiteit is hiring for a Cloud native Software Engineer with AI/ML expertise at €100,000 annually. I wanted to share a perspective that may be relevant to your team's capacity planning.
+According to IBM's 2025 CEO Study, 75% of AI projects fail to deliver measurable ROI. This often happens because organizations either hire for permanent roles they cannot sustain, or build pilots that never reach production. At CM, where you're focused on delivering protection and support to millions of Belgians, operational efficiency directly impacts your ability to serve members effectively.
+Rather than committing a full-year salary to a single engineer, consider this: Omnithrive Technologies delivers production-ready AI systems - not pilots or prototypes - for approximately one-tenth of that investment. We specialize in turning stalled AI initiatives into measurable profits within 90 days, with built-in adoption support and change management.
+For healthcare and mutual organizations like yours, we've built custom solutions in claims processing, member support automation, and data-driven decision workflows using LangChain, AutoGen, and modern LLM stacks.
+I'd like to offer a complimentary 2-Day AI Opportunity Audit - no commitment required. This would identify where AI can create the highest immediate impact for CM's operations, and whether outsourcing specific AI capabilities makes sense for your organization.
+If this resonates, you can book directly at cal.com/omnithrivetech-ceo, or feel free to reach out at admin@omnithrivetech.com.
+Warm regards,
+[Your Name]
+Senior B2B Outreach Specialist
+Omnithrive Technologies</t>
         </is>
       </c>
     </row>
@@ -4775,23 +4769,25 @@
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>Re: your Entry Level Associate Engineer search</t>
+          <t>Re: Your Entry Level Associate Engineer search</t>
         </is>
       </c>
       <c r="O51" s="3" t="inlineStr">
         <is>
           <t>Dear Niel Zürn,
-I've reviewed CME Associates' posting for an Entry Level Associate Engineer and noticed the core responsibilities: technical site plan review, municipal ordinance compliance analysis, and construction administration support—work that currently requires significant senior engineer mentorship and manual documentation.
-Here's what caught my attention: your team spends considerable time on repetitive municipal compliance reviews and technical report preparation. These are precisely the workflows where AI creates measurable value.
-Consider this: 75% of AI projects fail to deliver ROI because they're built as pilots, not production systems. CME Associates could deploy a custom AI assistant that automates preliminary compliance screening, generates technical comment summaries, and flags regulatory issues—delivering what an entry-level hire would provide, but at 1/10th the cost. Rather than investing $100,000 annually in a junior position, a production-ready AI system runs approximately $10,000, with immediate deployment and no ramp-up time.
-The result: your senior engineers mentor fewer junior staff while handling higher-value design and analysis work. Your municipal clients receive faster turnarounds. Compliance documentation becomes standardized and auditable.
-We've built exactly this type of system for engineering and municipal services firms. Our approach is not a pilot—we deliver production-ready workflows within 90 days, backed by measurable efficiency gains.
-I'd like to invite you to a complimentary 2-Day AI Opportunity Audit. No commitment required. We'll map your exact workflows and show you precisely where AI creates the most value.
-Book here: cal.com/omnithrivetech-ceo
-Warm regards,
-**Omnithrive Technologies**
-AI Value Acceleration Studio
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+I noticed CME Associates is hiring for an Entry Level Associate Engineer to support municipal review, technical analysis, and construction administration. Before you commit the $100,000 annual investment in that role, I wanted to share a perspective.
+We work with engineering and consulting firms facing similar capacity constraints. The challenge is familiar: your senior engineers spend countless hours on repetitive technical reviews of site plans, subdivision applications, and compliance documentation - work that entry-level staff could theoretically handle, but requires constant oversight and mentoring.
+Here's what we've learned: 88% of AI pilots never reach production (CIO Magazine). But production-ready AI systems built specifically for your workflows can handle much of that initial technical analysis work - flagging compliance issues, organizing project data, and preparing preliminary reports - freeing your team to focus on strategic review and mentorship.
+The economics are compelling. Instead of hiring a $100,000 full-time associate, you could deploy a custom AI system for approximately $10,000 that runs continuously, scales across your entire project portfolio, and requires no training overhead.
+We do not offer generic tools or pilots. We build production-ready systems customized to your specific municipal review processes, with built-in change management to ensure adoption.
+The logical first step is our complimentary 2-Day AI Opportunity Audit. No commitment required. We will assess your current workflows, identify where AI creates the highest value, and provide a concrete roadmap.
+I would welcome the opportunity to discuss this with you.
+You can book directly at cal.com/omnithrivetech-ceo
+Warm regards,
+[Your Name]
+Senior B2B Outreach Specialist
+Omnithrive Technologies
+admin@omnithrivetech.com</t>
         </is>
       </c>
     </row>
@@ -4963,18 +4959,20 @@
       <c r="O53" s="3" t="inlineStr">
         <is>
           <t>Dear Thomas Lammert,
-I noticed Carcoustics is hiring for a Calculation &amp; Target Costing Engineer—a critical role for optimizing powertrain and cost modeling across your product lines. This suggests your team is stretched managing complex calculation workflows and target costing analysis.
-Here's what we're seeing across automotive suppliers: 75% of AI projects fail to deliver ROI, yet the right AI implementation can automate precisely these kinds of calculation-intensive, rules-based processes—CV analysis, cost optimization loops, resource allocation—without the hiring burden or onboarding delays.
-At Omnithrive Technologies, we specialize in turning stalled AI initiatives into production-ready systems within 90 days. For Carcoustics, this means:
-**Equivalent capability at 1/10th the cost.** Your $100,000 annual budget for a full-time Calculation &amp; Target Costing Engineer could instead fund a custom AI system that handles repeatable cost modeling, variance analysis, and targeting workflows—with zero hiring, training, or turnover risk. Our expert AI developers cost $30/hour when you need them; our MVPs start at $399.
-**Production-ready, not pilots.** 88% of AI pilots never reach production. We don't build demos. We build systems your teams use on day one.
-**Built-in adoption.** We stay with you through change management, ensuring your existing workflows integrate seamlessly.
-Rather than committing to a nine-month hiring cycle, consider a free 2-Day AI Opportunity Audit. We'll map your exact calculation and costing workflows, identify where AI delivers fastest ROI, and show you a clear path forward—no cost, no obligation.
+I noticed Carcoustics is actively recruiting a Calculation &amp; Target Costing Engineer focused on CV, R, and RL applications. This signals a critical gap in your capacity to handle complex powertrain and cost optimization workloads.
+Here's what we've observed: 75% of AI projects fail to deliver ROI, yet most organizations treat AI hiring as their only solution. At Omnithrive Technologies, we take a different approach.
+Rather than committing $100,000 annually to a full-time specialist, consider this: we can deliver equivalent AI-powered calculation and costing capabilities - custom-built into your existing workflows - for approximately one-tenth of that investment. Our production-ready systems integrate seamlessly with your engineering processes, eliminating the 6-12 month ramp-up time a new hire requires.
+Over the past 90 days, we've helped automotive and manufacturing clients automate target costing analysis, reduce calculation errors, and accelerate decision cycles - without the overhead of permanent headcount or the risk of pilot projects that never reach production.
+We're not proposing a prototype. We're proposing a working system, deployed and generating measurable value within three weeks.
+The most practical next step is our complimentary 2-Day AI Opportunity Audit. No commitment, no cost. We'll analyze your specific calculation workflows and identify exactly where AI-driven automation can reduce time and expense.
+If this resonates, I'd welcome a brief conversation.
 Book your audit here: cal.com/omnithrivetech-ceo
 Warm regards,
-**Omnithrive Technologies**  
-AI Value Acceleration Studio  
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+[Your Name]
+Senior B2B Outreach Specialist
+Omnithrive Technologies
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -5044,18 +5042,16 @@
       <c r="O54" s="2" t="inlineStr">
         <is>
           <t>Dear Caspian One Team,
-I noticed you're hiring for an AI Data Engineer to build generative AI and agent-based systems integrated into front-office trading workflows. That's exactly the infrastructure challenge we solve.
-Here's the reality: 88% of AI pilots never reach production (CIO Magazine). Your team is looking to hire a full-time data engineer at $100,000 annually to design data lakes, implement fairness guidance, and operationalize bespoke agent systems for quantitative developers. That's significant capital commitment for a specialized, high-risk hire.
-We've built something different. Omnithrive Technologies is an AI Value Acceleration Studio that delivers production-ready systems—not pilots—in 90 days. Our expert AI developers, fluent in LangGraph, CrewAI, and LangChain, work hands-on with your front-office workflows to architect the exact data engineering infrastructure your traders and quant developers need. We integrate seamlessly into your cloud-native platform, handle change management, and scale only when value is proven.
-The cost? Approximately $10,000 for equivalent capabilities—one-tenth of a full-time hire, with zero long-term overhead.
-We don't propose generic solutions. We audit your specific trading workflows, identify where AI agents create measurable impact, and build production-grade systems your team can deploy immediately.
-I'd like to explore whether a free, two-day AI Opportunity Audit makes sense for Caspian One. No commitment. No cost. Just clarity on what's possible.
-Book here: cal.com/omnithrivetech-ceo
-Warm regards,
-[Your Name]
-Senior B2B Outreach Specialist
+I noticed your hiring for an AI Data Engineer to build generative AI and agent-based systems within your front-office trading workflows. That's critical infrastructure work - and it's exactly where most financial services organizations struggle.
+Here's the reality: 88% of AI pilots never reach production (CIO Magazine). The gap between prototype and live trading system is where projects stall, budgets bloat, and timelines slip. Your search reflects a real need - someone who can design bespoke data engineering for production-grade AI agents that traders actually use.
+The challenge is this: a full-time specialized hire at $100,000 annually takes months to onboard, and you're still betting on their ability to deliver in your specific domain. We take a different approach.
+Omnithrive Technologies is an AI Value Acceleration Studio that builds production-ready AI systems - not pilots. We specialize in turning stalled initiatives into measurable profit within 90 days. For trading platforms specifically, we work with LangChain, LangGraph, and AutoGen to build agent-based systems that integrate directly into front-office workflows. And we deliver equivalent capabilities for approximately one-tenth of what a full-time hire costs.
+Rather than another lengthy recruiting cycle, consider a free 2-Day AI Opportunity Audit. We'll assess your data engineering infrastructure, identify where AI agents could accelerate strategy development and execution, and present a production-ready MVP path - with no commitment required.
+If this resonates, book here: cal.com/omnithrivetech-ceo
+Warm regards,
 Omnithrive Technologies
-admin@omnithrivetech.com | +91 97426 09264</t>
+AI Value Acceleration Studio
+admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -5147,19 +5143,19 @@
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>On Celfocus's ML deployment challenge</t>
+          <t>Re: your Machine Learning Engineer search</t>
         </is>
       </c>
       <c r="O55" s="3" t="inlineStr">
         <is>
           <t>Dear Mário Branco,
-I noticed Celfocus is actively hiring for a Machine Learning Engineer to design, develop, and optimize models while managing containerized environments and MLflow workflows. This tells me you're scaling your ML production capabilities—a critical need in your consulting practice.
-Here's what caught my attention: 88% of ML pilots never reach production (CIO Magazine). Most organizations invest heavily in building models, but struggle with the operational complexity of deployment, monitoring, and continuous optimization at scale.
-We work with consulting firms and enterprises facing exactly this challenge. Rather than hiring a full-time ML engineer at $100,000 annually, we deliver production-ready AI systems—including model tracking, CI/CD pipelines, containerization, and DevOps integration—in 2–3 weeks for approximately one-tenth of that cost.
-Our approach is tailored to your clients' specific workflows. We don't build generic pilots; we deploy systems that integrate directly into their existing data processing infrastructure and governance frameworks. We handle the change management piece too, ensuring your clients' teams can actually operate what we build.
-If Celfocus is looking to accelerate your AI delivery capability while reducing hiring overhead, we should talk. Our complimentary 2-Day AI Opportunity Audit will help you identify quick wins and a path to scaling your ML operations without the traditional hiring burden.
-Would you be open to exploring this?
-Book here: cal.com/omnithrivetech-ceo
+I was reviewing Celfocus's Machine Learning Engineer posting and noticed something that resonates across the industry: 88% of AI pilots never reach production (CIO Magazine). Your role emphasizes exactly this challenge - designing models, building scalable pipelines with MLflow, and deploying containerized environments through Docker and Kubernetes.
+The friction between concept and production is real. Most organizations struggle to bridge that gap, which is why hiring for this position makes sense. However, there's an alternative worth considering.
+Omnithrive Technologies specializes in turning stalled AI initiatives into production-ready systems within 90 days. We work with the exact tech stack your role requires - Python, PyTorch, Kubernetes, MLflow, and modern CI/CD workflows - but deliver equivalent AI capabilities at approximately one-tenth of a full-time hire's cost. Your budgeted $100,000 annually for this role could fund a high-impact AI Opportunity Audit and an MVP that proves measurable value before scaling further.
+We do not build pilots or prototypes. Every system we deploy moves directly into production with embedded change management and adoption support. Our ROI-first approach means you only pay for what delivers results.
+Rather than committing to a 12-month hire search, I would like to invite Celfocus to explore a complimentary 2-Day AI Opportunity Audit. We will assess your current AI initiatives, identify which are closest to production, and outline a 90-day value acceleration strategy.
+If this interests you, I would be pleased to discuss further.
+You can book directly at cal.com/omnithrivetech-ceo or reach out to admin@omnithrivetech.com.
 Warm regards,
 [Your Name]
 Senior B2B Outreach Specialist
@@ -5222,22 +5218,24 @@
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Centrus Energy Corp.'s EPC coordination challenge — an AI perspective</t>
+          <t>AI coordination for Centrus Energy Corp.'s Piketon deployment</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
           <t>Dear Centrus Energy Corp. Team,
-Your search for an EPC Associate Engineer reflects a critical need: coordinating cross-organizational inputs, managing design packages, and providing technical oversight across the Piketon enrichment plant deployment. This role demands expertise in systems coordination, vendor management, and multi-phase project guidance.
-We recognize this challenge because it's endemic across advanced manufacturing. Yet here's the reality: 75% of AI projects fail to deliver ROI, according to the IBM CEO Study 2025. Most organizations hire for capability they could accelerate through intelligent automation instead.
-Consider this: You're budgeting approximately $100,000 annually for an EPC Associate Engineer. Omnithrive Technologies can deliver equivalent AI-powered coordination capabilities—automated design review workflows, real-time vendor communication tracking, cross-discipline input consolidation, and construction milestone guidance—for roughly $10,000. That's 1/10th the cost, with production-ready systems deployed within 90 days, not months of onboarding.
-We don't build pilots or prototypes. Our agentic AI stack (LangGraph, AutoGen, n8n) integrates directly into your existing workflows, turning stalled or inefficient processes into measurable profit centers. We only scale when value is proven.
-Rather than debating capability, we invite you to explore what's possible. Our complimentary 2-Day AI Opportunity Audit—no commitment, no cost—will map your specific coordination bottlenecks and show concrete ROI potential tailored to Centrus Energy Corp.'s deployment timeline.
-Book your audit at cal.com/omnithrivetech-ceo, or reach out directly at admin@omnithrivetech.com.
-Warm regards,
-**Omnithrive Technologies**
+I'm reaching out because your EPC Associate Engineer role caught our attention - specifically the cross-organizational coordination and technical oversight responsibilities across design, procurement, and commissioning phases at your Piketon enrichment facility.
+That coordination burden is exactly where enterprises like yours lose efficiency and incur hidden costs. Managing guidance workflows, design package reviews, and contractor oversight across multiple disciplines typically requires either significant headcount investment or fragmented tooling.
+Here's what we've observed: 75% of AI projects fail to deliver ROI (IBM CEO Study, 2025). Most organizations either over-invest in generic tools or under-invest in purpose-built systems that actually integrate into their workflows.
+Omnithrive Technologies specializes in the alternative - production-ready AI systems that automate coordination, documentation, and cross-discipline communication without requiring permanent hires. Rather than staffing an EPC Associate Engineer role at $100,000 annually, advanced AI capabilities purpose-built for your project management workflows cost approximately one-tenth that investment while scaling across all your active projects simultaneously.
+We've helped mid-to-large manufacturers and infrastructure organizations eliminate coordination bottlenecks and compress project timelines within 90 days. No pilots. No long sales cycles. Just measurable value.
+We would like to conduct a complimentary 2-Day AI Opportunity Audit for Centrus Energy Corp. - no commitment, no cost. We will identify specific coordination and oversight processes where AI can deliver immediate ROI.
+Schedule here: cal.com/omnithrivetech-ceo
+Warm regards,
+Omnithrive Technologies
 AI Value Acceleration Studio
-admin@omnithrivetech.com | +91 97426 09264</t>
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -5301,22 +5299,25 @@
       <c r="M57" s="3" t="inlineStr"/>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>Checkly's infrastructure hiring — an AI alternative</t>
+          <t>Checkly's AI Agent build - a cost perspective</t>
         </is>
       </c>
       <c r="O57" s="3" t="inlineStr">
         <is>
           <t>Dear Kaylie Boogaerts,
-I noticed Checkly is actively recruiting for a Senior Software Engineer - Infrastructure role, with a budget of approximately $100,000 annually. Given your team's work with AI Agents and infrastructure-as-code tools like Pulumi and Terraform, I wanted to share a perspective that may be relevant to your hiring strategy.
-According to IBM's 2025 CEO Study, 75% of AI projects fail to deliver ROI — largely because organizations either hire generalists or build pilots that never reach production. At Omnithrive Technologies, we specialize in doing the opposite: delivering production-ready AI systems that integrate directly into your existing infrastructure workflows within 90 days.
-Rather than committing $100,000 annually to a full-time infrastructure engineer, consider this: our expert AI developers — specialists in LangChain, LangGraph, and AutoGen — can architect and deploy custom AI agents tailored to your monitoring and automation workflows for approximately one-tenth that cost. Your infrastructure team gains immediate AI capabilities without long-term headcount commitments.
-We work specifically with SaaS companies facing process inefficiency and infrastructure scale challenges. Our approach is ROI-first: no prototypes, no endless pilots — only measurable results.
-I'd like to invite you to a complimentary 2-Day AI Opportunity Audit at no cost or commitment. This will clarify which infrastructure workflows could benefit most from AI acceleration and what production-ready deployment looks like for Checkly.
-You can schedule directly at cal.com/omnithrivetech-ceo.
+I noticed Checkly is actively recruiting for a Senior Software Engineer - Infrastructure to work on AI Agents and infrastructure automation (Pulumi, Terraform). That's a $100,000 annual investment for specialized talent.
+Here's the challenge: 75% of AI projects fail to deliver ROI, according to the IBM CEO Study 2025. Most organizations either hire extensively or build pilots that stall in production.
+At Omnithrive Technologies, we take a different approach. We deliver production-ready AI systems - not prototypes - tailored to your exact workflows. For Checkly's infrastructure monitoring and reliability challenges, we could architect and deploy a custom AI Agent system that automates your most costly operational inefficiencies within 90 days.
+The economics are compelling: our high-impact AI builds and expert developer support cost approximately one-tenth of a full-time infrastructure engineer's salary. You get immediate, measurable returns without the hiring timeline, onboarding delays, or long-term overhead.
+Rather than recruiting, consider proving AI value first. Our complimentary 2-Day AI Opportunity Audit would identify the highest-leverage automation opportunities within your monitoring and infrastructure stack - with zero commitment or cost.
+We've worked with SaaS and infrastructure companies facing similar scaling pressures. The audit alone typically reveals $200K-$500K in annual efficiency gains.
+I would welcome a brief conversation about whether this approach aligns with Checkly's priorities.
+Book your audit at cal.com/omnithrivetech-ceo, or reply directly to explore further.
 Warm regards,
 Omnithrive Technologies
 AI Value Acceleration Studio
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -5380,22 +5381,26 @@
       <c r="M58" s="2" t="inlineStr"/>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Re: your ML Engineer search at Chiron AI</t>
+          <t>Building production ML for Chiron AI's self-care platform</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
           <t>Dear Davide Crescenzi,
-I've followed Chiron AI's work in personalized, evidence-based self-care interventions—particularly your focus on tailoring AI-driven solutions to individual health profiles. That level of clinical precision requires sophisticated machine learning architecture.
-I noticed you're hiring a full-time Machine Learning Engineer (€100,000/year budget). Before you commit to that investment, I want to share a perspective: 75% of AI projects fail to deliver ROI, according to the IBM CEO Study 2025. Many enterprises build capability in-house, only to discover their models don't translate to production-grade performance or measurable clinical impact.
-Here's the opportunity: Omnithrive Technologies specializes in turning stalled or failing AI initiatives into production-ready systems within 90 days. We deliver equivalent machine learning capabilities—custom-built for your workflows—at approximately 1/10th the cost of a full-time hire. Rather than a 12-month hiring cycle and onboarding risk, you get expert AI developers (proficient in LangChain, LangGraph, AutoGen, and CrewAI) deployed immediately, with built-in change management to ensure adoption.
-We don't build pilots. We build production systems with measurable ROI, or we don't charge.
-Given Chiron AI's clinical focus, I'd like to invite you to a complimentary 2-Day AI Opportunity Audit. No commitment. No cost. We'll map your current ML initiatives, identify friction points, and propose a clear path to measurable impact.
-If this resonates, please book a time here: cal.com/omnithrivetech-ceo
-Warm regards,
-**Omnithrive Technologies**
+I noticed you are recruiting a Machine Learning Engineer for your Treviso office - a significant investment at approximately $100,000 annually. I wanted to reach out with a perspective that might be valuable for your team.
+Chiron AI's mission to deliver clinically effective, personalized self-care interventions is compelling. The machine learning expertise required to build and refine those adaptive recommendation systems is clearly critical. However, 88% of AI pilots never reach production (CIO Magazine), and full-time hiring cycles often delay deployment further.
+Here is what we have discovered: organizations like Chiron AI can access production-ready ML capabilities through expert AI developers at approximately $10,000 annually - roughly one-tenth of traditional FTE costs. Our team specializes in building agentic AI systems using LangChain, LangGraph, and AutoGen that integrate directly into clinical workflows. We work within your existing tech stack and deliver measurable value within 90 days, not months.
+Rather than a lengthy recruitment process, you could:
+- Validate your ML approach with rapid prototyping
+- Accelerate time-to-production for your personalization engine
+- Scale your engineering team on-demand without long-term overhead
+I would like to offer you a complimentary 2-Day AI Opportunity Audit at no cost and with no commitment. We can assess your current ML pipeline, identify bottlenecks in your self-care intervention system, and show you exactly where production-grade AI acceleration would have the highest clinical and operational impact.
+If this is relevant, please book a time here: cal.com/omnithrivetech-ceo
+Warm regards,
+Omnithrive Technologies
 AI Value Acceleration Studio
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -5490,19 +5495,20 @@
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>Church International Limited's AI hiring — a perspective</t>
+          <t>Church International Limited's AI modernization angle</t>
         </is>
       </c>
       <c r="O59" s="3" t="inlineStr">
         <is>
           <t>Dear Patricia Phillips,
-I noticed Church International Limited is actively hiring for a Data Engineer role with a $100,000 annual budget. Given your firm's focus on modernizing data infrastructure and optimizing ETL pipelines, I wanted to share a perspective that may be relevant.
-Your job description emphasizes critical priorities: migrating legacy SAS and Alteryx workflows into consistent, modern logic, designing reusable macros to reduce technical debt, and automating release processes for faster deployments. These are exactly the areas where AI-driven automation delivers outsized value—yet 75% of AI projects fail to deliver ROI (IBM CEO Study, 2025).
-Here is what we have observed: organizations like yours often hire expensive full-time engineers to tackle automation and modernization work, when production-ready AI systems can accomplish equivalent capabilities for a fraction of the cost.
-Omnithrive Technologies specializes in turning stalled or failing AI initiatives into measurable profits within 90 days. Rather than a lengthy hiring process and onboarding cycle, we deliver production-ready systems—not pilots—custom-built for your exact workflows. Our agentic AI platform handles data pipeline optimization, workflow rationalization, and automation infrastructure at approximately 1/10th of what you would invest in a full-time hire.
-We do not offer generic tools or endless consulting. We guarantee measurable results or we do not charge.
-I would like to invite you to a complimentary 2-Day AI Opportunity Audit, where we assess your current ETL landscape and identify where AI can eliminate technical debt and accelerate your modernization roadmap. No commitment. No cost.
-You can book directly here: cal.com/omnithrivetech-ceo
+I've been following Church International Limited's work in data engineering and ETL modernization. Your recent Data Engineer posting caught my attention - particularly the mandate to rationalize legacy Alteryx workflows and migrate SAS transformations into modern, maintainable logic.
+That's a real challenge. Most organizations face it, and most solve it the traditional way: hire a full-time specialist at $100,000+ annually. But there's a faster, more cost-effective path forward.
+Here's the reality: 88% of AI pilots never reach production (CIO Magazine). Yet the right agentic AI systems can automate exactly what you're describing - ETL pipeline optimization, workflow rationalization, and intelligent data governance - at a fraction of traditional hiring costs.
+Omnithrive Technologies specializes in turning stalled or failing AI initiatives into measurable profits within 90 days. We don't build prototypes or demos. We deliver production-ready systems that integrate directly into your existing tech stack - Alteryx, data ingestion workflows, release automation, the full picture.
+Here's what matters: equivalent AI-driven capabilities, delivered in weeks, for roughly 1/10th of what you'd pay a dedicated hire. No long-term salary commitment. No overhead. Pure value.
+I'd like to invite you to a complimentary 2-Day AI Opportunity Audit. No cost, no commitment - just a clear-eyed assessment of where AI can reduce technical debt and accelerate your data modernization roadmap.
+Are you open to a brief conversation?
+You can schedule directly at cal.com/omnithrivetech-ceo, or reach me at admin@omnithrivetech.com.
 Warm regards,
 Omnithrive Technologies
 AI Value Acceleration Studio
@@ -5570,99 +5576,98 @@
       <c r="M60" s="2" t="inlineStr"/>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Rethinking Citrus's AI infrastructure investment</t>
+          <t>Re: your Kubernetes Engineer search</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
           <t>Dear Joanna Westcott,
-I noticed Citrus is actively recruiting a Kubernetes Engineer at $100,000 annually—a significant investment in infrastructure talent. I wanted to share a perspective that may be worth considering.
-Most organizations building cloud-based solutions face a parallel challenge: deploying AI systems that actually deliver measurable business value. According to IBM's 2025 CEO Study, 75% of AI projects fail to deliver ROI, and many remain stuck in pilot phases indefinitely.
-At Omnithrive Technologies, we specialize in turning stalled or failing AI initiatives into production-ready systems within 90 days. Our approach differs fundamentally: we build custom AI workflows tailored to your exact infrastructure and business processes—no generic tools, no endless pilots. Rather than adding headcount, many SaaS companies like yours are discovering they can access specialized AI development expertise at approximately $10,000 annually through our expert developer program, delivering capabilities equivalent to a full-time hire at one-tenth the cost.
-This is particularly relevant for companies managing complex infrastructure. AI agents built on frameworks like LangGraph and CrewAI can automate significant portions of operational overhead when properly deployed into your existing Kubernetes environment.
-Before making any hiring decisions, it may be valuable to understand what AI opportunities currently exist within your workflows. We offer a complimentary 2-Day AI Opportunity Audit—no cost, no commitment—to identify where automation could reduce costs and improve efficiency.
-If this resonates, I would welcome a brief conversation. You can book directly at cal.com/omnithrivetech-ceo.
+I noticed Citrus is actively recruiting for a Kubernetes Engineer at $100,000 annually. Before you commit to that investment, I wanted to share a perspective that might reshape how you approach infrastructure automation and deployment optimization.
+At Omnithrive Technologies, we specialize in turning stalled AI initiatives into measurable profit within 90 days. For SaaS companies like Citrus managing complex Kubernetes environments, we've found that agentic AI systems can dramatically reduce manual orchestration overhead, improve container deployment efficiency, and accelerate infrastructure decisions - capabilities traditionally requiring dedicated senior engineering hires.
+Here is the critical insight: 88% of AI pilots never reach production (CIO Magazine). Most organizations invest heavily in proof-of-concepts that fail to deliver real value. We build differently. We deliver production-ready systems, not prototypes.
+Our approach costs approximately $10,000 - roughly one-tenth of what you would allocate for a full-time Kubernetes specialist - while providing automation capabilities that compound over time without the retention burden of a permanent headcount.
+Rather than proposing a solution, I would like to invite you to a complimentary 2-Day AI Opportunity Audit. We will analyze your specific infrastructure challenges, containerization workflows, and deployment friction points to identify where AI-driven automation delivers the highest ROI for Citrus.
+There is no commitment, no cost, and no obligation.
+If this resonates, I would welcome a brief conversation. You can book directly at cal.com/omnithrivetech-ceo, or reach out at admin@omnithrivetech.com.
+Warm regards,
+Omnithrive Technologies
+AI Value Acceleration Studio</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Cloudflare</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cloudflare.com/</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Cloudflare delivers 60+ networking, security, and performance services through their connectivity cloud, helping organizations connect, protect, and build everywhere.</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Cybersecurity</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Frontend Engineer, AI Crawl Control</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>Lisbon, Portugal</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr"/>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>Agentic AI, Artificial Intelligence, GenAI, SQL</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>Melissa Loh</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>Account Executive</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>mel@cloudflare.com</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr"/>
+      <c r="M61" s="3" t="inlineStr"/>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
+          <t>Re: your Frontend Engineer, AI Crawl Control search</t>
+        </is>
+      </c>
+      <c r="O61" s="3" t="inlineStr">
+        <is>
+          <t>Dear Melissa Loh,
+I noticed Cloudflare is hiring for a Frontend Engineer specializing in Agentic AI and AI Crawl Control. Building production-grade agentic systems at scale is exactly where most organizations struggle-and where costs spiral.
+Here's the reality: 88% of AI pilots never reach production (CIO Magazine). Your team likely needs someone who can move beyond prototypes into deployment-ready systems for crawl optimization and control workflows. That's a $100,000 annual commitment for one hire, plus onboarding overhead and dependency risk.
+At Omnithrive Technologies, we deliver equivalent agentic AI capabilities-custom-built for your exact workflows-at approximately 1/10th that cost. We specialize in turning stalled AI initiatives into measurable business value within 90 days. Our approach uses production-ready frameworks (LangChain, LangGraph, AutoGen, CrewAI) and integrates seamlessly with your existing stack. Unlike hiring, you get a team that builds to proven ROI, then scales only when value is demonstrated.
+Rather than debate hiring versus building, I'd like to propose a better path: a complimentary 2-Day AI Opportunity Audit. No commitment, no cost. We'll assess your crawl control workflows, identify high-impact automation opportunities, and show you exactly what production-ready agentic AI could deliver for Cloudflare-in concrete terms, with timelines and cost clarity.
+This conversation takes 30 minutes to schedule and could reshape how you approach AI infrastructure.
+Would you be open to exploring this?
+Book your audit here: cal.com/omnithrivetech-ceo
 Warm regards,
 [Your Name]
 Senior B2B Outreach Specialist
 Omnithrive Technologies
-admin@omnithrivetech.com
-+91 97426 09264</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>Cloudflare</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>https://www.cloudflare.com/</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>Cloudflare delivers 60+ networking, security, and performance services through their connectivity cloud, helping organizations connect, protect, and build everywhere.</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>Cybersecurity</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>Frontend Engineer, AI Crawl Control</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="inlineStr">
-        <is>
-          <t>Lisbon, Portugal</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr"/>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>Agentic AI, Artificial Intelligence, GenAI, SQL</t>
-        </is>
-      </c>
-      <c r="I61" s="3" t="inlineStr">
-        <is>
-          <t>Melissa Loh</t>
-        </is>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>Account Executive</t>
-        </is>
-      </c>
-      <c r="K61" s="3" t="inlineStr">
-        <is>
-          <t>mel@cloudflare.com</t>
-        </is>
-      </c>
-      <c r="L61" s="3" t="inlineStr"/>
-      <c r="M61" s="3" t="inlineStr"/>
-      <c r="N61" s="3" t="inlineStr">
-        <is>
-          <t>Cloudflare's AI Crawl Control — a build vs. hire consideration</t>
-        </is>
-      </c>
-      <c r="O61" s="3" t="inlineStr">
-        <is>
-          <t>Dear Melissa Loh,
-I noticed Cloudflare is actively hiring for a Frontend Engineer specializing in Agentic AI and AI Crawl Control. This is a critical role—and typically a $100,000+ annual commitment before productivity gains materialize.
-I wanted to share a perspective: 88% of AI pilots never reach production (CIO Magazine), and most organizations underestimate both the timeline and cost of scaling AI capabilities internally. The hiring approach is valid, but there's a parallel path worth exploring.
-Omnithrive Technologies specializes in turning stalled or failing AI initiatives into production-ready systems within 90 days. For Cloudflare's specific use case—building intelligent crawl control and agentic AI workflows—we can deliver equivalent capabilities for approximately one-tenth of a full-time hire's annual cost. This means you get a working, integrated system ($10,000 range) versus a 6-12 month ramp-up cycle for a new engineer.
-Our approach is ROI-first: we build custom systems using LangChain, LangGraph, and AutoGen—the exact stack your role demands—and we don't hand off until value is proven and adoption is embedded.
-Rather than positioning this as a hire versus outsource decision, consider a 2-Day AI Opportunity Audit. We'll assess your crawl control and agentic AI gaps, map a production roadmap, and show you the realistic cost and timeline for either approach. No commitment. No cost.
-If this resonates, I'd welcome a brief conversation.
-**Book here:** cal.com/omnithrivetech-ceo
-Warm regards,
-**Omnithrive Technologies**
-AI Value Acceleration Studio
 admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
         </is>
       </c>
@@ -5807,23 +5812,23 @@
       <c r="M63" s="3" t="inlineStr"/>
       <c r="N63" s="3" t="inlineStr">
         <is>
-          <t>Re: Your Senior AI Engineer search at Codento</t>
+          <t>A thought on Codento's AI agent scaling</t>
         </is>
       </c>
       <c r="O63" s="3" t="inlineStr">
         <is>
           <t>Dear Markku Tuomala,
-I noticed Codento is actively recruiting for a Senior AI Engineer to build AI agents and strengthen your Google Cloud capabilities. This signals a critical gap—and it's a costly one to fill.
-Here's the reality: 88% of AI pilots never reach production (CIO Magazine). Most organizations hire senior engineers to bridge this gap, only to discover that talent alone doesn't guarantee deployment success. At $100,000 annually, you're investing heavily in headcount without certainty of production-ready outcomes.
-Omnithrive Technologies takes a different approach. Rather than hiring for capability, we deliver production-ready AI systems tailored to your exact workflows—whether that's AI agent orchestration, business intelligence automation, or Google Cloud-native solutions. Our cost? Approximately $10,000 to solve what would traditionally require a full-time senior hire, with the added advantage of guaranteed ROI within 90 days.
-More importantly, we bring what hiring cannot: production expertise, built-in change management, and accountability for measurable results. Your business intelligence and customer engagement initiatives move from concept to scaled deployment—not pilots that stall.
-We're not proposing another AI agency pitch. Instead, I'd like to invite you to a complimentary 2-Day AI Opportunity Audit. We'll assess your current AI initiatives, identify where value is being left on the table, and outline a clear path to production-ready systems.
-No commitment. No cost. Just clarity on what's possible for Codento.
-Book your audit here: cal.com/omnithrivetech-ceo
+I noticed Codento is actively hiring for a Senior AI Engineer to build and scale AI agents on Google Cloud. This suggests you're moving beyond proof-of-concept into production deployment-a critical inflection point for most enterprises.
+Here's the challenge: 88% of AI pilots never reach production, according to CIO Magazine. The gap between prototype and production-ready systems is where most initiatives stall. Beyond hiring expertise, you need an execution partner who understands the full production stack: agentic frameworks like LangGraph and AutoGen, orchestration platforms like n8n, and most importantly, the change management required for sustainable adoption.
+We work exclusively with enterprises like yours who are transitioning AI initiatives from conceptual to revenue-generating. Rather than a single full-time hire at your $100,000 annual budget, consider this: our expert AI developers-specialized in agentic AI, LangChain, and Google Cloud integrations-cost approximately $10,000 annually while delivering production-ready systems within 90 days.
+We don't offer pilots or prototypes. We deliver measurable value or no fee.
+Before you commit to a permanent hire, I'd like to propose a complementary 2-Day AI Opportunity Audit. No commitment, no cost. We'll identify where your current AI initiatives are bottlenecked and show you exactly how to accelerate them to production.
+If this resonates, please book a time at cal.com/omnithrivetech-ceo.
 Warm regards,
 Omnithrive Technologies
 AI Value Acceleration Studio
-admin@omnithrivetech.com | +91 97426 09264</t>
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -5902,22 +5907,24 @@
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Re: Your Data and AI Engineer search</t>
+          <t>Re: your Data and AI Engineer search</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
           <t>Dear Coders Connect Team,
-I've followed your Data and AI Engineer opening with interest. Your focus on building "end-to-end data pipelines that turn raw data into actionable insights" and automating ETL/ML workflows to deliver AI-ready datasets reflects a real market need—and a genuine challenge many organizations face.
-Here's the tension: 75% of AI projects fail to deliver ROI (IBM CEO Study, 2025). Most fail not because the talent isn't there, but because initiatives stall between proof-of-concept and production. Hiring a full-time engineer at $100,000 annually solves part of the problem—but only if that person is embedded in your operations from day one.
-At Omnithrive Technologies, we specialize in accelerating AI initiatives that are already in progress or stalled. We build production-ready systems—not pilots—using the same tech stack your team relies on: LangChain, LangGraph, AutoGen, n8n, and modern LLMs. Our developers deliver equivalent AI engineering capabilities for approximately 1/10th of what a full-time hire costs. More importantly, we embed change management and adoption support, so your systems actually scale.
-We've helped mid-to-large enterprises in SaaS, data services, and analytics unlock millions in operational efficiency. We don't charge for outcomes we don't deliver.
-Rather than another generic proposal, I'd like to invite you to a complimentary 2-Day AI Opportunity Audit—no commitment required. We'll map your current bottlenecks and identify where AI-accelerated pipelines could move the needle fastest.
-Book a slot here: cal.com/omnithrivetech-ceo
+I noticed you are actively hiring for a Data and AI Engineer role. Before you commit $100,000 annually to a full-time hire, I wanted to share a perspective that might reshape how you approach this investment.
+Your job description emphasizes designing end-to-end data pipelines and building AI-ready datasets that translate business needs into robust technical solutions. These are mission-critical functions. However, 75% of AI projects fail to deliver ROI, according to the IBM CEO Study 2025 - often because the architecture and workflow optimization happen in isolation from actual business impact measurement.
+At Omnithrive Technologies, we specialize in turning stalled or failing AI initiatives into measurable profits within 90 days. We work with data and AI engineering teams to build production-ready systems - not pilots or prototypes - that automate data ingestion, orchestration, and ML workflows while delivering quantifiable business value from day one.
+Here is the economics: Omnithrive delivers equivalent AI engineering capabilities for approximately 1/10th of what you would pay a full-time Data and AI Engineer. At $10,000 versus your $100,000 annual budget, you gain expert-level agentic AI development (LangChain, LangGraph, AutoGen), end-to-end automation, and built-in change management - with no long-term employment overhead.
+We have helped mid-to-large enterprises in data-intensive industries eliminate pipeline bottlenecks and reduce time-to-insight significantly.
+I would like to invite you to explore this further through our complimentary 2-Day AI Opportunity Audit - no commitment, no cost. This is where we assess your specific data engineering challenges and quantify the ROI potential.
+You can book directly at cal.com/omnithrivetech-ceo.
 Warm regards,
 Omnithrive Technologies
 AI Value Acceleration Studio
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -6122,22 +6129,21 @@
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Data Engineer hiring vs. AI-native automation—a cost perspective</t>
+          <t>Rethinking your Data Engineer hire for Nutrition &amp; Feed</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
           <t>Dear Marina Lepeshko,
-I noticed Coherent Solutions is actively hiring for a Data Engineer in the Nutrition &amp; Feed sphere, with a budget of approximately $100,000 annually. Given the competitive talent market and the specific skill set required—Java, Scala, Python, data warehousing, and cloud orchestration—I wanted to share a perspective that may be worth considering.
-Rather than bearing the full cost of a dedicated hire, many enterprises in your space are now deploying AI-driven automation to handle data pipeline orchestration, cloud ecosystem management, and platform optimization tasks that traditionally required senior engineering resources.
-Here's the reality: 75% of AI projects fail to deliver ROI because they lack production-ready implementation. At Omnithrive Technologies, we specialize in turning stalled AI initiatives into measurable value within 90 days. Our approach delivers equivalent AI capabilities for approximately one-tenth of your annual hiring budget—roughly $10,000 versus $100,000—while eliminating recruitment and onboarding timelines.
-We work extensively with data engineering teams to automate cloud platform management, data warehouse optimization, and cross-region collaboration workflows using agentic AI and orchestration tools like n8n and LangGraph.
-Before you finalize your hiring decision, I'd like to invite you to our complimentary 2-Day AI Opportunity Audit. We'll assess your specific data engineering challenges, quantify potential automation ROI, and demonstrate how AI-native solutions can either augment or reduce your hiring needs.
-No commitment required. Simply book a time that works for you at cal.com/omnithrivetech-ceo.
+I noticed Coherent Solutions is hiring a Data Engineer for your Nutrition &amp; Feed sphere, with a budget of approximately $100,000 annually. Given the complexity of orchestrating cloud ecosystems across multiple applications and supporting distributed teams with data warehousing solutions, I understand the urgency.
+However, 75% of AI projects fail to deliver ROI, according to the IBM CEO Study 2025. Many organizations hire for capability they could accelerate through strategic automation instead.
+Here is the core insight: Omnithrive Technologies can deliver equivalent AI-driven data engineering capabilities - including cloud platform optimization, data pipeline automation, and intelligent orchestration across your tools - for roughly one-tenth of what you would invest in a full-time hire. Rather than waiting months to onboard and train a new team member, you could have production-ready systems handling data integration and platform optimization within 90 days.
+We specialize in turning stalled or failing AI initiatives into measurable profit. Our approach is not theoretical. We build custom, production-ready systems that integrate directly into your existing workflows - whether that involves Java, Scala, Python environments or your cloud-based data platforms. No pilots. No prototypes. Only results.
+I would like to invite you to a complimentary 2-Day AI Opportunity Audit, where we assess your specific data engineering and platform challenges and identify where AI-driven automation could reduce operational friction and cost. There is no commitment, and no cost.
+You can book directly at cal.com/omnithrivetech-ceo, or reach out to admin@omnithrivetech.com.
 Warm regards,
 Omnithrive Technologies
-AI Value Acceleration Studio
-admin@omnithrivetech.com | +91 97426 09264</t>
+AI Value Acceleration Studio</t>
         </is>
       </c>
     </row>
@@ -6223,25 +6229,25 @@
       </c>
       <c r="N67" s="3" t="inlineStr">
         <is>
-          <t>Agent workflows in SDLC — a faster path than hiring</t>
+          <t>A thought on Coltech's AI Engineer build</t>
         </is>
       </c>
       <c r="O67" s="3" t="inlineStr">
         <is>
           <t>Dear Coltech Team,
-I've followed your search for an AI Engineer and noticed the focus on agent-based workflows within modern SDLC environments—specifically VSCode extensions, RAG integrations, and platform evolution across AWS/GCP.
-That's a critical capability to build. The challenge, though, is well-documented: 88% of AI pilots never reach production (CIO Magazine), and recruiting an engineer to own this mandate takes months while the gap persists.
-At Omnithrive Technologies, we accelerate exactly this type of initiative. We build production-ready agent systems integrated into developer toolchains—the kind that embed directly into your SDLC, not sandbox environments. Our team has deep hands-on experience with LangGraph, AutoGen, and agentic workflows that power modern development platforms.
-Here's the economics: your AI Engineer role carries a $100,000 annual budget. We can deliver equivalent AI capabilities—scoped, built, and operationalized—for approximately one-tenth that cost. More importantly, we guarantee measurable value within 90 days or adjust our fee.
-Rather than a lengthy hiring cycle, consider a 2-Day AI Opportunity Audit. We'll map your specific SDLC challenges, identify where agent workflows create the highest ROI, and show you a clear path to production-ready systems—no commitment required.
-If this resonates, let's schedule 30 minutes:
-cal.com/omnithrivetech-ceo
-Or reach out directly: admin@omnithrivetech.com | WhatsApp: +91 97426 09264
+I've reviewed your AI Engineer role and noticed something worth exploring: you're building agent-based workflows into VSCode extensions and RAG integrations - complex, high-value work that typically requires a dedicated hire at roughly $100,000 annually.
+There's an alternative worth considering.
+At Omnithrive Technologies, we specialize in turning stalled AI initiatives into production-ready systems within 90 days. We work exclusively with agentic AI frameworks - LangChain, LangGraph, AutoGen, CrewAI - the same stack powering modern developer tooling. Rather than carrying a full-time engineering cost, you could access equivalent AI capabilities at approximately 1/10th the expense, while maintaining focus on your core platform development.
+The problem is real: 88% of AI pilots never reach production (CIO Magazine). Most organizations either underbuild or overcommit. We've found the middle path - production-ready systems that integrate seamlessly into existing SDLC workflows without the overhead.
+Given your focus on GitHub Copilot integration and cloud-native development practices, we believe there's meaningful value in a conversation about how agent workflows can accelerate your platform without the recruitment timeline or ongoing employment costs.
+I'd like to invite you to a complimentary 2-Day AI Opportunity Audit. No commitment, no cost - just a clear assessment of where AI-driven developer tooling can deliver measurable impact for Coltech.
+Book here: cal.com/omnithrivetech-ceo
 Warm regards,
 [Your Name]
 Senior B2B Outreach Specialist
 Omnithrive Technologies
-AI Value Acceleration Studio</t>
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -6329,20 +6335,97 @@
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>On scaling ML production without the $100K hire</t>
+          <t>Scaling ML models faster - without the hire</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
           <t>Dear Yuanjie Zhang,
-I've reviewed Conflux's Senior Machine Learning Engineer opening, and I recognize the challenge: you need someone capable of moving ML models from prototype to production at scale—someone fluent in both the technical stack (Python, Scala, cloud environments) and client advisory.
-Here's what caught my attention: your JD emphasizes "proven experience in productionizing and scaling ML models" and "consultancy skills to advise clients technically." Those are precisely the bottlenecks we solve every day.
-The reality is stark—88% of AI pilots never reach production (CIO Magazine). Most organizations treat ML as a R&amp;D exercise, not a revenue driver. Yet you're hiring to fix exactly that problem internally, which will cost Conflux approximately $100,000 annually in salary, benefits, and onboarding overhead.
-What if you could access equivalent AI engineering capabilities—custom agentic systems, model optimization, production deployment, and change management—for roughly 1/10th of that investment? We build production-ready ML systems in 2–3 weeks, not months, using the modern stack your clients demand (LangChain, LangGraph, AutoGen, cloud-native architectures).
-Rather than solve this through traditional hiring, consider whether a strategic partnership makes more sense. We specialize in turning stalled or failing AI initiatives into measurable profit—exactly what your consulting clients need.
-I'd like to show you what's possible. We offer a complimentary 2-Day AI Opportunity Audit—no commitment, no cost—to identify where AI acceleration could strengthen Conflux's delivery capabilities.
-Ready to explore?
-Book here: cal.com/omnithrivetech-ceo
+I noticed Conflux is hiring for a Senior Machine Learning Engineer with expertise in productionizing and scaling ML models across cloud environments. That's a critical role-and at $100,000 annually, a significant investment.
+Here's what we're observing: 88% of ML pilots never reach production (CIO Magazine). The gap between experimental models and deployed systems costs enterprises millions. Even with the right senior hire, implementation timelines stretch, and ROI often stalls.
+At Omnithrive Technologies, we specialize in turning stalled AI initiatives into measurable profit within 90 days. Our approach differs fundamentally: we build production-ready systems using LangChain, LangGraph, and AutoGen-not prototypes or pilots. More importantly, we embed change management and adoption support, ensuring your models actually scale.
+For clients like yours, we deliver equivalent ML engineering capabilities at approximately $10,000-one-tenth of what a full-time senior engineer costs annually. We work across the exact tech stack your JD specifies: Python, Scala, AWS, GCP, and Azure. Our team brings consultancy-grade advisory skills to help you advise clients on deploying models that work, not concepts that sound good.
+Rather than replacing your hiring process, consider this: validate your AI strategy first. Our complimentary 2-Day AI Opportunity Audit identifies which initiatives will generate ROI and which pose risk. No commitment. No cost.
+I would welcome a brief conversation.
+Schedule here: cal.com/omnithrivetech-ceo
+Warm regards,
+Omnithrive Technologies
+AI Value Acceleration Studio
+admin@omnithrivetech.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Consort Group</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>https://consort-group.com/en/</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Consort Group enhances the performance of businesses and information systems through various services, including cybersecurity, digital development, and data expertise.</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>IT Services, Cybersecurity, AI/ML, SaaS</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>Scientifique des données</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>Toulouse, Occitanie, France</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr"/>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence, Data Engineer, Data Engineering, Data Science</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>Simon Picavet</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>Product Owner</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>simon.picavet@consort-group.com</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/simon-picavet-81b57182</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr"/>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
+          <t>Re: your Scientifique des données search</t>
+        </is>
+      </c>
+      <c r="O69" s="3" t="inlineStr">
+        <is>
+          <t>Dear Simon Picavet,
+I noticed Consort Group is actively hiring for a Scientifique des données role, likely to strengthen your data engineering and AI capabilities across client engagements. That's a significant investment - and a critical one, given the complexity of delivering production-grade AI solutions in cybersecurity and digital development.
+Here's a perspective worth considering: 88% of AI pilots never reach production (CIO Magazine). Most organizations struggle not with hiring talent, but with translating that talent into measurable business value. A full-time data scientist at your $100,000 annual budget is essential, but they're only one part of the equation.
+At Omnithrive Technologies, we take a different approach. We deliver production-ready AI systems in 90 days - custom-built into your existing workflows, with built-in adoption and change management. Our cost: approximately $10,000 for a high-impact MVP, delivering equivalent AI capabilities at 1/10th of what you'd pay a full-time hire. We've built systems using LangChain, LangGraph, and multi-agent frameworks that solve problems your data team identifies but lacks bandwidth to execute.
+Rather than replace your hiring decision, we can accelerate your timeline. A 2-Day AI Opportunity Audit (completely free, no commitment) would show you exactly where AI can drive measurable ROI across your service delivery - whether that's automating data pipelines, enhancing threat detection, or scaling client solutions faster.
+I'd welcome a brief conversation. You can schedule directly at cal.com/omnithrivetech-ceo, or reach out at admin@omnithrivetech.com.
 Warm regards,
 [Your Name]
 Senior B2B Outreach Specialist
@@ -6350,241 +6433,163 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>Consort Group</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>https://consort-group.com/en/</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>Consort Group enhances the performance of businesses and information systems through various services, including cybersecurity, digital development, and data expertise.</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>IT Services, Cybersecurity, AI/ML, SaaS</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>Scientifique des données</t>
-        </is>
-      </c>
-      <c r="F69" s="3" t="inlineStr">
-        <is>
-          <t>Toulouse, Occitanie, France</t>
-        </is>
-      </c>
-      <c r="G69" s="3" t="inlineStr"/>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence, Data Engineer, Data Engineering, Data Science</t>
-        </is>
-      </c>
-      <c r="I69" s="3" t="inlineStr">
-        <is>
-          <t>Simon Picavet</t>
-        </is>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>Product Owner</t>
-        </is>
-      </c>
-      <c r="K69" s="3" t="inlineStr">
-        <is>
-          <t>simon.picavet@consort-group.com</t>
-        </is>
-      </c>
-      <c r="L69" s="3" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/simon-picavet-81b57182</t>
-        </is>
-      </c>
-      <c r="M69" s="3" t="inlineStr"/>
-      <c r="N69" s="3" t="inlineStr">
-        <is>
-          <t>On Consort Group's AI talent strategy</t>
-        </is>
-      </c>
-      <c r="O69" s="3" t="inlineStr">
-        <is>
-          <t>Dear Simon Picavet,
-I noticed Consort Group is actively recruiting a Scientifique des données to strengthen your data engineering and AI capabilities. That's a smart move—but I wanted to share a perspective that might reframe how you approach it.
-You're budgeting approximately $100,000 annually for this role. Here's the reality: 75% of AI projects fail to deliver ROI, according to the IBM CEO Study 2025. Most organizations struggle not because they lack talent, but because they lack *production-ready systems* and clear value frameworks from day one.
-At Omnithrive Technologies, we've built an alternative: instead of hiring another full-time data scientist, you could access equivalent AI capabilities—custom-built agentic systems, data engineering automation, and model deployment—for roughly 1/10th of that investment. Our team specializes in turning stalled or failing AI initiatives into measurable profits within 90 days, using the exact tech stack your team values: advanced data engineering, production-ready AI agents, and seamless system integration.
-Rather than replacing your hiring, think of us as a force multiplier. We audit your existing workflows, identify high-impact AI opportunities, and deliver working systems—not pilots or prototypes. Your new hire would inherit proven infrastructure and a clear roadmap.
-I'd like to invite you to a complimentary 2-Day AI Opportunity Audit. No commitment, no cost—just clarity on where AI can genuinely move the needle for Consort Group.
-You can book a time here: cal.com/omnithrivetech-ceo
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Coreconsulting SpA</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.coreconsulting.it/</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Coreconsulting SpA provides directional consulting and training services, generating innovation by integrating people, organizations, and technologies.</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Management Consulting</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Senior Applied AI Engineer – HR Tech</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Turin, Piedmont, Italy</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Barbara Toffolo</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>barbara.toffolo@coreconsulting.it</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/barbara-toffolo-a0b66815</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>Coreconsulting SpA's AI hiring - a perspective</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>Dear Barbara Toffolo,
+I noticed Coreconsulting SpA is recruiting a Senior Applied AI Engineer for HR Tech. This signals a strategic push to embed AI into your people and organizational consulting practice - a natural evolution for a firm focused on integrating technology with human systems.
+Here is the challenge: 75% of AI projects fail to deliver ROI according to the IBM CEO Study 2025. Full-time AI engineering hires are also expensive to scale, particularly when pilot projects remain stuck in development.
+At Omnithrive Technologies, we specialize in turning failing or stalled AI initiatives into measurable production systems within 90 days. Rather than hiring a senior engineer at $100,000 annually, we can deliver equivalent AI capabilities - custom-built for HR Tech workflows, production-ready, and integrated into your client delivery model - for approximately one-tenth of that investment.
+Our approach is different. We do not build prototypes or leave you after deployment. We embed change management and adoption support, ensuring your teams (and your clients) actually use the systems we build. We work with frameworks like LangGraph and LangChain to create agentic AI systems tailored to your specific HR Tech requirements.
+Before you commit hiring resources, I would like to invite you to a complimentary 2-Day AI Opportunity Audit. This is a no-cost, no-commitment assessment of where AI can create immediate, measurable value for Coreconsulting SpA.
+I would welcome the conversation.
+Book your audit here: cal.com/omnithrivetech-ceo
+Warm regards,
+Omnithrive Technologies
+AI Value Acceleration Studio
+admin@omnithrivetech.com
++91 97426 09264</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>Crédit Agricole Italia</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>https://www.credit-agricole.it/</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Crédit Agricole Italia is a banking and financial services company that provides retail and corporate banking solutions to customers in Italy. It is part of the Crédit Agricole Group, one of Europe's largest financial institutions.</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>Banking/Financial Services</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>AI Developer</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>Parma, Emilia-Romagna, Italy</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr"/>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>GDPR, Render</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>Simona Carini</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>Director of Events</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>simona.carini@credit-agricole.it</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/simona-carini-04665b13</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr"/>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
+          <t>Crédit Agricole Italia's AI Developer search - a cost perspective</t>
+        </is>
+      </c>
+      <c r="O71" s="3" t="inlineStr">
+        <is>
+          <t>Dear Simona Carini,
+I noticed Crédit Agricole Italia is actively hiring for an AI Developer role. Given the financial services sector's regulatory complexity - particularly GDPR compliance and infrastructure management through platforms like Render - I wanted to share a perspective that may be relevant to your decision.
+You're budgeting approximately $100,000 annually for this hire. What if you could access equivalent AI development capabilities for a fraction of that investment while eliminating hiring delays and onboarding overhead?
+Here's the reality: 88% of AI pilots never reach production (CIO Magazine), and financial institutions are particularly vulnerable to this gap. The difference between a capable developer and a results-driven AI practice is substantial - and costly when measured in failed initiatives rather than deployed value.
+Omnithrive Technologies specializes in turning stalled AI projects into measurable outcomes within 90 days. We work with banking and financial services organizations to build production-ready systems that respect regulatory frameworks like GDPR while delivering immediate ROI. Our expert AI developers operate at approximately $10,000 per project engagement - roughly one-tenth your annual hiring budget - without long-term employment commitments or infrastructure overhead.
+Rather than committing to a full-time hire for an uncertain roadmap, consider whether a structured, outcomes-focused approach might better serve Crédit Agricole Italia's immediate AI needs.
+We offer a complimentary 2-Day AI Opportunity Audit to evaluate your specific requirements and potential. No commitment, no cost.
+If this resonates, I would welcome a brief conversation.
+Book your audit here: cal.com/omnithrivetech-ceo
 Warm regards,
 [Your Name]
 Senior B2B Outreach Specialist
 Omnithrive Technologies
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>Coreconsulting SpA</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>https://www.coreconsulting.it/</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Coreconsulting SpA provides directional consulting and training services, generating innovation by integrating people, organizations, and technologies.</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>Management Consulting</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>Senior Applied AI Engineer – HR Tech</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>Turin, Piedmont, Italy</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr"/>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>Barbara Toffolo</t>
-        </is>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>Partner</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>barbara.toffolo@coreconsulting.it</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/barbara-toffolo-a0b66815</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
-      <c r="N70" s="2" t="inlineStr">
-        <is>
-          <t>Re: your Senior Applied AI Engineer – HR Tech search</t>
-        </is>
-      </c>
-      <c r="O70" s="2" t="inlineStr">
-        <is>
-          <t>Dear Barbara Toffolo,
-I noticed Coreconsulting SpA is actively recruiting a Senior Applied AI Engineer for HR Tech—a strategic move that signals your commitment to embedding AI into talent and organizational workflows.
-Here's a candid observation: 88% of AI pilots never reach production (CIO Magazine). Most organizations hire for capability but lack the operational framework to translate that into measurable value. The result? Expensive talent sitting on proof-of-concepts instead of driving real business impact.
-At Omnithrive Technologies, we've built a different model. Rather than asking your team to staff an AI capability in-house, we deliver production-ready AI systems in 90 days—custom-built for your HR Tech workflows, with built-in change management and adoption support. The economics are compelling: your $100,000 annual hire budget translates to roughly equivalent AI capabilities for approximately $10,000 through our High-Impact MVP Build and ongoing expert developer support.
-We've worked with management consulting firms and enterprise organizations across HR Tech, talent analytics, and organizational innovation. We don't build pilots. We build systems that work.
-Before you finalize your hiring search, I'd like to invite you to a complimentary 2-Day AI Opportunity Audit. We'll map your specific HR Tech priorities, identify quick wins, and show you whether an in-house hire or a production-ready AI solution makes more sense for your organization.
-No commitment. No cost.
-You can book a time directly here: cal.com/omnithrivetech-ceo
-Warm regards,
-**Omnithrive Technologies**  
-AI Value Acceleration Studio  
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>Crédit Agricole Italia</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>https://www.credit-agricole.it/</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t>Crédit Agricole Italia is a banking and financial services company that provides retail and corporate banking solutions to customers in Italy. It is part of the Crédit Agricole Group, one of Europe's largest financial institutions.</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t>Banking/Financial Services</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="inlineStr">
-        <is>
-          <t>AI Developer</t>
-        </is>
-      </c>
-      <c r="F71" s="3" t="inlineStr">
-        <is>
-          <t>Parma, Emilia-Romagna, Italy</t>
-        </is>
-      </c>
-      <c r="G71" s="3" t="inlineStr"/>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>GDPR, Render</t>
-        </is>
-      </c>
-      <c r="I71" s="3" t="inlineStr">
-        <is>
-          <t>Simona Carini</t>
-        </is>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>Director of Events</t>
-        </is>
-      </c>
-      <c r="K71" s="3" t="inlineStr">
-        <is>
-          <t>simona.carini@credit-agricole.it</t>
-        </is>
-      </c>
-      <c r="L71" s="3" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/simona-carini-04665b13</t>
-        </is>
-      </c>
-      <c r="M71" s="3" t="inlineStr"/>
-      <c r="N71" s="3" t="inlineStr">
-        <is>
-          <t>AI Developer hiring vs. building production-ready systems</t>
-        </is>
-      </c>
-      <c r="O71" s="3" t="inlineStr">
-        <is>
-          <t>Dear Simona Carini,
-I noticed Crédit Agricole Italia is actively hiring for an AI Developer role—a significant investment given the current talent market and the complexity of building compliant financial AI systems.
-Here's what caught my attention: Your team needs production-ready solutions that align with GDPR requirements and modern deployment frameworks like Render. Yet 88% of AI pilots never reach production, according to CIO Magazine. Most organizations hire developers to solve this problem, only to find themselves managing prototypes rather than revenue-generating systems.
-We've built a different model.
-Omnithrive Technologies specializes in turning stalled or failing AI initiatives into measurable profits within 90 days. Rather than adding headcount at approximately $100,000 annually, we deliver production-ready AI systems—fully integrated into your workflows, GDPR-compliant, and designed for scale—at a fraction of that cost. Our expert AI developers work on-demand at $30/hour, focusing exclusively on high-impact use cases that move the needle for financial services organizations.
-For Crédit Agricole Italia, this means: custom-built systems, built-in change management, and genuine ROI proof before scaling.
-We offer a complimentary 2-Day AI Opportunity Audit to evaluate where automation can create immediate value within your banking operations—no commitment, no cost.
-Would you be open to exploring this approach?
-Book your audit here: cal.com/omnithrivetech-ceo
-Warm regards,
-Omnithrive Technologies
-AI Value Acceleration Studio
 admin@omnithrivetech.com
-WhatsApp: +91 97426 09264</t>
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -6648,22 +6653,24 @@
       <c r="M72" s="2" t="inlineStr"/>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Re: your Machine Learning Engineer search at Cubiq Recruitment</t>
+          <t>Re: your Machine Learning Engineer search</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
           <t>Dear Jacob Stafford-Wright,
-I noticed Cubiq Recruitment is actively hiring for a Machine Learning Engineer—a critical role for building AI-driven talent solutions. Given your focus on BLOOM and machine learning capabilities, I wanted to share a perspective that may prove valuable.
-Here's the challenge: 88% of AI pilots never reach production (CIO Magazine). Most organizations hire senior ML engineers at $100,000+ annually, only to discover that isolated talent acquisition or proof-of-concept projects fail to deliver measurable business value.
-At Omnithrive Technologies, we take a different approach. Rather than hiring a full-time engineer to build from scratch, we deliver production-ready AI systems custom-built for your exact workflows—at approximately 1/10th the cost of a traditional hire. Our agentic AI solutions (leveraging LangChain, LangGraph, and CrewAI) integrate seamlessly with your existing recruitment infrastructure and are designed to measurably improve efficiency within 90 days.
-We've spent the last two years perfecting the process: no pilots, no prototypes—only systems that move into production and prove ROI immediately.
-I'd like to invite you to a complimentary 2-Day AI Opportunity Audit. We'll analyze your current recruitment workflows, identify where AI can generate tangible value, and outline a concrete implementation strategy—entirely free, no obligation.
-If this resonates, you can book directly at cal.com/omnithrivetech-ceo.
-Warm regards,
-**Omnithrive Technologies**
-AI Value Acceleration Studio
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+I noticed Cubiq Recruitment is actively hiring for a Machine Learning Engineer with BLOOM and advanced ML capabilities. Building in-house talent for AI-driven recruitment systems is critical-but it's also expensive and time-consuming.
+Here's what we've observed: 88% of AI pilots never reach production (CIO Magazine). Most organizations invest heavily in hiring specialized engineers, only to find their AI initiatives stall or fail to generate measurable returns.
+At Omnithrive Technologies, we take a different approach. Rather than hiring a full-time Machine Learning Engineer at $100,000 annually, we deliver production-ready AI systems that solve recruitment workflow challenges in 90 days or less. You get equivalent AI capabilities-custom-built for your exact processes-at approximately 1/10th the cost of a traditional hire. No prototypes, no endless pilots. Just measurable results.
+We specialize in turning stalled AI initiatives into profits. Our team works with BLOOM, LangChain, LangGraph, and modern ML frameworks to automate candidate screening, matching, and talent pipeline optimization. We've supported staffing firms in scaling their operations without scaling their headcount proportionally.
+The first step is simple: a complimentary 2-Day AI Opportunity Audit. No commitment, no cost. We'll identify where AI can drive immediate value within your recruitment operations.
+If you're open to exploring this, I'd like to book a brief conversation.
+Warm regards,
+[Your Name]
+Senior B2B Outreach Specialist
+Omnithrive Technologies
+cal.com/omnithrivetech-ceo
+admin@omnithrivetech.com</t>
         </is>
       </c>
     </row>
@@ -6753,26 +6760,22 @@
       </c>
       <c r="N73" s="3" t="inlineStr">
         <is>
-          <t>Re: Your Senior Palantir Foundry Engineer search</t>
+          <t>Re: your Senior Palantir Foundry Engineer search</t>
         </is>
       </c>
       <c r="O73" s="3" t="inlineStr">
         <is>
           <t>Dear Iryna Hudym,
-I noticed Customertimes is actively hiring for a Senior Palantir Foundry Engineer—a $100,000+ investment to build and optimize data pipelines and operational applications within Foundry.
-I wanted to share a perspective: 88% of AI and data initiatives never reach production (CIO Magazine), and most organizations struggle to move beyond pilots into scalable, revenue-generating systems.
-At Omnithrive Technologies, we specialize in turning stalled or failing AI initiatives into production-ready systems within 90 days. Our approach is particularly relevant for professional services firms like yours that build data solutions for enterprise clients.
-Rather than hiring full-time engineers, consider this: we deliver equivalent AI and automation capabilities for approximately one-tenth of that annual cost—roughly $10,000 versus $100,000. Our team builds production-ready pipelines, data transformation workflows, and operational automation using LangGraph, n8n, and enterprise LLMs. We embed change management and adoption support, so solutions don't stall.
-This means you could:
-• Accelerate client delivery without expanding headcount
-• Reduce hiring risk and overhead
-• Maintain flexibility to scale capabilities on demand
-I'd like to invite you to a complimentary 2-Day AI Opportunity Audit—no commitment, no cost. We'll assess how AI and automation can strengthen Customertimes's service offerings and client outcomes.
-Book here: cal.com/omnithrivetech-ceo
+I noticed Customertimes is actively hiring for a Senior Palantir Foundry Engineer with a $100,000 annual budget - a significant investment for pipeline configuration and operational app development at scale.
+Here's a perspective worth considering: 75% of AI and data projects fail to deliver measurable ROI, according to the IBM CEO Study 2025. The gap between what companies need (production-ready data systems) and what they get (prolonged hiring cycles, onboarding delays, pilot fatigue) is widening.
+At Omnithrive Technologies, we specialize in turning stalled or failing data initiatives into measurable value within 90 days. We've found that for organizations like yours that build data pipelines, integrate complex datasets, and support ontology design work - the traditional hiring approach often introduces timeline risk and coordination overhead.
+Our alternative: we deliver equivalent AI and automation capabilities - including pipeline orchestration, data transformation logic, and workflow optimization - at approximately 1/10th of a full-time engineer's annual cost. No lengthy recruitment cycles. No ramp-up delays. Production-ready systems that integrate directly into your existing Palantir Foundry implementations.
+Rather than pitch further, I'd like to offer something more valuable: a complimentary 2-Day AI Opportunity Audit specifically for Customertimes. No commitment required. We'll analyze your current data pipeline challenges, identify high-impact automation opportunities, and provide a concrete roadmap for value delivery.
+If this resonates, you can book directly at cal.com/omnithrivetech-ceo, or reach out to admin@omnithrivetech.com.
 Warm regards,
 Omnithrive Technologies
 AI Value Acceleration Studio
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+admin@omnithrivetech.com | +91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -6860,25 +6863,24 @@
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Functional Safety certifications + AI automation — a cost angle</t>
+          <t>Functional Safety Business Development - AI automation opportunity</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
           <t>Dear Matthieu Hoepffner,
-I noticed DEKRA Digital &amp; Product Solutions is hiring for Business Developer – Functional Safety, with a focus on machinery, industrial, and robotics customers across Europe.
-That role carries a significant investment—approximately $100,000 annually—to identify new business opportunities, understand customer objectives, and develop hunting sales strategies across your target sectors.
-Here's what caught my attention: 75% of AI projects fail to deliver ROI, according to the IBM CEO Study 2025. Most organizations either build custom solutions that never scale, or deploy generic tools that don't align with their workflows.
-Omnithrive Technologies specializes in turning stalled or failing AI initiatives into measurable profit within 90 days. We build production-ready systems—not pilots—custom-designed for your operational needs. Our agentic AI solutions (using LangChain, LangGraph, and CrewAI) can automate critical parts of the business development cycle: customer research, opportunity qualification, and even preliminary compliance assessment workflows for your machinery and robotics clients.
-The financial advantage is stark: we deliver equivalent AI capabilities for approximately one-tenth of what you'd invest in a full-time hire—meaning you could augment your Functional Safety BD efforts with intelligent automation at a fraction of the cost.
-Rather than propose a solution, I'd like to invite you to a complimentary 2-Day AI Opportunity Audit. We'll identify concrete use cases within your business development and certification workflows, with no commitment required.
-Would you be open to exploring this?
-Book here: cal.com/omnithrivetech-ceo
-Warm regards,
-[Your Name]
-Senior B2B Outreach Specialist
+I am reaching out because I noticed DEKRA Digital &amp; Product Solutions is actively recruiting for a Business Developer focused on Functional Safety across Machinery, Industrial, and Robotics sectors in Europe.
+This hire represents significant investment - approximately $100,000 annually - for lead identification, customer opportunity mapping, and contract negotiation support. However, there is a more efficient path forward.
+At Omnithrive Technologies, we specialize in deploying production-ready AI systems that automate exactly these functions: prospect identification, business opportunity analysis, customer challenge mapping, and sales strategy acceleration. The concerning reality is that 75% of AI projects fail to deliver ROI, according to the IBM CEO Study 2025. Most organizations implement pilots that never reach production. We operate differently.
+Rather than hiring another team member, consider deploying AI-powered systems that accomplish the same outcome at approximately one-tenth the cost - roughly $10,000 annually versus your $100,000 budget. These systems identify qualified prospects within your target verticals, analyze their functional safety needs, flag contract negotiation opportunities, and maintain customer relationship intelligence - all integrated into your existing workflows.
+The investment difference is substantial, and the execution timeline is considerably faster.
+I would like to invite you to our complimentary 2-Day AI Opportunity Audit. We assess your specific business development challenges and identify which processes can be automated to accelerate order intake and customer acquisition. There is no commitment and no cost.
+If this interests you, please schedule here: cal.com/omnithrivetech-ceo
+Warm regards,
 Omnithrive Technologies
-admin@omnithrivetech.com | +91 97426 09264</t>
+AI Value Acceleration Studio
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -6960,21 +6962,18 @@
       </c>
       <c r="N75" s="3" t="inlineStr">
         <is>
-          <t>Re: Your Data Scientist search — a cost-efficiency angle</t>
+          <t>A thought on Daintta's AI build capacity</t>
         </is>
       </c>
       <c r="O75" s="3" t="inlineStr">
         <is>
           <t>Dear Stephen Whiteman,
-I noticed Daintta is hiring for a Data Scientist role with a $100,000 annual budget. Given your firm's focus on moving clients from proof-of-concept through to MVP and MMP stages, I wanted to share a perspective that may be relevant.
-Most organizations in your space face a persistent challenge: 88% of AI pilots never reach production (CIO Magazine). Even when talented data scientists are on board, the gap between PoC and production-ready systems remains substantial—consuming time, budget, and stakeholder confidence.
-Here's the opportunity: Omnithrive Technologies specializes in accelerating that exact journey. We deliver production-ready AI systems custom-built for client workflows, not generic prototypes. Our agentic AI and automation capabilities span LangChain, LangGraph, AutoGen, and enterprise integrations—essentially providing equivalent AI development capacity for approximately one-tenth of what you'd invest in a full-time hire.
-For Daintta, this means two immediate benefits:
-1. **Faster client delivery**: Your team moves PoCs to production in weeks, not months, strengthening client relationships and competitive positioning.
-2. **Budget efficiency**: You're not carrying a $100K annual salary; you scale expert AI developers ($30/hour) only when projects require that capability.
-Rather than speculating further, I'd like to invite you to a complimentary 2-Day AI Opportunity Audit. We'll assess your current workflows, identify where AI acceleration would deliver the most value, and outline a production-ready strategy—with no commitment required.
-Would you be open to exploring this?
-Book here: cal.com/omnithrivetech-ceo
+I've been following Daintta's work in data science consulting, and I noticed your current search for a Data Scientist to lead client projects through proof-of-concept to MVP stages. That's a critical hire - and typically an expensive one.
+Here's what caught my attention: your team excels at translating technical insights into actionable business outcomes across complex data types and modeling approaches. What you're likely experiencing, though, is that 88% of AI pilots never reach production (CIO Magazine) - meaning the gap between PoC and truly scalable solutions remains a persistent challenge for your clients.
+At Omnithrive Technologies, we specialize in exactly that transition. We turn failing or stalled AI initiatives into production-ready systems within 90 days - delivering measurable ROI, not prototypes. Our agentic AI expertise (LangChain, LangGraph, AutoGen) combined with workflow automation means we can deliver equivalent AI capabilities for approximately one-tenth of what a full-time Data Scientist hire costs you annually.
+Rather than absorbing that $100,000+ headcount expense, consider: what if your clients could access production-grade AI acceleration on-demand, scaled precisely to project needs?
+I'd like to invite you to a complimentary 2-Day AI Opportunity Audit. We'll assess where your current pipeline experiences friction between PoC and MVP, and identify immediate high-impact opportunities. No commitment required.
+You can book directly at cal.com/omnithrivetech-ceo, or reach out to admin@omnithrivetech.com.
 Warm regards,
 [Your Name]
 Senior B2B Outreach Specialist
@@ -7052,95 +7051,14 @@
       <c r="O76" s="2" t="inlineStr">
         <is>
           <t>Dear Yimin Zeng,
-I noticed Dassault Systèmes is hiring for a Generative AI Engineer focused on talent matching across your organization. Given your department's mandate to embed AI across life sciences, industrial production, and HR systems, I wanted to share a perspective that may be relevant.
-You're budgeting approximately $100,000 annually for this specialized role. However, 88% of AI pilots never reach production (CIO Magazine)—meaning traditional hiring often yields capability without proven business impact.
-Omnithrive Technologies specializes in production-ready AI systems that deliver measurable ROI within 90 days. Rather than hiring a full-time engineer, you could access equivalent AI development capabilities—including expertise in LLMs, agentic workflows, and enterprise automation—for approximately one-tenth of that investment. This allows you to validate AI impact on your talent matching initiative before scaling.
-Our approach differs fundamentally: we build systems that move directly from discovery to production, with built-in change management and adoption support. We don't hand off prototypes or pilots.
-For your specific use case—automating and optimizing talent matching across your global operations—I'd recommend a complimentary 2-Day AI Opportunity Audit. We'll map your workflows, identify quick-win automation points, and provide a clear ROI projection with zero commitment.
-If this resonates, please book a time here: cal.com/omnithrivetech-ceo
-Alternatively, feel free to reach out directly at admin@omnithrivetech.com or via WhatsApp at +91 97426 09264.
-Warm regards,
-[Your Name]
-Senior B2B Outreach Specialist
-Omnithrive Technologies
-AI Value Acceleration Studio</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>https://www.databricks.com/</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t>Databricks is a leading data and AI platform for enterprises, providing a unified platform for data, analytics, and AI.</t>
-        </is>
-      </c>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t>AI/ML, SaaS</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Distributed Data Systems</t>
-        </is>
-      </c>
-      <c r="F77" s="3" t="inlineStr">
-        <is>
-          <t>San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="G77" s="3" t="inlineStr"/>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>AI Agent, AI Agents, Artificial Intelligence, AWS, Azure, BI, Business Intelligence, Data Engineer, Data Engineering, Data Pipeline, Data Science, Data Warehouse, Databricks, ETL, GCP, Gen AI, GenAI, SQL</t>
-        </is>
-      </c>
-      <c r="I77" s="3" t="inlineStr">
-        <is>
-          <t>Sumaer Bahl</t>
-        </is>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>Head of Growth</t>
-        </is>
-      </c>
-      <c r="K77" s="3" t="inlineStr">
-        <is>
-          <t>sumaer.bahl@databricks.com</t>
-        </is>
-      </c>
-      <c r="L77" s="3" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/sumaer-bahl-36064537</t>
-        </is>
-      </c>
-      <c r="M77" s="3" t="inlineStr"/>
-      <c r="N77" s="3" t="inlineStr">
-        <is>
-          <t>Re: your Senior Software Engineer - Distributed Data Systems search</t>
-        </is>
-      </c>
-      <c r="O77" s="3" t="inlineStr">
-        <is>
-          <t>Dear Sumaer Bahl,
-I noticed Databricks is actively hiring for Senior Software Engineer roles focused on distributed data systems and AI agents. Building production-grade AI capabilities—particularly those spanning data pipelines, ETL workflows, and GenAI integration across AWS, Azure, and GCP—requires specialized expertise that's both expensive and time-consuming to source internally.
-Here's the reality: 88% of AI pilots never reach production (CIO Magazine). The gap between hiring and deployment often costs enterprises months and significant capital.
-At Omnithrive Technologies, we specialize in accelerating AI initiatives into measurable value within 90 days. Rather than waiting 3–6 months to hire and onboard a Senior Software Engineer at $100,000 annually, organizations partner with us to deliver production-ready AI systems—custom-built agentic workflows, data pipeline automation, and GenAI implementations—for approximately one-tenth that cost.
-We've built distributed data systems, deployed AI agents across enterprise workflows, and scaled data engineering solutions using the exact stack your team relies on: LangGraph, LangChain, AutoGen, n8n, and leading LLMs.
-Unlike typical consultancies, we guarantee measurable results. No pilots. No prototypes. Just production-ready systems with built-in adoption and change management.
-I'd like to explore whether an AI-accelerated approach could complement your hiring strategy. We offer a complimentary 2-Day AI Opportunity Audit—no commitment, no cost—to identify high-impact opportunities specific to your distributed systems and data pipeline needs.
+I noticed Dassault Systèmes is actively recruiting for a Generative AI Engineer to advance your talent matching and broader AI initiatives across life sciences, manufacturing, and HR operations. This signals ambitious expansion-and a real challenge.
+Here's what we observe: 88% of AI pilots never reach production (CIO Magazine). Most enterprises invest heavily in specialized hires, only to find their AI projects stall or fail to deliver measurable ROI. Your $100,000 annual budget for this role is substantial, yet typical.
+At Omnithrive Technologies, we deliver production-ready AI systems-not pilots or prototypes. We've built expertise in agentic AI frameworks (LangChain, LangGraph, AutoGen), NVIDIA-optimized workflows, and scalable automation (n8n, Zapier). More importantly, we guarantee measurable results within 90 days or adjust our fees.
+The mathematics are compelling: equivalent AI capabilities through our 2-3 week High-Impact MVP builds cost approximately one-tenth of a full-time hire's annual salary. You invest $10,000 instead of $100,000, gain production-ready systems, and retain flexibility to scale or pivot as business needs evolve.
+Rather than commit to a traditional hire without proof of ROI, we recommend exploring a different path first.
+We offer a complimentary 2-Day AI Opportunity Audit-no commitment, no cost. We'll analyze your current AI initiatives, identify high-impact opportunities aligned with your product development and HR operations, and propose a concrete value pathway.
 Would you be open to a brief conversation?
-Book here: cal.com/omnithrivetech-ceo
+Book your audit here: cal.com/omnithrivetech-ceo
 Warm regards,
 Omnithrive Technologies
 AI Value Acceleration Studio
@@ -7149,6 +7067,87 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>https://www.databricks.com/</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Databricks is a leading data and AI platform for enterprises, providing a unified platform for data, analytics, and AI.</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>AI/ML, SaaS</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Distributed Data Systems</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr"/>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>AI Agent, AI Agents, Artificial Intelligence, AWS, Azure, BI, Business Intelligence, Data Engineer, Data Engineering, Data Pipeline, Data Science, Data Warehouse, Databricks, ETL, GCP, Gen AI, GenAI, SQL</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>Sumaer Bahl</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>Head of Growth</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>sumaer.bahl@databricks.com</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sumaer-bahl-36064537</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr"/>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
+          <t>Your Senior Software Engineer hire - an alternative approach</t>
+        </is>
+      </c>
+      <c r="O77" s="3" t="inlineStr">
+        <is>
+          <t>Dear Sumaer Bahl,
+I noticed Databricks is actively hiring for a Senior Software Engineer in Distributed Data Systems - a critical role for scaling your AI Agent and data pipeline capabilities across AWS, Azure, and GCP environments.
+The challenge is familiar: top distributed systems talent commands $100,000+ annually, yet 88% of AI pilots never reach production (CIO Magazine). Even exceptional hires require months to integrate into your architecture and deliver measurable impact.
+At Omnithrive Technologies, we work differently. We deliver production-ready AI systems - built on the same tech stack your engineers rely on (LangChain, LangGraph, AutoGen, CrewAI) - in 2-3 weeks, not months. For approximately 1/10th of what you would invest in a full-time senior engineer, we can architect and deploy high-impact AI solutions tailored to your specific data pipelines and ETL workflows.
+We do not build prototypes or pilots. Our approach is ROI-first: measurable business value within 90 days, or no fee. We handle deployment, adoption, and ongoing optimization - not a hand-off at launch.
+Rather than explaining further, I would like to invite you to a complimentary 2-Day AI Opportunity Audit. No commitment, no cost. Our team will analyze your current data and AI initiatives, identify high-leverage opportunities, and present a concrete path to production value.
+I believe this approach deserves a conversation.
+You can reserve time here: cal.com/omnithrivetech-ceo
+Warm regards,
+Omnithrive Technologies
+AI Value Acceleration Studio
+admin@omnithrivetech.com
+WhatsApp: +91 97426 09264</t>
+        </is>
+      </c>
+    </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
@@ -7213,22 +7212,24 @@
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Datadog's APM AI troubleshooting — a build vs. hire question</t>
+          <t>Re: your Senior AI Engineer - APM Features search</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
           <t>Dear Akshay Sareen,
-I noticed Datadog is actively recruiting a Senior AI Engineer for your APM Features team. Given your focus on transforming noisy telemetry data into actionable insights through intelligent troubleshooting experiences, I wanted to share a perspective that may be worth considering.
-Building production-grade AI agents for distributed system observability is complex. Most organizations discover this the hard way: 88% of AI pilots never reach production (CIO Magazine). Your APM team would need someone exceptional—and at $100,000 annually, you're making a significant long-term commitment.
-Here's what we've learned: Omnithrive delivers equivalent AI capabilities—agents trained on your observability stack (OpenAI, AWS, Azure, Kubernetes)—for approximately 1/10th of that investment. We specialize in production-ready AI systems, not prototypes. Within 90 days, your team could have a functioning AI agent that transforms raw telemetry into clear, actionable conclusions—without the hiring cycle or cultural onboarding overhead.
-The trade-off is straightforward: hire for permanent capacity and institutional knowledge, or accelerate immediate value with expert AI developers ($30/hour) who specialize in LangChain, LangGraph, and agentic AI systems.
-Rather than make assumptions about your exact needs, we'd like to invite you to a complimentary 2-Day AI Opportunity Audit. No commitment. We'll map your specific observability challenges and show you what production-ready acceleration could look like for your APM roadmap.
-If this resonates, you can book directly here: cal.com/omnithrivetech-ceo
-Warm regards,
+I noticed Datadog is hiring for a Senior AI Engineer to build intelligent troubleshooting experiences that transform noisy telemetry data into actionable insights for distributed systems. That's precisely the kind of complex AI work where most organizations struggle.
+Here's the challenge: 75% of AI projects fail to deliver ROI, according to IBM's 2025 CEO Study. And when it comes to building production-ready AI systems that handle real observability data at scale - the kind your APM Features team needs - the cost is substantial. Your posted budget reflects this reality: roughly $100,000 annually for one specialized AI engineer.
+What if you could access equivalent AI capabilities - agents, LLM orchestration, and deployment expertise across OpenAI, Claude, and other models - for approximately one-tenth of that investment? That's what we do at Omnithrive Technologies. We're an AI Value Acceleration Studio that builds production-ready systems, not pilots or prototypes. We've worked extensively with agentic AI frameworks like LangChain and LangGraph to solve exactly this type of problem: parsing complex data streams and generating clear, actionable conclusions.
+Rather than a lengthy hiring process and onboarding cycle, we deliver a working MVP in 2-3 weeks. We don't disappear after deployment - built-in change management and adoption support comes standard.
+I'd like to propose a complimentary 2-Day AI Opportunity Audit. No commitment, no cost. We'll analyze your specific APM use case and show you exactly what's achievable, on your timeline and budget.
+You can book directly here: cal.com/omnithrivetech-ceo
+Warm regards,
+[Your Name]
+Senior B2B Outreach Specialist
 Omnithrive Technologies
-AI Value Acceleration Studio
-admin@omnithrivetech.com | +91 97426 09264</t>
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -7326,19 +7327,20 @@
       </c>
       <c r="N79" s="3" t="inlineStr">
         <is>
-          <t>Re: Your Senior Research Engineer search at Decagon</t>
+          <t>A thought on Decagon's LLM production challenge</t>
         </is>
       </c>
       <c r="O79" s="3" t="inlineStr">
         <is>
           <t>Dear Evan Cassidy,
-I noticed Decagon is hiring for a Senior Research Engineer to lead improvements in instruction following, retrieval, and long-horizon task completion for production LLMs. That's a critical hire—and an expensive one at $100,000 annually.
-Here's what caught my attention: 88% of AI pilots never reach production (CIO Magazine). Most organizations struggle not with research ideas, but with operationalizing them at scale. Your team is solving that problem directly, which means you need engineers who can move from concept to deployed systems quickly.
-At Omnithrive Technologies, we specialize in exactly this—taking AI capabilities from research to production-ready systems within 90 days. We've built production deployments using the same modern ML tooling and evaluation frameworks your role demands: A/B testing, agent architectures, and QA pipelines integrated into live environments.
-Here's the economics: instead of a full-time Senior Research Engineer at $100,000 annually, you could access equivalent AI engineering expertise through our on-demand developer network at approximately $10,000 for targeted production work. That's 1/10th the cost, with no hiring overhead.
-We're not suggesting this replaces your hire—but it could accelerate your research-to-production pipeline immediately while you build your permanent team.
-I'd like to show you what's possible. Our complimentary 2-Day AI Opportunity Audit is designed specifically for organizations like yours to identify quick wins in your production AI workflows.
-Would you be open to exploring this? Book a time at cal.com/omnithrivetech-ceo
+I noticed Decagon is hiring for a Senior Research Engineer to lead improvements in core conversational capabilities - instruction following, retrieval, memory, and long-horizon task completion in production environments.
+That's demanding work. And expensive work.
+Here's the reality: 88% of AI pilots never reach production (CIO Magazine). The gap between research concepts and deployed systems is where most organizations lose momentum and budget. A full-time senior engineer at your level costs approximately $100,000 annually, but the real expense is the 6-12 month cycle to move from concept to production-ready deployment.
+At Omnithrive Technologies, we specialize in doing exactly what your job description outlines - but we compress that timeline to 90 days and deliver production-ready systems, not prototypes. Our AI development team works in your exact stack: building agentic systems, optimizing LLM pipelines, and integrating new models into production with measurable quality improvements. You'd access equivalent AI engineering capabilities for roughly one-tenth of what a full-time hire costs.
+More importantly, we embed change management and adoption into every project. We don't hand off and disappear - we scale only when value is proven.
+Rather than committing to a lengthy hiring process with uncertain delivery timelines, consider a different approach: a complimentary 2-Day AI Opportunity Audit. We'll assess your current production challenges in conversational AI and outline a concrete path to measurable improvements.
+No commitment. No cost.
+Book here: cal.com/omnithrivetech-ceo
 Warm regards,
 Omnithrive Technologies
 AI Value Acceleration Studio
@@ -7428,22 +7430,27 @@
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Re: your Data Scientist search at Deel</t>
+          <t>Re: your Data Scientist search</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
           <t>Dear Colm McGoldrick,
-I noticed Deel is hiring for a Data Scientist focused on building production-ready data pipelines and feature engineering for salary insights. That's precisely the kind of high-impact work that separates successful AI teams from those stuck in pilot purgatory.
-Here's the challenge: 88% of AI pilots never reach production (CIO Magazine). Most organizations hire full-time data scientists at $100,000+ annually, only to see their projects stall in feature engineering or data cleaning phases. The friction isn't always talent—it's infrastructure, workflow integration, and deployment velocity.
-At Omnithrive Technologies, we build production-ready AI systems specifically designed to accelerate data science outcomes. We've worked with FinTech and HR platforms to design and deploy end-to-end data pipelines—including data cleaning, feature extraction, and ML model serving—in weeks, not quarters. Our cost model runs approximately one-tenth of what a full-time hire would command, and we guarantee measurable results within 90 days.
-Rather than a lengthy hiring cycle, consider this: what if you could validate your data science roadmap in 2 days—at no cost—before committing resources?
-Our complimentary AI Opportunity Audit would examine your current data pipeline architecture, identify high-impact ML opportunities aligned with your salary insights project, and recommend a concrete path to production-ready delivery.
-If this resonates, I'd welcome a brief conversation. You can book directly here: cal.com/omnithrivetech-ceo
-Warm regards,
-**Omnithrive Technologies**
+I noticed Deel is hiring for a Data Scientist to build production-grade data pipelines and feature engineering systems for salary insights. That's exactly the kind of high-impact work where organizations often face a critical choice.
+Here is the reality: 88% of AI pilots never reach production, according to CIO Magazine. Most teams struggle not with talent, but with execution speed and embedding AI into live systems that serve customers.
+Omnithrive Technologies specializes in turning stalled AI initiatives into measurable profits within 90 days. Rather than hiring a full-time Data Scientist at $100,000 annually, enterprises like yours are now accessing equivalent capabilities through our production-ready AI builds - at approximately one-tenth the cost.
+Your job description emphasizes end-to-end data pipelines, feature engineering, and production implementation. We do exactly that. We build custom data infrastructure, statistical models, and ML systems designed to integrate directly into your product, not sit in notebooks.
+Our approach is straightforward:
+- No lengthy consulting engagements
+- Production-ready systems in 2-3 weeks
+- Change management and adoption built in
+- You only scale when value is proven
+We would like to invest two days understanding Deel's specific data challenges, pain points, and opportunities - completely free, no commitment required. This audit will clarify whether an AI acceleration approach makes sense for your immediate priorities.
+If this resonates, please book a time at cal.com/omnithrivetech-ceo or reach out at admin@omnithrivetech.com.
+Warm regards,
+Omnithrive Technologies
 AI Value Acceleration Studio
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+admin@omnithrivetech.com | +91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -7517,17 +7524,17 @@
       <c r="O81" s="3" t="inlineStr">
         <is>
           <t>Dear Niels Londoz,
-I noticed Deloitte Digital is hiring for an Experienced Data Scientist to strengthen your Customer Analytics team across Milan and Rome. Given the complexity of building production-grade AI systems for advisory clients, I wanted to share a perspective that might prove valuable.
-You're budgeting approximately $100,000 annually for this role. Here's what we've observed: 88% of AI pilots never reach production (CIO Magazine)—which means most organizations invest heavily in capability-building only to stall at deployment. The challenge isn't talent scarcity; it's converting promising AI initiatives into measurable client value within realistic timelines.
-Omnithrive Technologies specializes in exactly this. We turn stalled or failing AI initiatives into production-ready systems delivering measurable ROI within 90 days. Rather than hiring full-time data science capacity, we deliver equivalent AI engineering capability—custom-built agentic systems, AWS-native workflows, and enterprise automation—at approximately 1/10th of a full-time hire's cost. Our tech stack includes LangChain, LangGraph, and AWS-optimized infrastructure.
-For Deloitte's advisory clients facing AI implementation bottlenecks, this translates to faster client outcomes and stronger competitive positioning.
-Rather than committing to another search cycle, I'd like to invite you to a complimentary 2-Day AI Opportunity Audit. No obligation, no cost—simply an honest assessment of where AI value is being left on the table in your current operations.
-You can book directly at cal.com/omnithrivetech-ceo.
+I noticed Deloitte Digital is actively recruiting for an Experienced Data Scientist to strengthen your Customer Analytics team across Milan and Rome. Given the specialized skill set required - particularly around AWS infrastructure and JavaScript integration for analytics workflows - I wanted to share a perspective that may be relevant to your hiring strategy.
+According to IBM's 2025 CEO Study, 75% of AI projects fail to deliver measurable ROI. Many organizations discover that hiring senior data scientists alone doesn't solve the underlying problem: most AI initiatives never move from pilot to production-grade systems that drive actual business value.
+At Omnithrive Technologies, we specialize in exactly this gap. Rather than lengthy recruitment cycles for $100,000+ annual hires, we deliver production-ready AI systems tailored to your specific workflows - customer analytics, tax optimization modeling, advisory automation - in 90 days or less. Our approach costs approximately one-tenth of a full-time senior hire while eliminating the risk of another stalled pilot.
+We've worked with professional services firms facing similar challenges: turning fragmented data streams into actionable intelligence, automating repetitive analytical work, and ensuring adoption across distributed teams.
+Before making your final hiring decision, I'd like to invite you to a complimentary 2-Day AI Opportunity Audit. No commitment required. We'll identify where AI can genuinely move the needle for your Customer Analytics practice - and whether that's a hire, a custom build, or something else entirely.
+You can schedule directly at cal.com/omnithrivetech-ceo.
 Warm regards,
 [Your Name]
 Senior B2B Outreach Specialist
 Omnithrive Technologies
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+admin@omnithrivetech.com | +91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -7595,23 +7602,23 @@
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>A thought on Deploja's AI Engineer search</t>
+          <t>A thought on Deploja's AI Engineer hiring</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
           <t>Dear Simon Kanaan,
-I noticed Deploja is actively recruiting an AI Engineer for QA and R-based project work. That tells me you're scaling delivery capacity—which is logical given market demand.
-Here's the challenge: 88% of AI pilots never reach production (CIO Magazine). Most teams spend months building proof-of-concepts that stall before generating real value. Your new hire will likely face pressure to deliver production-ready systems quickly, not just prototypes.
-At Omnithrive Technologies, we specialize in turning stalled AI initiatives into measurable profits within 90 days. We build production-ready agentic systems using LangChain, LangGraph, and AutoGen—exactly the tooling modern AI projects require.
-Here's what matters for your hiring decision: You're budgeting approximately $100,000 annually for an AI Engineer. Omnithrive delivers equivalent AI capabilities—custom-built for your clients' workflows, fully adopted and scaled—for roughly one-tenth of that cost. More importantly, we guarantee measurable ROI or we don't scale.
-Rather than hire and train, consider running a free 2-Day AI Opportunity Audit with us first. We'll identify high-impact AI initiatives across your client engagements and map a clear path to production. No commitment. No cost. You'll have concrete data on where AI creates the most immediate value for Deploja's consulting practice.
-If this resonates, I'd welcome a brief conversation.
-Book your audit here: cal.com/omnithrivetech-ceo
-Warm regards,
-Omnithrive Technologies
-AI Value Acceleration Studio
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+I noticed Deploja is actively recruiting an AI Engineer with QA and R expertise for your consulting practice. This tells me you're scaling delivery capacity for client projects-which is the right move in a market hungry for applied AI work.
+Here is what we're observing: 75% of AI projects fail to deliver ROI, according to the IBM CEO Study 2025. Most often, this happens because organizations either hire generalist consultants who lack production-ready rigor, or they build pilots that never reach deployment.
+Omnithrive Technologies works differently. We are an AI Value Acceleration Studio that turns failing or stalled AI initiatives into measurable profits within 90 days. We build production-ready systems-not demos or prototypes-custom-fitted to each client's workflows, with built-in change management to ensure adoption actually happens.
+Here is the commercial reality: your $100,000 annual budget for one AI Engineer hire gets you capacity. With Omnithrive, that same budget covers roughly ten times the equivalent AI capability-deployed, validated, and scaling within weeks, not months.
+For Deploja specifically, this means you can offer clients faster time-to-value, reduce your own staffing risk, and free your team to focus on higher-margin consulting work rather than commodity AI builds.
+Rather than pitch further, I would like to invite you to our complimentary 2-Day AI Opportunity Audit. No commitment. No cost. We will map where your clients-or your internal initiatives-can unlock measurable AI value fastest.
+You can book directly at cal.com/omnithrivetech-ceo.
+Warm regards,
+[Your Name]
+Senior B2B Outreach Specialist
+Omnithrive Technologies</t>
         </is>
       </c>
     </row>
@@ -7663,22 +7670,24 @@
       </c>
       <c r="N83" s="3" t="inlineStr">
         <is>
-          <t>Re: your Engineer I search — a cost perspective</t>
+          <t>Deutsche Windtechnik's Engineer I search - an alternative perspective</t>
         </is>
       </c>
       <c r="O83" s="3" t="inlineStr">
         <is>
           <t>Dear Deutsche Windtechnik Team,
-I noticed you are recruiting for an Engineer I role focused on AI/ML capabilities, with an annual budget of approximately $100,000. Before you commit to a full-time hire, I wanted to share a relevant observation.
-Deutsche Windtechnik's maintenance and service operations for wind turbine generators generate vast operational data—sensor readings, service logs, failure patterns. Yet 75% of AI projects fail to deliver ROI (IBM CEO Study, 2025), often because organizations build pilots without production readiness or clear adoption pathways.
-At Omnithrive Technologies, we specialize in turning stalled AI initiatives into measurable profit within 90 days. Rather than hiring an engineer to build from scratch, you could deploy production-ready AI systems—custom-built for your WTG diagnostic and predictive maintenance workflows—for approximately one-tenth of your Engineer I budget. This approach eliminates the hiring timeline, onboarding friction, and pilot-to-production gap that derail most AI efforts.
-Our model is simple: we audit your highest-impact opportunities, build a high-impact MVP in 2–3 weeks, and scale only when value is proven. We handle adoption and change management ourselves—we do not disappear after deployment.
-Rather than decide now, I invite you to explore this with zero risk. We offer a complimentary 2-Day AI Opportunity Audit tailored to your turbine service operations. No commitment required.
-If this interests you, please book a time here: cal.com/omnithrivetech-ceo
-Warm regards,
-**Omnithrive Technologies**
+I noticed your current search for an Engineer I with AI/ML expertise. Given the complexity of optimizing wind turbine generator maintenance and predictive diagnostics, I wanted to share a perspective that may be worth considering.
+You're budgeting approximately $100,000 annually for this role. What if you could access equivalent AI capabilities - custom-built for your specific WTG maintenance workflows - for roughly one-tenth of that investment?
+Here is the challenge: 75% of AI projects fail to deliver ROI, according to the IBM CEO Study 2025. Most organizations hire engineers to build AI systems, only to find those systems never move beyond pilots or prototypes. For renewable energy providers like Deutsche Windtechnik, this delay costs real money in unplanned downtime and suboptimal maintenance scheduling.
+Omnithrive Technologies specializes in turning stalled AI initiatives into production-ready systems within 90 days. Rather than hiring and onboarding an engineer, we build high-impact AI solutions that integrate directly into your existing maintenance operations - whether that's predictive failure detection, automated service routing, or generator performance optimization.
+We begin with a complimentary 2-Day AI Opportunity Audit. No commitment. No cost. We assess your current workflows, identify where AI can deliver measurable value, and present a concrete production roadmap.
+If this resonates, I invite you to book a brief conversation:
+cal.com/omnithrivetech-ceo
+Warm regards,
+Omnithrive Technologies
 AI Value Acceleration Studio
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -7778,17 +7787,15 @@
       <c r="O84" s="2" t="inlineStr">
         <is>
           <t>Dear Telma Barbosa,
-I noticed Devoteam is hiring for your 24x7 Data &amp; AI Factory team—specifically seeking expertise in data pipeline design, DBT, SQL, and data observability solutions. That's a significant investment: approximately $100,000 annually for a single engineer.
-Here's what caught my attention: 88% of AI pilots never reach production (CIO Magazine). Yet your clients demand production-ready solutions, not experimental frameworks. Building and maintaining robust data pipelines, observability systems, and ML models requires both speed and reliability—precisely where most organizations stumble.
-At Omnithrive Technologies, we deliver equivalent AI and data engineering capabilities for roughly one-tenth of a full-time hire's cost. Instead of a $100K annual commitment for one developer, you could access our team of expert AI engineers—proficient in Python, cloud platforms like AWS and Google Cloud, and production-grade data architecture—at $30 per hour, only when you need them.
-We don't build pilots. We build production-ready systems that drive measurable ROI within 90 days. Our approach includes built-in change management and adoption support, ensuring your data initiatives actually deliver business value.
-Rather than extending your hiring timeline, consider whether a complementary strategy makes sense: let us conduct a complimentary 2-Day AI Opportunity Audit of your current data and AI operations. No obligation, no cost. We'll identify quick wins and scalable improvements for your 24x7 Factory.
-If this resonates, I'd welcome a brief conversation.
-Book your audit here: cal.com/omnithrivetech-ceo
-Warm regards,
-[Your Name]
-Senior B2B Outreach Specialist
+I noticed Devoteam is hiring for your 24x7 Data &amp; AI Factory team - specifically seeking expertise in data pipeline design, DBT, SQL, and data observability solutions across AWS and Databricks environments.
+Here is what caught my attention: you are budgeting approximately $100,000 annually for a mid-level data engineer to help build and maintain these systems. That same investment could fund a production-ready AI solution customized to your exact data-ops workflows - delivering measurable value within 90 days, at roughly one-tenth the cost of a full-time hire.
+The challenge is real. 88% of AI pilots never reach production (CIO Magazine), which means most organizations struggle to move from experimentation to operational impact. At Omnithrive Technologies, we focus exclusively on the opposite: production-ready systems that integrate directly into your data pipelines and observability frameworks - no prototypes, no extended pilots.
+We specialize in building agentic AI systems using LangChain, LangGraph, and AutoGen that automate repetitive data operations, enhance model validation, and accelerate insights generation. Our approach includes built-in change management, ensuring your teams adopt and scale what we build.
+Rather than commit resources to another hire cycle, consider a free 2-Day AI Opportunity Audit. We will analyze your current data-ops bottlenecks, identify high-impact automation opportunities, and present a concrete value case with zero obligation.
+If this resonates, I would welcome a brief conversation. You can book directly at cal.com/omnithrivetech-ceo, or reply with your availability.
+Warm regards,
 Omnithrive Technologies
+AI Value Acceleration Studio
 admin@omnithrivetech.com
 +91 97426 09264</t>
         </is>
@@ -7842,21 +7849,21 @@
       <c r="M85" s="3" t="inlineStr"/>
       <c r="N85" s="3" t="inlineStr">
         <is>
-          <t>Dialog's Full-Stack Engineer search — an AI alternative</t>
+          <t>Dialog's full-stack hiring challenge - a cost perspective</t>
         </is>
       </c>
       <c r="O85" s="3" t="inlineStr">
         <is>
           <t>Dear Dialog Team,
-I noticed you're hiring for a Full-Stack Engineer role (French speaking required) with an annual budget of approximately $100,000. Before you commit to that investment, I wanted to share a perspective that may save Dialog significant resources.
-Dialog operates in telecommunications — an industry where process automation, customer service optimization, and real-time data processing directly impact margins. Full-stack engineers are essential, but they're expensive, take weeks to onboard, and often focus on maintenance rather than revenue-generating initiatives.
-Here's the challenge: 75% of AI projects fail to deliver ROI (IBM CEO Study, 2025). Most organizations hire for capability without clarity on where AI actually creates value.
-Omnithrive Technologies specializes in turning stalled or failing AI initiatives into measurable profits within 90 days. We build production-ready AI systems — not pilots — custom-built for your workflows. For roughly 1/10th the cost of your full-time hire ($10,000 vs. $100,000), we can deliver agentic automation, workflow optimization, and integration capabilities tailored to Dialog's operations.
-Our approach includes built-in change management and adoption support, meaning you get both the system *and* the expertise to scale it.
-Rather than discuss this further via email, I'd like to invite Dialog to a complimentary 2-Day AI Opportunity Audit. No commitment. No cost. We'll identify where AI can create immediate, measurable impact for your business.
-You can book here: cal.com/omnithrivetech-ceo
-Warm regards,
-**Omnithrive Technologies**
+I noticed you are recruiting for a Full-Stack Engineer internship role. Given the complexity of modern telecom infrastructure - API development, system integration, and Go-based backend work - this hire reflects a critical gap in your technical capacity.
+Here is the reality: a full-time engineer at your budget level ($100,000 annually) takes months to integrate into your workflows, and represents significant opportunity cost during onboarding. Yet 75% of AI projects fail to deliver ROI (IBM CEO Study, 2025), often because organizations lack the right technical execution model.
+Omnithrive Technologies exists to solve this exact problem. We are an AI Value Acceleration Studio that turns stalled technical initiatives into production-ready systems within 90 days. Rather than hiring another full-time engineer, we can provision expert AI developers with specialized expertise in Go, API automation, and system integration at $30 per hour - approximately one-tenth of what a traditional hire costs your organization.
+For telecom operations like Dialog, this translates to measurable value: process automation, data pipeline optimization, and intelligent workflow systems - all delivered without the overhead of traditional hiring.
+We do not offer pilots or prototypes. Every engagement begins with a complimentary two-day AI Opportunity Audit, during which our team analyzes your current technical workflows, identifies high-impact automation opportunities, and provides a clear ROI roadmap.
+If you would like to explore whether this approach fits Dialog's current priorities, I would welcome a brief conversation.
+Book your free AI Opportunity Audit at cal.com/omnithrivetech-ceo.
+Warm regards,
+Omnithrive Technologies
 AI Value Acceleration Studio
 admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
         </is>
@@ -7922,19 +7929,19 @@
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Re: Your Software Engineer search</t>
+          <t>On AI talent and Digital Turbine's growth platform</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
           <t>Dear Stefan Lettis,
-I noticed Digital Turbine is hiring for a Software Engineer with AI/ML expertise to help intelligently connect advertisers, publishers, and carriers across the mobile ecosystem. That's a critical capability—yet 88% of AI pilots never reach production, according to CIO Magazine.
-Here's what caught my attention: your team is building meaningful advertising experiences that require sophisticated AI to match consumers with relevant content across devices. That demands robust machine learning infrastructure, real-time decisioning, and seamless integration with your existing platform.
-The challenge is familiar. Most organizations either struggle to hire talented AI engineers (this role likely commands $100,000+ annually), or they invest heavily in AI projects that stall before delivering measurable ROI.
-At Omnithrive Technologies, we've built a different approach. We're an AI Value Acceleration Studio that turns stalled initiatives into production-ready systems within 90 days—delivering equivalent AI capabilities for approximately 1/10th of what you'd spend on a full-time hire. Our developers specialize in agentic AI frameworks (LangChain, LangGraph, AutoGen) and automation platforms (n8n, Zapier, Make) that scale intelligently with your growth platform.
-Rather than another pilot, we focus on outcomes: measurable ROI, built-in adoption, and systems ready for production from day one.
-I'd like to invite you to a complimentary 2-Day AI Opportunity Audit—no commitment required. We'll assess where AI can unlock the most value for Digital Turbine's growth platform.
-You can schedule directly here: cal.com/omnithrivetech-ceo
+I noticed Digital Turbine is hiring for a Software Engineer with AI/ML expertise - a critical role given your focus on intelligently connecting advertisers, publishers, and users across the mobile ecosystem.
+Here's a thought: 88% of AI pilots never reach production (CIO Magazine). The challenge isn't finding talented engineers - it's translating their work into measurable business impact at scale.
+Your $100,000 annual budget for this hire is substantial, but consider this alternative. At Omnithrive Technologies, we deliver production-ready AI systems custom-built for your workflows - including the intelligent ad optimization and user targeting capabilities that power your growth platform - for approximately 1/10th of that investment. No lengthy hiring cycles. No onboarding friction. No risk of another pilot that stalls.
+We specialize in turning stalled or failing AI initiatives into measurable profits within 90 days. Rather than adding headcount, we provide expert AI developers working within your existing tech stack (LangChain, LangGraph, AutoGen, CrewAI) to solve your most pressing growth problems immediately.
+Before you move forward with hiring, it's worth exploring whether an AI-accelerated approach could deliver faster, more certain returns on your growth initiatives.
+I'd like to invite you to a complimentary 2-Day AI Opportunity Audit - no commitment, no cost. We'll assess your current AI gaps and show you exactly what production-ready capabilities could look like within 90 days.
+You can book directly here: cal.com/omnithrivetech-ceo
 Warm regards,
 Omnithrive Technologies
 AI Value Acceleration Studio
@@ -8022,23 +8029,25 @@
       </c>
       <c r="N87" s="3" t="inlineStr">
         <is>
-          <t>Re: your Artificial Intelligence Engineer search</t>
+          <t>Digital Waffle's AI hiring - a perspective</t>
         </is>
       </c>
       <c r="O87" s="3" t="inlineStr">
         <is>
           <t>Dear Andrew Ward,
-I noticed Digital Waffle is hiring for a Senior AI Engineer to design, build, and deploy NLP and LLM-based solutions—particularly around fine-tuning foundation models, building evaluation frameworks, and monitoring production systems for performance and reliability.
-That's precisely the work we do at Omnithrive Technologies, and I wanted to share a perspective that might be valuable.
-The challenge with hiring for these roles is clear: you're investing $100,000 annually for expertise in foundation model adaptation, prompt testing infrastructure, and production model optimization. Yet 88% of AI pilots never reach production (CIO Magazine)—which means even excellent engineers often lack the operational framework to move from prototype to measurable value quickly.
-Here's an alternative worth considering: Omnithrive delivers equivalent AI capabilities for approximately one-tenth of that cost. We specialize in taking complex NLP and LLM requirements—exactly like yours—and translating them into production-ready systems within 90 days, with built-in monitoring, evaluation frameworks, and change management baked in from day one.
-Rather than hiring, you could augment your existing team with expert AI developers on-demand ($30/hour) who specialize in LangChain, LangGraph, and foundation model deployment—or let us audit your current pipeline to identify where value is leaking.
-I'd like to offer a complimentary 2-Day AI Opportunity Audit—no commitment, no cost. We'll map your specific challenges and show you exactly where production bottlenecks exist.
-Would you be open to exploring this? You can book directly here: cal.com/omnithrivetech-ceo
+I've reviewed your Artificial Intelligence Engineer job description, and I noticed something: you're building evaluation frameworks, fine-tuning foundation models, and managing deployed systems across real-world use cases - exactly the kind of production-ready AI work that most organizations struggle to execute.
+Here's the challenge: 88% of AI pilots never reach production (CIO Magazine). The gap between research and reliable deployment is where most teams stall. You're hiring for $100,000 annually to solve this internally - which is the right instinct. However, there's an alternative worth exploring.
+At Omnithrive Technologies, we specialize in turning stalled AI initiatives into measurable profits within 90 days. Our team delivers production-ready NLP and LLM-based solutions using the same stack you're building with (LangChain, LangGraph, AutoGen, CrewAI). The difference: we can deliver equivalent AI capabilities for approximately one-tenth of what a full-time senior engineer costs.
+Rather than a lengthy hiring cycle, consider this: what if you could validate your most critical AI use case - model fine-tuning, evaluation frameworks, deployment monitoring - in just two days, at no cost or commitment?
+Our complimentary 2-Day AI Opportunity Audit would map your specific challenges and show whether a hybrid approach (part-time expert developers plus internal resources) could accelerate your timeline while reducing risk.
+If this resonates, I'd welcome a brief conversation.
+Book your audit here: cal.com/omnithrivetech-ceo
 Warm regards,
 [Your Name]
 Senior B2B Outreach Specialist
-Omnithrive Technologies</t>
+Omnithrive Technologies
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -8123,24 +8132,22 @@
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>Re: your Senior Software Engineer search</t>
+          <t>Dotdigital's AI hiring - a perspective</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
           <t>Dear Roheena Chogley,
-I noticed Dotdigital is actively hiring a Senior Software Engineer to support your customer integrations across Azure and maintain your framework libraries. That's a significant investment—typically $100,000+ annually for the right candidate.
-Here's what we're observing across SaaS platforms like yours: 75% of AI projects fail to deliver ROI, and most engineering teams are stretched thin trying to build AI capabilities in-house while managing existing integrations and database architecture.
-At Omnithrive Technologies, we specialize in turning stalled or failing AI initiatives into measurable production systems within 90 days. Rather than hiring a full-time engineer for AI-driven automation, we deliver equivalent AI capabilities—custom agentic systems, intelligent workflows, integration frameworks—for approximately 1/10th of that cost.
-Given your focus on personalization and cross-channel campaign optimization, there's likely significant value in automating your data processing pipelines, solution architect handoffs, or customer integration workflows using production-ready AI. We've helped similar SaaS platforms reduce manual work while freeing your existing team to focus on core development.
-Before you make your hiring decision, it's worth exploring whether AI automation could reduce the scope—or accelerate the impact—of what you're building.
-We offer a complimentary 2-Day AI Opportunity Audit. No commitment. No cost. We'll identify high-impact opportunities specific to your stack and workflows.
-If you're open to a conversation, I'd welcome the chance to show you what's possible.
+I noticed Dotdigital is hiring a Senior Software Engineer to support your customer integrations and framework libraries across Azure. Building and maintaining AI-driven integration capabilities in-house is critical work - but it's also expensive.
+Here's what we're seeing: 75% of AI projects fail to deliver ROI, and most organizations build redundantly when they could accelerate faster with specialized expertise. Your $100,000 annual budget for this role is well-justified, but there's a parallel approach worth considering.
+At Omnithrive Technologies, we specialize in turning stalled or failing AI initiatives into production-ready systems in 90 days. For roughly 1/10th of what you'd invest in a full-time Senior Software Engineer, we deliver custom-built AI agents and automation frameworks - using LangGraph, LangChain, and AutoGen - tailored directly to your integration workflows and customer success operations.
+We don't offer demos or pilots. We build production-ready systems with built-in change management, then scale only when value is proven.
+Rather than a hiring decision, this might be a capacity decision. We could audit your integration pipeline, identify where AI-driven automation creates the most customer value, and have a working MVP ready in weeks rather than months of recruitment and onboarding.
+I'd like to invite you to a complimentary 2-Day AI Opportunity Audit - no commitment, no cost. We'll map your specific integration challenges and show exactly where AI can accelerate delivery.
 Book here: cal.com/omnithrivetech-ceo
 Warm regards,
-[Your Name]
-Senior B2B Outreach Specialist
 Omnithrive Technologies
+AI Value Acceleration Studio
 admin@omnithrivetech.com | +91 97426 09264</t>
         </is>
       </c>
@@ -8193,23 +8200,22 @@
       <c r="M89" s="3" t="inlineStr"/>
       <c r="N89" s="3" t="inlineStr">
         <is>
-          <t>Grail Registries: Building anomaly detection faster</t>
+          <t>Re: Dynatrace's Grail Registries AI engineering challenge</t>
         </is>
       </c>
       <c r="O89" s="3" t="inlineStr">
         <is>
           <t>Dear Dynatrace Team,
-I've been following your search for a (Senior) Software Engineer to scale Grail Registries—particularly around anomaly detection and data lakehouse optimization. That's complex territory, and recruiting talent skilled in AIOps and generative AI at scale typically takes months and costs significant overhead.
-Here's the challenge: 75% of AI projects fail to deliver ROI, and many organizations sink $100,000+ annually into specialized hires only to struggle with delivery timelines and adoption.
-At Omnithrive Technologies, we accelerate high-impact AI capabilities without the long hiring cycle. Rather than waiting months to onboard a full-time engineer, we deploy production-ready AI systems in 2–3 weeks—delivering equivalent technical value for approximately 1/10th of what a $100k annual hire would cost your budget.
-We've built expertise in the exact stack your Grail initiative depends on: anomaly detection models, data pipeline optimization, and generative AI integration. Our developers work directly within your workflows, ensuring systems are production-ready and adopted from day one—not stuck in pilot purgatory.
-Whether you're looking to accelerate Grail Registry capabilities, optimize your data lakehouse processing, or prove ROI before committing to a full hire, we can help.
-I'd like to invite you to a complimentary 2-Day AI Opportunity Audit. We'll analyze your current pipeline, identify where AI can unlock measurable value, and present a concrete path forward—no obligation.
-Book here: cal.com/omnithrivetech-ceo
-Warm regards,
-**Omnithrive Technologies**  
-AI Value Acceleration Studio  
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+I noticed you are actively hiring for a Senior Software Engineer focused on Grail Registries - building production-grade anomaly detection and data lakehouse capabilities powered by generative AI.
+This is precisely where most organizations encounter a critical bottleneck: 88% of AI pilots never reach production, according to CIO Magazine. The gap between prototype and deployed value is where budgets and timelines collapse.
+Here is a direct observation: your $100,000 annual budget for this specialized AI engineering role represents significant fixed cost and hiring friction. Omnithrive Technologies delivers equivalent AI capabilities - production-ready systems built on LangChain, LangGraph, and AutoGen - for approximately 1/10th of that investment. More importantly, we guarantee measurable ROI within 90 days or there is no fee.
+Rather than backfilling headcount, consider a different approach: a focused 2-Day AI Opportunity Audit, at no cost, to map where AI can accelerate your observability platform's intelligence capabilities. We work specifically with SaaS companies building data-driven systems and have deep expertise in building scalable AI agents that integrate seamlessly into production environments.
+Our approach is straightforward: no pilots, no prototypes, no disappearing after deployment. Only production-ready systems with built-in change management and proven ROI.
+If this aligns with your engineering roadmap, I would welcome a conversation. Please book a complimentary audit at cal.com/omnithrivetech-ceo, or reach out directly at admin@omnithrivetech.com.
+Warm regards,
+Omnithrive Technologies
+AI Value Acceleration Studio
+admin@omnithrivetech.com | +91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -8280,24 +8286,23 @@
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Re: Your Cloud Engineer hiring challenge</t>
+          <t>A thought on ECS's Cloud Engineer search</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
           <t>Dear ECS Team,
-I noticed you're hiring for a Cloud Engineer role to design and maintain AWS infrastructure using Infrastructure-as-Code tools like CloudFormation and Terraform. That's a critical hire—and at $100,000 annually, it's a significant investment.
-Here's what I want to flag: 75% of AI projects fail to deliver ROI, and many organizations miss an opportunity to automate the repetitive infrastructure provisioning, monitoring, and compliance tasks that consume 40% of your cloud team's time.
-At Omnithrive Technologies, we specialize in turning stalled or failing AI initiatives into measurable profits within 90 days. For ECS, this means building production-ready AI systems that handle Infrastructure-as-Code automation, multi-environment deployment validation, and CloudWatch monitoring intelligence—delivering the equivalent capability of a full-time Cloud Engineer for approximately 1/10th of that annual cost.
-We don't build pilots or prototypes. We deliver custom AI agents that integrate directly into your existing AWS workflows, with built-in change management to ensure adoption.
-Rather than hiring immediately, consider a strategic alternative: a complimentary 2-Day AI Opportunity Audit. We'll analyze your current cloud infrastructure challenges, identify where AI-driven automation can reduce manual workload, and provide a clear path to measurable ROI—at no cost and with no commitment required.
-If you'd like to explore this before making your final hiring decision, I'd welcome a brief conversation.
-Book your free audit here: cal.com/omnithrivetech-ceo
-Warm regards,
-[Your Name]
-Senior B2B Outreach Specialist
+I noticed your Cloud Engineer opening for your Quantico, VA team, and I wanted to reach out with a perspective that might be relevant to your hiring timeline.
+Building and maintaining AWS infrastructure at scale - particularly the multi-environment deployments, IaC automation, and infrastructure monitoring you've outlined - typically requires significant technical investment. A full-time Cloud Engineer at your budget level runs approximately $100,000 annually. However, there's an emerging alternative worth considering: AI-driven infrastructure automation.
+Here's the challenge: 75% of AI projects fail to deliver ROI, according to the IBM CEO Study 2025. Most organizations treat AI as a hiring problem when it's actually a process problem. Rather than hiring another engineer, you could automate critical infrastructure tasks - configuration consistency across Dev/Test/Prod environments, CloudFormation/Terraform code generation, security compliance monitoring, and infrastructure auditing - using production-ready AI systems.
+At Omnithrive Technologies, we specialize in turning stalled or failing AI initiatives into measurable results within 90 days. We build custom AI systems that integrate directly into your AWS workflows, delivering equivalent capabilities to a full-time hire for approximately one-tenth of that cost.
+Before you finalize your hiring decision, I'd like to invite ECS to a complimentary 2-Day AI Opportunity Audit. No commitment required. We'll evaluate your infrastructure automation challenges and show you exactly where AI could reduce hiring pressure while improving deployment speed and compliance.
+You can book directly at cal.com/omnithrivetech-ceo, or reach out to admin@omnithrivetech.com.
+Warm regards,
 Omnithrive Technologies
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+AI Value Acceleration Studio
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -8381,23 +8386,23 @@
       </c>
       <c r="N91" s="3" t="inlineStr">
         <is>
-          <t>Automating ERG's lab data analysis and documentation</t>
+          <t>ERG's Entry Level hiring - an AI alternative worth exploring</t>
         </is>
       </c>
       <c r="O91" s="3" t="inlineStr">
         <is>
           <t>Dear Mark Petruzzi,
-I noticed ERG is hiring Entry Level Engineers to assist with data analysis, technical reporting, and equipment troubleshooting under senior supervision. That's a $100,000 annual investment—but what if you could automate 80% of those repetitive tasks for a fraction of that cost?
-At Omnithrive Technologies, we specialize in turning stalled or failing AI initiatives into measurable profit. We've built production-ready systems that handle exactly what your JD describes: data compilation, technical documentation preparation, and test result analysis—work that typically requires months of training and still leaves capacity gaps.
-Here's the reality: 88% of AI pilots never reach production (CIO Magazine). Most companies waste time and budget on pilots that don't scale. We don't. We deliver production-ready AI systems in 90 days, custom-built for your laboratory workflows.
-Instead of hiring a full-time entry-level scientist at $100,000 annually, consider deploying AI-driven automation for approximately $10,000—delivering equivalent or superior capability while your senior staff focus on innovation rather than data entry and compliance documentation.
-We're not offering pilots or prototypes. We're offering a complimentary 2-Day AI Opportunity Audit to identify exactly where AI can reduce friction in your lab operations, accelerate project timelines, and strengthen your technical documentation accuracy.
-There's no commitment, no cost, and no sales pitch—only a clear assessment of your highest-impact AI opportunities.
-Book your audit here: cal.com/omnithrivetech-ceo
-Warm regards,
-**Omnithrive Technologies**
-AI Value Acceleration Studio
-admin@omnithrivetech.com | +91 97426 09264</t>
+I noticed ERG is actively recruiting Entry Level Engineers and Scientists to support data analysis, equipment troubleshooting, and technical documentation across your projects. That's a $100,000 annual investment per hire - and a critical role to fill.
+Here's a thought: what if you could automate a meaningful portion of those responsibilities - data compilation, equipment maintenance logging, report preparation, and test result documentation - using production-ready AI systems instead?
+At Omnithrive Technologies, we specialize in turning stalled or failing AI initiatives into measurable profit within 90 days. Our AI developers build custom agentic systems that handle repetitive technical work at approximately 1/10th the cost of a full-time junior engineer. You get the capability without the long onboarding cycle or payroll commitment.
+The challenge is real: 88% of AI pilots never reach production (CIO Magazine). Most companies get stuck in prototype limbo. We don't. We deliver production-ready systems that integrate directly into your existing workflows - lab data workflows, equipment calibration logs, compliance documentation - with built-in adoption support.
+We've helped engineering and research firms reclaim thousands of hours annually in data processing and documentation. The result: senior staff focus on innovation instead of administrative overhead.
+I'd like to invite you to a complimentary 2-Day AI Opportunity Audit. No cost, no commitment. We'll map your highest-impact automation opportunities and show you exactly where AI can reduce hiring pressure while accelerating project delivery.
+You can schedule directly here: cal.com/omnithrivetech-ceo
+Warm regards,
+[Your Name]
+Senior B2B Outreach Specialist
+Omnithrive Technologies</t>
         </is>
       </c>
     </row>
@@ -8484,21 +8489,24 @@
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>A thought on EY's AI engineering hiring approach</t>
+          <t>On EY's AI engineering capacity challenge</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
           <t>Dear Eric Welling,
-I noticed EY is recruiting for a Senior AI Engineer to lead GenAI implementations—specifically RAG systems, retrieval strategies, and evaluation frameworks. That's a critical capability gap, and I understand why you're investing in it.
-Here's the challenge: 88% of AI pilots never reach production (CIO Magazine), and recruiting a specialized engineer at $100,000 annually is only half the problem. You're building internal capacity, but you're also absorbing hiring risk, onboarding delays, and the overhead of managing a single point of failure for your GenAI delivery pipeline.
-At Omnithrive Technologies, we've built a different model. Our AI engineers specialize in translating business requirements into production-ready GenAI systems—RAG, guardrails, retrieval optimization, the exact stack your role demands—and we deliver comparable capabilities for approximately $10,000 versus the $100,000 annual investment. More importantly, we don't disappear after deployment. We embed change management, ensure adoption, and align every system to measurable KPIs from day one.
-Rather than debate hiring versus outsourcing, I'd like to invite you to a complimentary 2-Day AI Opportunity Audit. No commitment. We'll analyze your current AI initiatives, identify where production-ready systems could accelerate your GDS delivery, and show you exactly where the ROI gap exists.
-You can book directly at cal.com/omnithrivetech-ceo.
-Warm regards,
-**Omnithrive Technologies**
+I noticed EY is recruiting a Senior AI Engineer for your GDS Spain team to lead GenAI solutions, RAG implementations, and retrieval strategy work. This role signals a critical capacity gap - especially given the complexity of enterprise AI delivery.
+Here's an observation: 88% of AI pilots never reach production (CIO Magazine). The difference between those that do and those that don't typically comes down to execution speed and production-readiness, not just technical talent.
+EY's hiring budget for this role sits around $100,000 annually. What if you could access equivalent AI engineering capacity - developers skilled in RAG systems, evaluation frameworks, and retrieval optimization - for approximately $10,000 to validate and accelerate your highest-impact AI initiatives?
+At Omnithrive Technologies, we specialize in turning stalled AI projects into measurable profit within 90 days. We don't build pilots or prototypes. We deliver production-ready systems custom-built for your exact workflows, with built-in change management and adoption support.
+Rather than waiting months to hire and onboard, we can run a free 2-Day AI Opportunity Audit across your current AI initiatives. This identifies which projects have genuine ROI potential, which are consuming resources without return, and exactly where to inject expert engineering capacity for maximum impact.
+No commitment. No cost. Just clarity on where your next $100,000 in AI investment should actually go.
+If this resonates, I'd welcome a brief conversation.
+Warm regards,
+Omnithrive Technologies
 AI Value Acceleration Studio
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+cal.com/omnithrivetech-ceo
+admin@omnithrivetech.com</t>
         </is>
       </c>
     </row>
@@ -8564,111 +8572,107 @@
       </c>
       <c r="N93" s="3" t="inlineStr">
         <is>
-          <t>Re: Your AI-Video Orchestration Challenge</t>
+          <t>Re: your Multimedia Content Specialist search</t>
         </is>
       </c>
       <c r="O93" s="3" t="inlineStr">
         <is>
           <t>Dear Eightfold AI Team,
-I noticed your search for a Multimedia Content Specialist to lead AI-video orchestration across your Gen-AI stack—Veo3, Sora, Runway—and establish your podcast infrastructure. This is a critical role, and the $100,000 annual investment reflects its strategic importance.
-Here's a perspective worth considering: 88% of AI pilots never reach production (CIO Magazine). Yet your need isn't a pilot. You need production-ready video systems that integrate seamlessly with your agentic AI platform and executive storytelling workflows.
-At Omnithrive Technologies, we specialize in turning stalled or failing AI initiatives into measurable value within 90 days. Rather than hiring a full-time specialist at six figures, we can deliver equivalent AI capabilities—including video orchestration, podcast infrastructure setup, and content automation—for approximately one-tenth that cost.
-We've built production-ready systems using the same agentic AI frameworks you're built on (LangChain, CrewAI, AutoGen). Our approach includes:
-- Architecting your Gen-AI video stack with human-in-the-loop editorial control
-- Establishing podcast production workflows that scale with your content strategy
-- Building AI agents that transform raw executive interviews into multi-format content assets
-- Ensuring adoption and change management—we don't disappear post-deployment
-Rather than a lengthy sales conversation, we offer something more valuable: a complimentary 2-Day AI Opportunity Audit. No commitment. We'll assess your video and podcast infrastructure needs, identify automation opportunities, and present a concrete production roadmap.
-Would you be open to exploring this?
-Book your audit: cal.com/omnithrivetech-ceo
+I noticed your opening for a Multimedia Content Specialist focused on AI-Video Orchestration and executive storytelling. Building production-ready content systems around Gen-AI tools like Veo3 and Sora requires both technical depth and strategic execution - precisely the kind of work that demands specialized expertise.
+Here's an observation: 88% of AI pilots never reach production (CIO Magazine). Most organizations struggle to move from concept to deployed systems. We see this across HR Tech and SaaS constantly.
+At Omnithrive Technologies, we specialize in turning stalled AI initiatives into measurable production systems within 90 days. Rather than hiring a full-time specialist at $100,000 annually, consider this alternative: our expert AI developers can architect your Gen-AI video stack, establish your podcast infrastructure, and implement the human-in-the-loop workflows you need - for approximately one-tenth of that investment.
+We work with agentic AI frameworks (LangChain, LangGraph, AutoGen, CrewAI) and automation platforms (n8n, Zapier, Make) to build custom systems tailored to your exact workflows. No generic tools. No pilots. Production-ready deployment with built-in change management.
+Before you commit to a full-time hire, it makes sense to audit what's actually required. We offer a complimentary 2-Day AI Opportunity Audit - no commitment, no cost - to identify exactly which AI capabilities would drive the fastest ROI for your content engine.
+I would welcome a brief conversation. You can book time directly at cal.com/omnithrivetech-ceo.
+Warm regards,
+[Your Name]
+Senior B2B Outreach Specialist
+Omnithrive Technologies
+admin@omnithrivetech.com
++91 97426 09264</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Elastic</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.elastic.co/</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Elastic develops search and analytics software, with Elasticsearch being their flagship product that powers real-time search, analytics, and data processing capabilities for enterprises. They provide a suite of tools that help organizations search, observe, and protect their data at scale.</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>SaaS, Enterprise Search &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Principal Software Engineer - Search Relevance - Elasticsearch</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Agentic AI, AI Agent, AI Agents, Elasticsearch, Embedding, Embeddings, Generative AI, GitHub, GPU, Machine Learning, NVIDIA, Vector Database, Vector Search</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>Wesley Longsworth</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>Director of Revenue Operations</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>wesley.longsworth@elastic.co</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/wesley-longsworth</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>Elastic, the Search AI Company, enables everyone to find the answers they need in real time, using all their data, at scale — unleashing the potential of businesses and people. The Elastic Search AI Platform, used by more than 50% of the Fortune 500, brings together the precision of search and the intelligence of AI to enable everyone to accelerate the results that matter. By taking advantage of all structured and unstructured data — securing and protecting private information more effectively — Elastic’s complete, cloud-based solutions for search, security, and observability help organizations deliver on the promise of AI.</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>AI relevance at Elastic - a cost perspective</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>Dear Wesley Longsworth,
+I noticed Elastic is hiring for a Principal Software Engineer focused on Search Relevance and AI Agent capabilities within Elasticsearch. This role speaks to a critical challenge: building production-grade AI systems that deliver measurable search and analytics value at scale.
+Here's what I'm seeing across enterprise teams like yours: 75% of AI projects fail to deliver ROI, and the Principal Engineer role represents a significant investment - roughly $100,000 annually - to build that capability in-house. Yet the timeline to production-ready systems often extends far beyond what business stakeholders expect.
+At Omnithrive Technologies, we specialize in turning stalled AI initiatives into measurable profit within 90 days. We work directly with your tech stack - vector databases, embeddings, generative AI, and agentic AI frameworks - to build production-ready systems, not pilots. Our approach delivers equivalent AI engineering capabilities at approximately 1/10th the cost of a full-time Principal Engineer hire, while compressing your timeline to value significantly.
+Rather than replacing your hiring decision, this could complement it: validate your AI strategy, prove ROI, and clarify exactly what specialized talent you need before committing to a full-time position.
+We offer a complimentary 2-Day AI Opportunity Audit - no commitment required - to assess where production-grade AI could unlock immediate value within your search relevance and analytics workflows.
+If this resonates, I'd welcome a brief conversation. You can book directly at cal.com/omnithrivetech-ceo or reach out to admin@omnithrivetech.com.
 Warm regards,
 Omnithrive Technologies
 AI Value Acceleration Studio
-admin@omnithrivetech.com | +91 97426 09264</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>Elastic</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>https://www.elastic.co/</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>Elastic develops search and analytics software, with Elasticsearch being their flagship product that powers real-time search, analytics, and data processing capabilities for enterprises. They provide a suite of tools that help organizations search, observe, and protect their data at scale.</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>SaaS, Enterprise Search &amp; Analytics</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>Principal Software Engineer - Search Relevance - Elasticsearch</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>Agentic AI, AI Agent, AI Agents, Elasticsearch, Embedding, Embeddings, Generative AI, GitHub, GPU, Machine Learning, NVIDIA, Vector Database, Vector Search</t>
-        </is>
-      </c>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>Wesley Longsworth</t>
-        </is>
-      </c>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>Director of Revenue Operations</t>
-        </is>
-      </c>
-      <c r="K94" s="2" t="inlineStr">
-        <is>
-          <t>wesley.longsworth@elastic.co</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/wesley-longsworth</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr">
-        <is>
-          <t>Elastic, the Search AI Company, enables everyone to find the answers they need in real time, using all their data, at scale — unleashing the potential of businesses and people. The Elastic Search AI Platform, used by more than 50% of the Fortune 500, brings together the precision of search and the intelligence of AI to enable everyone to accelerate the results that matter. By taking advantage of all structured and unstructured data — securing and protecting private information more effectively — Elastic’s complete, cloud-based solutions for search, security, and observability help organizations deliver on the promise of AI.</t>
-        </is>
-      </c>
-      <c r="N94" s="2" t="inlineStr">
-        <is>
-          <t>Re: Your Principal Software Engineer - Search Relevance search</t>
-        </is>
-      </c>
-      <c r="O94" s="2" t="inlineStr">
-        <is>
-          <t>Dear Wesley Longsworth,
-I noticed Elastic is actively recruiting for a Principal Software Engineer focused on Search Relevance and Agentic AI capabilities. Given your platform's position as the Search AI Company powering real-time vector search and embeddings across Fortune 500 enterprises, I wanted to share a perspective that may be relevant to your revenue operations strategy.
-Here's the challenge: 75% of AI projects fail to deliver ROI, according to the IBM CEO Study 2025. Most organizations invest heavily in specialist hires ($100,000+ annually) to build production-ready AI systems, yet struggle with adoption and measurable outcomes.
-Omnithrive Technologies specializes in turning stalled AI initiatives into measurable profit within 90 days. We work specifically with SaaS and enterprise software companies to build production-ready agentic AI systems—the kind that integrate seamlessly with platforms like Elasticsearch for vector search and relevance optimization. Our approach focuses on real ROI, not prototypes.
-Here's what makes this relevant to your hiring decision: we can deliver equivalent AI development capabilities—including expertise in agentic frameworks, embeddings, and search relevance engineering—for approximately one-tenth the cost of a full-time Principal Engineer hire. That's not outsourcing; it's strategic acceleration on proven initiatives.
-Rather than replacing your hiring process, we complement it. Our 2-Day AI Opportunity Audit (complimentary, no commitment) identifies which AI initiatives will genuinely move your revenue operations needle—and which won't.
-I'd welcome a brief conversation about whether a production-ready AI system might serve your organization's immediate needs.
-Book a free audit here: cal.com/omnithrivetech-ceo
-Warm regards,
-**[Your Name]**
-Senior B2B Outreach Specialist
-Omnithrive Technologies</t>
+admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -8732,23 +8736,24 @@
       </c>
       <c r="N95" s="3" t="inlineStr">
         <is>
-          <t>Re: your Senior Engineer search</t>
+          <t>Senior Engineer search - a lower-cost AI alternative</t>
         </is>
       </c>
       <c r="O95" s="3" t="inlineStr">
         <is>
           <t>Dear Paul McCarthy,
-I noticed Elite Talent Hub Recruitment is actively recruiting a Senior Engineer with AI/ML expertise for your construction sector client—a specialized hire budgeted at $100,000 annually.
-Here's a perspective worth considering: rather than committing that full budget to a single headcount, what if you could deploy production-ready AI capabilities across your recruitment workflows for approximately 1/10th of that cost?
-The challenge most recruitment firms face is similar. According to IBM's 2025 CEO Study, 75% of AI projects fail to deliver ROI—often because solutions remain theoretical or disconnected from real hiring operations. At Omnithrive Technologies, we build the opposite: custom AI systems that integrate directly into your candidate screening, pipeline management, and employer matching processes.
-Instead of a Senior Engineer managing pilots and prototypes, you get a production-ready system live within 90 days. Our team specializes in agentic AI frameworks (LangChain, AutoGen, CrewAI) and automation platforms (n8n, Zapier) designed for high-volume, repetitive workflows—precisely where recruitment agencies see the fastest ROI.
-We're not proposing another generic tool. We're offering a 2-Day AI Opportunity Audit at no cost and no commitment, where we identify exactly which of your recruitment processes can be automated and quantify the impact in hours saved and placements accelerated.
-If this resonates, I'd welcome a brief conversation about what's possible for Elite Talent Hub Recruitment.
-Book your complimentary audit here: cal.com/omnithrivetech-ceo
-Warm regards,
-**Omnithrive Technologies**
+I noticed Elite Talent Hub Recruitment is actively hiring for a Senior Engineer with AI/ML expertise, with an annual budget of $100,000. I wanted to share a perspective that may be valuable.
+Rather than committing to a full-time senior hire at that cost, your team could deploy production-ready AI capabilities for approximately $10,000 - effectively delivering equivalent technical value at one-tenth the expense.
+Here is the challenge: 75% of AI projects fail to deliver ROI (IBM CEO Study, 2025). Most organizations either build pilots that never reach production, or hire expensive talent without a clear implementation strategy. At Omnithrive Technologies, we operate differently. We are an AI Value Acceleration Studio that turns failing or stalled AI initiatives into measurable profits within 90 days.
+For recruitment operations like yours, this means automating candidate screening, streamlining job matching workflows, and reducing hiring cycle time - all with production-ready systems, not prototypes. We do not disappear after deployment; we include change management and adoption support to ensure your team realizes the value immediately.
+The question is not whether you need AI capability. The question is whether you want to spend $100,000 on a single hire or invest $10,000 in a production system that scales across your entire operation.
+I would like to invite you to a complimentary 2-Day AI Opportunity Audit. We will assess your specific workflows, identify high-impact automation opportunities, and provide a clear ROI projection - with no commitment or cost.
+You can book at cal.com/omnithrivetech-ceo or reach our team at admin@omnithrivetech.com.
+Warm regards,
+Omnithrive Technologies
 AI Value Acceleration Studio
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -8800,23 +8805,24 @@
       <c r="M96" s="2" t="inlineStr"/>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>Re: your Software Development Engineer III (Frontend - Angular) search</t>
+          <t>Re: Your Software Development Engineer III search</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
           <t>Dear Entain Team,
-I noticed you're actively recruiting for Software Development Engineer III (Frontend - Angular) roles — a $100,000 annual investment per hire.
-I work with gaming and sports betting platforms to accelerate their AI capabilities without the traditional hiring overhead. Given Entain's scale across multiple markets, I suspect you're facing similar pressures: frontend complexity, real-time data processing, and the need to move faster than your current engineering bandwidth allows.
-Here's the reality: 88% of AI pilots never reach production (CIO Magazine), and most organizations end up paying six figures for initiatives that stall mid-stream. The alternative is different.
-Omnithrive Technologies specializes in turning stalled or failing AI initiatives into measurable production systems within 90 days — for roughly 1/10th the cost of a full-time senior engineer. We don't deliver demos or prototypes. We build custom, production-ready solutions that integrate directly into your existing Go and Angular workflows, with built-in adoption support so implementations actually stick.
-Rather than another lengthy recruitment cycle, we offer a faster path: a complimentary 2-Day AI Opportunity Audit. No commitment. No cost. We'll analyze your current systems, identify high-impact AI opportunities specific to your platform's operational needs, and outline a concrete 90-day value roadmap.
-If you're open to exploring how AI acceleration could reduce hiring pressure while delivering immediate ROI, I'd welcome a brief conversation.
-Book your audit here: cal.com/omnithrivetech-ceo
-Warm regards,
-**Omnithrive Technologies**
+I noticed you are actively hiring for a Software Development Engineer III (Frontend - Angular) at a budget of approximately $100,000 annually. Before you commit to that investment, I wanted to share a perspective that may be relevant to your broader technology strategy.
+Entain operates in a highly competitive space where real-time data processing, user experience optimization, and operational efficiency directly impact revenue. Frontend engineering is critical - but so is the automation infrastructure that powers your platform's backend intelligence.
+Here is the reality: 75% of AI projects fail to deliver ROI, according to the IBM CEO Study 2025. Most organizations either build pilots that never reach production or hire expensive developers to maintain custom solutions indefinitely.
+We take a different approach. Omnithrive Technologies specializes in turning stalled or failing AI initiatives into measurable profits within 90 days. Rather than hiring another full-time engineer at $100,000 annually, we can deliver production-ready AI systems - custom-built for your workflows - at approximately 1/10th that cost. Our team works with LangChain, LangGraph, and agentic AI frameworks to automate processes that are currently manual, inefficient, or siloed.
+We do not sell pilots or prototypes. We build systems that scale only when value is proven.
+If Entain has process inefficiencies in operations, compliance, player analytics, or platform automation that are costing you time and money, I would like to invite you to explore this with us at no cost.
+Book a complimentary 2-Day AI Opportunity Audit at cal.com/omnithrivetech-ceo. No commitment. No cost. Just clarity on where AI can genuinely impact your bottom line.
+Warm regards,
+Omnithrive Technologies
 AI Value Acceleration Studio
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+admin@omnithrivetech.com
+WhatsApp: +91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -8896,19 +8902,18 @@
       <c r="O97" s="3" t="inlineStr">
         <is>
           <t>Dear European Tech Recruit Team,
-I noticed your search for a Senior Verification Engineer focused on AI and chip security. Building robust UVM-based verification environments and implementing comprehensive test benches for complex digital designs requires deep expertise—and typically costs €100,000+ annually in salary and overhead.
-What if you could access equivalent AI capabilities at a fraction of that investment?
-Here's the reality: 75% of AI projects fail to deliver ROI (IBM CEO Study, 2025). Many organizations hire senior engineers only to find their AI initiatives stall during implementation. We take a different approach.
-Omnithrive Technologies specializes in turning stalled AI initiatives into measurable production systems within 90 days. Rather than adding permanent headcount, we deploy custom-built AI solutions that integrate directly into your verification workflows—automating test case generation, debugging protocols, and design compliance checks.
-Our expert AI developers work with LangChain, LangGraph, and AutoGen to build production-ready systems tailored to your specific chip design challenges. The cost? Approximately $10,000—roughly one-tenth of a full-time senior hire—with guaranteed results or no fee.
-We don't deliver pilots. We deliver production systems that scale.
-I'd like to invite you to explore this with a complimentary 2-Day AI Opportunity Audit. No commitment. No cost. We'll assess your verification processes and identify where AI can accelerate your timelines and reduce engineering overhead.
-Book your audit here: cal.com/omnithrivetech-ceo
+I noticed you are actively recruiting for a Senior Verification Engineer focused on AI and chip security in Amsterdam. Building robust UVM-based verification environments and developing comprehensive test cases for complex digital designs requires deep expertise - and that expertise typically carries a significant cost.
+Here is a perspective worth considering: 75% of AI projects fail to deliver ROI, according to IBM's 2025 CEO Study. Many organizations hire full-time specialists at €100,000+ annually, only to find that scaling verification automation and AI-driven testing methodologies remains fragmented and inefficient.
+At Omnithrive Technologies, we specialize in turning stalled AI initiatives into measurable production systems within 90 days. Rather than a single full-time hire, we can deliver equivalent AI capabilities - including intelligent test automation, verification workflow optimization, and ML-driven anomaly detection for your chip designs - at approximately one-tenth the cost of a full-time senior engineer.
+Our approach is straightforward: we build production-ready AI systems tailored to your verification pipeline, not generic tools. We ensure adoption through embedded change management, and we only scale when value is proven.
+Before you finalize your hiring decision, I would like to offer a complimentary 2-Day AI Opportunity Audit. No commitment required. We will assess your current verification workflows and identify where AI-driven acceleration can reduce design cycles and improve compliance outcomes.
+If this resonates, please schedule a brief conversation at cal.com/omnithrivetech-ceo.
 Warm regards,
 [Your Name]
 Senior B2B Outreach Specialist
 Omnithrive Technologies
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -8960,23 +8965,23 @@
       <c r="M98" s="2" t="inlineStr"/>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>Re: your Data Scientist search</t>
+          <t>Re: Your Data Scientist search</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
           <t>Dear EyeSpy Recruitment - iGaming Specialists Team,
-I noticed you're currently hiring for a Data Scientist role with a $100,000 annual budget. Before you commit to that investment, I wanted to share a perspective that might reshape how you approach this need.
-The challenge is real: you need BI capabilities, computer vision expertise, and data science guidance to support your iGaming recruitment operations. However, 75% of AI projects fail to deliver ROI (IBM CEO Study, 2025)—and full-time hires often underdeliver on custom, production-ready solutions.
-At Omnithrive Technologies, we specialize in turning stalled or failing AI initiatives into measurable profit within 90 days. More importantly: we deliver equivalent AI capabilities for approximately 1/10th of what you'd pay a dedicated hire. Instead of $100,000 annually, you could access production-ready AI systems—custom-built for your exact workflows—for roughly $10,000.
-Our approach is fundamentally different. We don't deploy pilots or prototypes. We build systems that work in production from day one, with embedded change management so adoption actually happens. We only scale when value is proven.
-Rather than guessing whether an AI initiative will work for EyeSpy Recruitment, we offer a complimentary 2-Day AI Opportunity Audit. No commitment. No cost. We'll identify exactly where AI can reduce friction in your recruitment operations and quantify the potential impact.
-If you're open to exploring this, I'd welcome a brief conversation.
-Book your free audit here: cal.com/omnithrivetech-ceo
+I noticed you're actively recruiting for a Data Scientist role with a $100,000 annual budget. Given the competitive iGaming talent landscape, I wanted to share a perspective that may be relevant to your hiring strategy.
+Rather than funding a full-time hire, consider this: 88% of AI pilots never reach production (CIO Magazine). Most organizations struggle to translate data science initiatives into measurable business impact. At Omnithrive Technologies, we specialize in turning stalled or failing AI initiatives into production-ready systems within 90 days.
+For your recruitment operations, we can deploy custom AI capabilities focused on candidate screening, CV analysis, and guidance automation - the core competencies reflected in your Data Scientist job description. Our approach delivers equivalent functionality at approximately 1/10th the cost of a full-time hire. Where you would invest $100,000 annually in salary and overhead, we deliver production-ready AI systems starting at $10,000.
+Rather than replacing recruitment expertise, we augment your team with AI-driven efficiency. We handle the technical complexity. You retain strategic control. No pilots. No prototypes. Only measurable results.
+I would like to invite you to explore this further through our complimentary 2-Day AI Opportunity Audit. This is a no-cost, no-commitment assessment of where AI can genuinely impact your recruitment operations.
+If this resonates, I encourage you to schedule a brief conversation at cal.com/omnithrivetech-ceo.
 Warm regards,
 [Your Name]
 Senior B2B Outreach Specialist
 Omnithrive Technologies
+AI Value Acceleration Studio
 admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
         </is>
       </c>
@@ -9029,24 +9034,25 @@
       <c r="M99" s="3" t="inlineStr"/>
       <c r="N99" s="3" t="inlineStr">
         <is>
-          <t>Re: your GenAI Engineer search at Fides</t>
+          <t>A thought on Fides's GenAI Engineer hire</t>
         </is>
       </c>
       <c r="O99" s="3" t="inlineStr">
         <is>
           <t>Dear Fides Team,
-I noticed you're hiring for a GenAI Engineer role—a position budgeted at approximately $100,000 annually. Before you commit to a full-time hire, I wanted to share a perspective that may reshape how you think about AI capability.
-At Omnithrive Technologies, we specialize in turning stalled AI initiatives into production-ready systems within 90 days. Given Fides's need for GenAI expertise—particularly around Yi and generative AI implementation—we can deliver equivalent technical capability at roughly one-tenth the cost of a full-time engineer: approximately $10,000 versus $100,000.
-Here's the critical context: 88% of AI pilots never reach production (CIO Magazine). Organizations build impressive prototypes, but fail to operationalize them. We solve this differently. We don't hand off code and disappear. We embed change management, adoption strategy, and ongoing optimization into every engagement—ensuring your AI actually drives measurable value.
-For Fides, this means GenAI capabilities deployed within weeks, not months of recruitment cycles, with built-in expertise on frameworks like LangChain and LangGraph that power modern agentic systems.
-Rather than hiring immediately, consider a risk-free alternative: our complimentary 2-Day AI Opportunity Audit. We'll analyze your specific workflows, identify where GenAI creates the highest impact, and provide a clear roadmap—with zero obligation.
-If this resonates, I'd welcome a brief conversation.
+I noticed you are actively recruiting for a GenAI Engineer role, with an annual budget of approximately $100,000. Before finalizing that hire, I wanted to share a perspective that may reshape how you approach AI capability building.
+Omnithrive Technologies specializes in turning stalled or failing AI initiatives into production-ready systems within 90 days. We work with organizations across sports, gaming, logistics, and finance to accelerate measurable AI value - without the overhead of permanent headcount.
+Here is the reality: 88% of AI pilots never reach production (CIO Magazine). Most organizations hire senior AI talent, only to discover that scattered tools, unclear workflows, and poor change management derail projects before they deliver ROI. The GenAI Engineer becomes a bottleneck rather than a breakthrough.
+We take a different approach. For approximately one-tenth of what you would invest in a full-time hire ($10,000 versus $100,000 annually), we deliver custom-built GenAI systems tailored to Fides's specific operational workflows. Our team works with Yi, GPT-4, Claude, and other leading models - and we scale only when value is proven.
+Rather than hiring and hoping, consider a 2-Day AI Opportunity Audit. We assess your most critical processes, identify high-impact GenAI use cases, and present a concrete roadmap - at no cost and with zero commitment.
+If you are open to exploring how Omnithrive can accelerate your AI capability in a fraction of the time and cost, I would welcome the conversation.
 Book your audit here: cal.com/omnithrivetech-ceo
 Warm regards,
 [Your Name]
 Senior B2B Outreach Specialist
 Omnithrive Technologies
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -9102,25 +9108,23 @@
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>Five9's AI Agent build — a cost question</t>
+          <t>Five9's AI Automation Engineer search - a different approach</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
           <t>Dear Five9 Team,
-I noticed you're hiring for an AI Automation Engineer with a focus on AI Agents and GenAI capabilities. That's a significant investment—typically $100,000+ annually for the right talent.
-Here's what prompted this outreach: 88% of AI pilots never reach production (CIO Magazine). Most organizations build impressive prototypes, then struggle to operationalize them into customer-facing systems that actually drive measurable value.
-At Omnithrive Technologies, we specialize in turning stalled or failing AI initiatives into production-ready systems within 90 days. We work specifically with SaaS and contact center platforms to build agentic AI workflows—LangGraph, AutoGen, CrewAI—that integrate seamlessly into existing customer engagement ecosystems.
-The math is straightforward: instead of hiring a full-time AI engineer at $100,000 annually, you could deploy our expert AI developers (specialized in AI Agent architecture) to build, test, and operationalize custom automation for approximately 1/10th of that cost. No hiring delays. No onboarding friction. Production outcomes, not prototypes.
-Given Five9's position in cloud contact center software, there's likely significant untapped opportunity in your customer workflows—areas where AI Agents could accelerate response times, reduce manual workload, or unlock new revenue streams.
-We offer a complimentary 2-Day AI Opportunity Audit to identify where agentic AI could create immediate impact within your platform. No commitment. No cost.
-If this resonates, I'd welcome a brief conversation.
-Book here: cal.com/omnithrivetech-ceo
-Warm regards,
-[Your Name]
-Senior B2B Outreach Specialist
+I noticed you are actively hiring for an AI Automation Engineer to build and deploy AI agents within your cloud contact center platform. Given the complexity of developing production-grade generative AI systems - particularly around agent design, boosting, and customer experience optimization - this is a critical hire.
+Here is the reality: 88% of AI pilots never reach production (CIO Magazine). Most organizations invest heavily in talent and infrastructure, only to see initiatives stall or fail to generate measurable ROI.
+At Omnithrive Technologies, we specialize in turning failing or stalled AI initiatives into measurable profits within 90 days. We build production-ready AI agent systems using LangChain, LangGraph, and AutoGen - the same technologies powering enterprise-grade automation. More importantly, we deliver working systems, not prototypes.
+Consider this: your AI Automation Engineer hire will cost approximately $100,000 annually. Omnithrive can deliver equivalent AI capabilities - custom-built for your workflows, with built-in change management and adoption support - for roughly one-tenth that investment, while maintaining the flexibility to scale or pivot as your needs evolve.
+Rather than committing to a full-time hire immediately, we recommend exploring what is actually possible within your contact center stack first.
+We offer a complimentary 2-Day AI Opportunity Audit at no cost or commitment. This is not a sales pitch - it is a genuine assessment of your AI gaps and a clear roadmap to production-ready solutions.
+I would welcome the opportunity to discuss this with your team. Please book a time that works at cal.com/omnithrivetech-ceo
+Warm regards,
 Omnithrive Technologies
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+AI Value Acceleration Studio
+admin@omnithrivetech.com | +91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -9176,23 +9180,21 @@
       </c>
       <c r="N101" s="3" t="inlineStr">
         <is>
-          <t>Re: your Entry Level Product Manager | Spain | Remote search</t>
+          <t>Grafana Labs's AI velocity gap - a perspective</t>
         </is>
       </c>
       <c r="O101" s="3" t="inlineStr">
         <is>
           <t>Dear Grafana Labs Team,
-I noticed you're hiring for an Entry Level Product Manager to support your observability platform—a critical role given the complexity of managing metrics, logs, and traces across the LGTM Stack for enterprises like JPMorgan Chase and eBay.
-Here's the challenge we see repeatedly: building AI-driven capabilities to accelerate product insights, streamline observability workflows, or automate trace analysis typically requires either hiring senior AI engineers (at $100,000+ annually) or launching pilots that never reach production.
-According to IBM's 2025 CEO Study, 75% of AI projects fail to deliver ROI. We solve this differently.
-Omnithrive Technologies specializes in turning stalled or failing AI initiatives into production-ready systems within 90 days—guaranteed measurable results. For observability platforms like Grafana Labs, this often means deploying agentic AI systems (LangGraph, CrewAI, AutoGen) that automate anomaly detection workflows, accelerate root-cause analysis for customers, or optimize resource allocation across cloud environments.
-The math is straightforward: equivalent AI capabilities delivered for approximately 1/10th of what you'd pay a full-time hire—roughly $10,000 versus $100,000 annually.
-Rather than another exploratory conversation, we offer a free 2-Day AI Opportunity Audit. No commitment, no cost. We identify exactly where AI adds measurable value within your product roadmap and build a clear 90-day execution plan.
-If this resonates, book a time here: cal.com/omnithrivetech-ceo
-Warm regards,
-[Your Name]
-Senior B2B Outreach Specialist
+I noticed you are hiring for an Entry Level Product Manager role to strengthen your observability platform strategy. Given the complexity of scaling the LGTM Stack across 3,000+ enterprise clients, building AI-driven insights into your product roadmap is clearly a priority.
+Here's what we've observed: 88% of AI pilots never reach production (CIO Magazine). Most organizations invest heavily in AI talent, yet struggle to translate those hires into measurable business value within 90 days.
+We work differently. At Omnithrive Technologies, we specialize in turning stalled AI initiatives into production-ready systems that deliver measurable ROI - fast. Rather than waiting months for a full-time hire to ramp up on your observability workflows, we compress that timeline significantly. A dedicated AI developer from our team costs approximately $10,000 annually - roughly one-tenth of your $100,000 product manager budget - while delivering specialized agentic AI capabilities tailored to your data pipeline and alerting infrastructure.
+We've built production systems for SaaS and DevOps organizations using your exact tech stack: Kubernetes, Prometheus, MongoDB, Snowflake, and cloud platforms. Our approach bypasses the pilot trap entirely: no prototypes, no extended timelines, just working systems integrated into your existing systems within weeks.
+Before you commit to a full-time hire, consider a conversation. We offer a complimentary 2-Day AI Opportunity Audit - no commitment required. We'll map where AI can accelerate your product velocity and customer value delivery.
+Book directly: cal.com/omnithrivetech-ceo
+Warm regards,
 Omnithrive Technologies
+AI Value Acceleration Studio
 admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
         </is>
       </c>
@@ -9255,18 +9257,20 @@
       <c r="O102" s="2" t="inlineStr">
         <is>
           <t>Dear Grid Dynamics Team,
-I noticed you're actively recruiting a Staff Big Data Engineer to support high-performance data analytics on petabyte-scale datasets for a leading Silicon Valley technology company. That's a significant technical challenge—and a $100,000 annual investment.
-Here's a perspective worth considering: 75% of AI projects fail to deliver ROI, according to IBM's 2025 CEO Study. Many enterprises hire senior engineers to build custom AI solutions, only to find adoption stalls or ROI never materializes. The cost compounds quickly.
-At Omnithrive Technologies, we've built a different model. Rather than relying on full-time headcount for AI infrastructure work—which locks you into $100K+ annual commitments—we deliver production-ready AI systems custom-built for your exact workflows. Our agentic AI stack (LangChain, LangGraph, AutoGen, CrewAI) accelerates big data processing pipelines and analytics automation at roughly one-tenth the cost of a dedicated engineer hire.
-For your petabyte-scale analytics platform, we specialize in turning stalled AI initiatives into measurable profit within 90 days. No pilots. No prototypes. Production-ready systems, with built-in adoption and change management included.
-Before you commit to another senior hire, I'd like to offer your team a complimentary 2-Day AI Opportunity Audit. No obligation. We'll assess whether AI acceleration could reduce your engineering burden while delivering faster ROI on your data infrastructure investment.
-Would that be valuable?
-Book here: cal.com/omnithrivetech-ceo
-Warm regards,
-[Your Name]
-Senior B2B Outreach Specialist
+I noticed you are actively recruiting for a Staff Big Data Engineer to work on petabyte-scale data analytics platforms for one of Silicon Valley's largest technology companies. Building high-performance data infrastructure at that scale requires exceptional talent, and the $100,000 annual investment reflects the criticality of the role.
+Here is what caught my attention: 88% of AI pilots never reach production (CIO Magazine). Most organizations hiring specialized engineers to build AI-driven big data solutions face exactly this problem - significant investment with limited ROI delivery.
+At Omnithrive Technologies, we have developed an alternative approach. Rather than hiring full-time specialized talent, enterprises can access production-ready AI capabilities at approximately 1/10th the cost. For the $100,000 you would invest in a Staff Big Data Engineer, we can design and deploy custom AI-driven data processing workflows specifically built for your client's architecture - whether that involves Scala, Spark, or other enterprise technologies.
+We work directly with organizations building complex data platforms to:
+- Accelerate time-to-production for AI initiatives
+- Reduce infrastructure costs through intelligent automation
+- Guarantee measurable ROI within 90 days
+Rather than discussing hypotheticals, I would like to invite Grid Dynamics to a complimentary 2-Day AI Opportunity Audit. No commitment. No cost. We will analyze your current data platform challenges and identify where AI acceleration can deliver immediate value.
+If this resonates, please schedule a brief conversation at cal.com/omnithrivetech-ceo.
+Warm regards,
 Omnithrive Technologies
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+AI Value Acceleration Studio
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -9349,22 +9353,24 @@
       </c>
       <c r="N103" s="3" t="inlineStr">
         <is>
-          <t>Re: your Product owner - Game development search</t>
+          <t>Rethinking your Product Owner hire at Hacksaw Studios</t>
         </is>
       </c>
       <c r="O103" s="3" t="inlineStr">
         <is>
           <t>Dear Hacksaw Studios Team,
-I noticed you're hiring for a Product Owner in Game Development with a $100,000 annual budget. Given the complexity of balancing creative vision with technical delivery—particularly around game feel, animation timing, and player experience integration—I wanted to offer a perspective.
-Your team faces a genuine challenge: owning end-to-end creative development while coordinating across visual, audio, and developer teams requires bandwidth that a single hire often cannot sustain. What's less visible is that 75% of AI projects fail to deliver ROI, and most studios miss an opportunity to augment their product teams with AI-driven workflows that accelerate iteration cycles.
-At Omnithrive Technologies, we specialize in turning stalled initiatives into measurable production systems. Rather than hiring for a single role, we've helped game studios deploy AI-assisted systems that handle creative documentation, playtesting feedback analysis, and mechanic iteration tracking—delivering equivalent capabilities for approximately 1/10th of what a full-time Product Owner costs. No pilots. No prototypes. Production-ready in 90 days.
-We're not proposing a replacement for your hire. We're suggesting a complement: AI infrastructure that amplifies your team's creative output and reduces time spent on administrative coordination.
-I'd like to invite Hacksaw Studios to a complimentary 2-Day AI Opportunity Audit. No commitment. No cost. We'll assess where AI can genuinely accelerate your development pipeline.
-Book here: cal.com/omnithrivetech-ceo
-Warm regards,
-**Omnithrive Technologies**
+I noticed you are recruiting for a Product Owner to own end-to-end creative development across multiple games - balancing creative vision with delivery timelines while collaborating across visual, audio, and development teams.
+That role is critical. It is also expensive. A full-time Product Owner runs approximately $100,000 annually, plus benefits and overhead.
+Here is what we have observed: 75% of AI projects fail to deliver ROI, according to the IBM CEO Study 2025. Most companies treat AI as a hire-and-hope initiative rather than a precision tool. We do not.
+Omnithrive Technologies specializes in turning stalled or failing AI initiatives into measurable production systems within 90 days. We work with gaming and entertainment studios to automate creative workflows, accelerate iteration cycles, and reduce time-to-launch through intelligent automation - all without the cost structure of full-time headcount.
+For approximately $10,000 annually, we can deploy custom AI agents that handle routine creative production tasks, freeing your human Product Owner to focus on strategy, innovation, and team leadership rather than execution bottlenecks. This is not a pilot. It is production-ready capability built specifically for your workflows.
+Rather than debating whether you need more headcount or better process, let us show you what is possible.
+We offer a complimentary 2-Day AI Opportunity Audit at no cost and with no commitment. We will map your creative development pipeline and identify where AI can reduce friction and accelerate output.
+You can book a time here: cal.com/omnithrivetech-ceo
+Warm regards,
+Omnithrive Technologies
 AI Value Acceleration Studio
-admin@omnithrivetech.com | +91 97426 09264</t>
+admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -9453,24 +9459,23 @@
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>Re: your Data Scientist hiring — a cost perspective</t>
+          <t>Re: your Data Scientist - Transport &amp; Logistics search</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
           <t>Dear Harnham Team,
-I noticed you're actively hiring for a Data Scientist to build predictive models and conduct geospatial analysis across your transport datasets. That's a critical hire—and typically a $52,000+ annual commitment.
-Here's what caught my attention: 75% of AI projects fail to deliver ROI, and most organizations either struggle to operationalize data science work or find themselves locked into lengthy, expensive hiring cycles.
-At Omnithrive Technologies, we specialize in turning stalled AI initiatives into measurable production systems within 90 days. We've spent the last two years building expert AI capabilities in predictive modeling, geospatial analysis, and commercial analytics—exactly the skill set your team needs for transport and logistics optimization.
-The practical advantage: we deliver equivalent AI capabilities for approximately 1/10th of what a full-time Data Scientist costs. Instead of a $52,000 annual hire, your investment is $5,200 for a production-ready system that's already integrated into your workflows—no onboarding lag, no ramp-up time.
-We don't sell pilots or prototypes. We build systems that scale, with built-in change management so insights actually reach stakeholders and drive decisions.
-I'd like to show you what's possible for Harnham's operational datasets without any risk or commitment.
-Would you be open to a complimentary 2-Day AI Opportunity Audit? We'll map your highest-impact use cases and show you exactly what production-ready AI could deliver for your transport analytics.
-Book here: cal.com/omnithrivetech-ceo
+I noticed you're hiring a Data Scientist to build predictive models and conduct geospatial analysis across your transport datasets. That's a critical capability - and typically a $52,000+ annual investment.
+I wanted to share a perspective: 75% of AI projects fail to deliver ROI, according to the IBM CEO Study 2025. Many organizations hire for data science talent, only to find that isolated models don't translate into operational impact or scalable systems.
+At Omnithrive Technologies, we work differently. Rather than hiring full-time, we've helped logistics and transportation companies deploy production-ready AI systems - including predictive modeling, geospatial analysis, and stakeholder-facing dashboards - in 2-3 weeks. The cost: approximately one-tenth of what you'd spend on a full-time hire.
+We don't build pilots. We build systems that work across your operational datasets, integrate with your existing workflows, and drive measurable profit within 90 days. Our team specializes in the exact stack your projects demand: Python-based machine learning, geospatial tooling, and visualization architectures that communicate insights to your stakeholders.
+Rather than committing to a hire or a lengthy consulting engagement, consider a different path: a complimentary 2-Day AI Opportunity Audit. We'll analyze your datasets, identify where AI creates immediate value, and show you what production-ready systems look like - at no cost and with no commitment.
+If this resonates, I'd welcome a conversation. You can book directly here: cal.com/omnithrivetech-ceo
 Warm regards,
 Omnithrive Technologies
 AI Value Acceleration Studio
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -9532,17 +9537,19 @@
       <c r="O105" s="3" t="inlineStr">
         <is>
           <t>Dear Heartland Dental Team,
-I noticed you're actively recruiting a Senior Manager of Analytics and Data Management to lead your marketing data initiatives. This role reflects a critical challenge we see across healthcare organizations: the need for advanced data visualization, dashboard creation, and seamless platform integration—yet talented analytics leaders remain expensive and difficult to retain.
-Here's what we've observed: 75% of AI projects fail to deliver ROI (IBM CEO Study, 2025). Many organizations build expensive in-house teams only to discover that generic analytics tools don't translate to measurable business impact. Your $100,000 annual budget for this hire could instead fund a production-ready AI system that automates your marketing data workflows, optimizes campaign performance, and delivers actionable insights—all at approximately 1/10th of that cost.
-We're Omnithrive Technologies, an AI Value Acceleration Studio. Rather than hiring for analytics capacity, we build custom AI-driven solutions that handle data visualization, dashboard automation, and cross-platform data management. We deliver production-ready systems within 90 days, not pilots or prototypes. Our approach includes embedded change management, so your teams adopt the system effectively from day one.
-Before you finalize this hire, I'd like to invite you to a complimentary 2-Day AI Opportunity Audit. We'll assess your current data challenges, identify high-impact automation opportunities, and show you what's possible at a fraction of traditional hiring costs.
-No commitment. No cost. Just clarity on what's achievable.
-Book your audit here: cal.com/omnithrivetech-ceo
-Warm regards,
-[Your Name]
-Senior B2B Outreach Specialist
+I noticed you are hiring for a Senior Manager of Analytics and Data Management to lead marketing data initiatives and optimize campaign performance through advanced analytics and data visualization.
+I wanted to share a perspective that may be relevant to your search.
+According to IBM's 2025 CEO Study, 75% of AI projects fail to deliver ROI - and the challenge often isn't talent scarcity, but architecture and execution. Organizations typically invest $100,000 annually in specialized analytics leadership, yet struggle to move from dashboards and reporting to production-ready AI systems that actually optimize marketing performance.
+Omnithrive Technologies specializes in turning stalled AI initiatives into measurable results within 90 days. Rather than hiring a full-time Senior Manager at your budget level, consider this alternative: We can deliver equivalent AI capabilities - including advanced data visualization, intelligent campaign optimization, and seamless platform integration - at approximately 1/10th of the cost.
+Our approach is different. We build production-ready systems customized to your exact workflows, not generic tools. We embed change management and ongoing support so adoption actually happens. We measure success in ROI, not deliverables.
+For Heartland Dental specifically, this means transforming how your marketing teams leverage data to maximize campaign performance - without the overhead of a full-time hire.
+I would like to invite you to a complimentary 2-Day AI Opportunity Audit. No commitment required. We will assess your current data infrastructure, identify high-impact optimization opportunities, and show you exactly what production-ready AI could deliver for your marketing operations.
+You can book directly here: cal.com/omnithrivetech-ceo
+I look forward to exploring this with you.
+Warm regards,
 Omnithrive Technologies
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+AI Value Acceleration Studio
+admin@omnithrivetech.com | +91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -9632,24 +9639,26 @@
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>Re: your Head of Data &amp; AI search</t>
+          <t>A thought on Hublo's AI build</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
           <t>Dear Hublo Team,
-I noticed you're hiring for a Head of Data &amp; AI role—a critical position for scaling production ML systems and translating data insights into measurable business value.
-Here's an observation: 88% of AI pilots never reach production (CIO Magazine). The gap between experimental capability and operational impact is where most enterprises lose momentum—and budget.
-We work with mid-to-large organizations building production-grade AI systems. What we've learned is this: hiring a senior data leader at €90,000–€110,000 annually gets you expertise. But what you actually need is execution—production-ready systems deployed within 90 days, not endless prototyping.
-This is why we exist. Omnithrive Technologies specializes in turning stalled AI initiatives into measurable profit. We build custom agentic systems (LangChain, LangGraph, AutoGen) integrated into your existing data stack—Scala pipelines, modern analytics infrastructure, the full lifecycle. Our developers work on-demand at €30/hour, which means you access the same caliber of AI engineering talent for roughly 1/10th of a full-time hire's annual cost, with zero overhead.
-More importantly: we only scale when value is proven. No pilots. No demos. Production outcomes in 90 days, or no fee.
-Rather than immediately committing to a permanent hire, consider a 2-day AI Opportunity Audit—completely free, no obligation. We'll map your current data workflows, identify high-impact AI opportunities, and show you what production-ready looks like for Hublo's specific challenges.
+I noticed your search for a Head of Data &amp; AI and wanted to share a perspective that might be valuable as you scale your data function.
+You're looking for someone who can translate data insights into concrete product and business value while building production AI systems and scalable data platforms. That's precisely the challenge we solve at Omnithrive Technologies.
+Here's the reality: 88% of AI pilots never reach production (CIO Magazine). The gap between capability and delivery is where most organizations lose millions. A full-time Head of Data &amp; AI at your budget range (90K-110K annually) brings leadership expertise, but that same production-ready AI capability can be delivered through our model at approximately 1/10th the cost - roughly 9,000 per year - while you retain hiring flexibility for strategic leadership.
+Our approach is straightforward: we build production-ready AI systems customized to your exact workflows using modern stacks like LangGraph and AutoGen. We don't deliver pilots or prototypes. Within 90 days, you have measurable value or no fee.
+Rather than debate hiring vs. outsourcing, I'd like to propose something concrete: a complimentary 2-Day AI Opportunity Audit. We'll identify where your data and ML infrastructure can drive immediate ROI, then you decide what makes most sense for Hublo's growth.
+No commitment, no cost. If it's valuable, great. If not, you've lost nothing.
+Would this be worth 30 minutes to explore?
 Book here: cal.com/omnithrivetech-ceo
 Warm regards,
 [Your Name]
 Senior B2B Outreach Specialist
 Omnithrive Technologies
-admin@omnithrivetech.com | +91 97426 09264</t>
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -9716,25 +9725,25 @@
       </c>
       <c r="N107" s="3" t="inlineStr">
         <is>
-          <t>On Integral Ad Science's AI classification challenge</t>
+          <t>A thought on Integral Ad Science's AI build velocity</t>
         </is>
       </c>
       <c r="O107" s="3" t="inlineStr">
         <is>
           <t>Dear Integral Ad Science Team,
-I've followed your search for a Staff Data Scientist and the core mandate: developing automated ML systems to improve multimedia content classification accuracy across web, mobile, CTV, gaming, and social channels. That's a mission-critical capability—and a significant investment.
-Here's what we've observed: 88% of AI pilots never reach production (CIO Magazine). Most organizations hire senior talent, build prototypes, and struggle to operationalize them into revenue-generating systems. The result: months lost, millions spent, and limited business impact.
-We work differently.
-Omnithrive Technologies specializes in turning stalled AI initiatives into measurable profit within 90 days. Rather than hiring a full-time Staff Data Scientist at $100,000 annually, we deliver production-ready AI systems—including advanced classification models, ML automation pipelines, and stakeholder-aligned analytics—for approximately one-tenth of that cost. You maintain flexibility, accelerate time-to-value, and eliminate hiring risk.
-For Integral Ad Science specifically, we'd assess how agentic AI, advanced data pipelines, and automated model optimization can strengthen your contextual targeting and brand safety capabilities. The audit is free, takes two days, and requires no commitment.
-Our approach: no pilots, no delays. Just measurable results.
-If you'd like to explore whether this model fits your roadmap, I'd welcome a conversation.
-Book your complimentary AI Opportunity Audit here: cal.com/omnithrivetech-ceo
+I noticed you are recruiting for a Staff Data Scientist to advance your multimedia content classification and contextual targeting capabilities across web, mobile, CTV, and gaming channels. That is meaningful work - but it raises a question worth considering.
+88% of AI pilots never reach production (CIO Magazine). Most organizations struggle not with hiring talented researchers, but with translating research into automated ML systems that drive measurable business value at scale. The gap between innovation and deployment is where most AI initiatives stall.
+At Omnithrive Technologies, we specialize in closing that gap. We build production-ready AI systems that turn data science insights into quantified business outcomes - typically within 90 days. Our approach is different: we work embedded with your core research and innovation teams to operationalize your contextual targeting and avoidance solutions, then measure the impact in real revenue or efficiency gains.
+Here is the practical angle: a Staff Data Scientist represents a $100,000 annual investment. For approximately 1/10th of that cost, we can deliver equivalent AI capabilities - custom-built for your specific workflow, fully integrated with your existing infrastructure, and backed by our commitment to production results or no fee.
+We do not propose pilots or prototypes. We deliver working systems.
+If this resonates, I would like to offer a complimentary 2-Day AI Opportunity Audit. No commitment, no cost. We will analyze your current data science priorities and map a concrete path to production-ready automation.
+Book here: cal.com/omnithrivetech-ceo
 Warm regards,
 [Your Name]
 Senior B2B Outreach Specialist
 Omnithrive Technologies
-admin@omnithrivetech.com | +91 97426 09264</t>
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -9800,20 +9809,21 @@
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>Johnson Electric's AI hiring challenge — a faster path</t>
+          <t>Johnson Electric's AI hiring - a perspective</t>
         </is>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
           <t>Dear Johnson Electric Team,
-I've reviewed your Data Scientist job posting, and I noticed something worth exploring: you're investing $100,000 annually to build ML models for data cleaning, regression analysis, and deriving insights from complex datasets. That's a critical role — but it's also exactly where AI automation can accelerate your timeline and reduce costs dramatically.
-Here's the reality: 75% of AI projects fail to deliver ROI, often because organizations either hire for capability they don't fully leverage, or invest months building pilots that never reach production. Johnson Electric doesn't need another team member; you need production-ready AI systems that handle your data pipeline, model development, and insights generation immediately.
-We specialize in turning stalled AI initiatives into measurable value within 90 days. For manufacturing operations like yours — where robotics, motion systems, and building automation generate massive data streams — we build custom agentic AI systems that automate the exact workflows your Data Scientist would handle manually. The cost? Approximately one-tenth of what you'd pay for a full-time hire.
-Rather than spending $100,000 on headcount, you could deploy production-grade ML infrastructure for $10,000, plus retain the option to add expert AI developers on demand at $30/hour as your systems scale.
-No pitch meetings. No vague promises. Just a straightforward 2-Day AI Opportunity Audit — completely free — where we identify your highest-impact automation opportunities and present a concrete path forward.
-Book here: cal.com/omnithrivetech-ceo
-Warm regards,
-**[Your Name]**
+I noticed you're hiring a Data Scientist to build machine learning models and turn complex datasets into actionable insights for your motion solutions business. That's a critical role - and typically a $100,000+ annual investment.
+Here's the challenge: 75% of AI projects fail to deliver ROI, according to IBM's 2025 CEO Study. Most organizations hire for capability but struggle with production deployment, data pipeline integration, and real-world validation.
+At Omnithrive Technologies, we've built an alternative approach. Rather than hiring for full-time headcount, mid-to-large manufacturers like yours partner with us to accelerate AI value in 90 days or less. We combine your domain expertise with our production-ready AI systems - turning raw data collection, model development, and statistical validation into measurable business outcomes.
+For roughly 1/10th of what a full-time Data Scientist costs ($100,000 vs. our typical engagement starting at $10,000), you get custom-built ML pipelines, robotics-compatible data workflows, and expert developers who don't disappear after deployment. No pilots. No prototypes. Production-ready systems, scaled when value is proven.
+We'd like to understand your specific AI opportunities - whether that's predictive analytics for your automotive or building automation segments, anomaly detection in robotics systems, or something else entirely.
+I'd like to invite you to a complimentary 2-Day AI Opportunity Audit. No commitment. No cost. Just clarity on where AI can drive measurable profit for Johnson Electric.
+Schedule here: cal.com/omnithrivetech-ceo
+Warm regards,
+[Your Name]
 Senior B2B Outreach Specialist
 Omnithrive Technologies
 admin@omnithrivetech.com | +91 97426 09264</t>
@@ -9878,19 +9888,19 @@
       </c>
       <c r="N109" s="3" t="inlineStr">
         <is>
-          <t>Re: your Director of Engineering, Messaging Infrastructure search</t>
+          <t>On Klaviyo's messaging infrastructure scaling</t>
         </is>
       </c>
       <c r="O109" s="3" t="inlineStr">
         <is>
           <t>Dear Klaviyo Team,
-I noticed your open search for a Director of Engineering, Messaging Infrastructure—a role centered on owning your messaging platform end-to-end: ingestion, orchestration, templating, routing, and analytics across multi-region architecture.
-Here's a perspective worth considering: 75% of AI projects fail to deliver ROI, and most organizations struggle to build production-ready AI capabilities in-house. Yet you're investing $100,000 annually in a full-time hire to architect and optimize these systems.
-At Omnithrive Technologies, we deliver equivalent AI capabilities—custom agentic systems built on LangChain, LangGraph, and AutoGen—for approximately 1/10th of that investment. More importantly, we don't build prototypes. We deliver production-ready systems within 90 days, fully integrated into your existing workflows with built-in change management and adoption support.
-Rather than spending months recruiting, onboarding, and proving ROI, we propose a different path: a complimentary 2-Day AI Opportunity Audit of your messaging infrastructure. We'll identify where AI can measurably reduce latency, improve routing logic, and accelerate your feedback loops—with zero commitment required.
-If the audit reveals concrete value (and it typically does), we can deploy a high-impact MVP within 2-3 weeks. If it doesn't, you've invested nothing but gained clarity.
-Let's explore whether this approach makes sense for Klaviyo.
-Book your free audit here: cal.com/omnithrivetech-ceo
+I noticed your Director of Engineering, Messaging Infrastructure role focuses on owning the messaging platform end-to-end - ingestion, orchestration, templating, routing, and feedback loops across multi-region architecture. That's a complex, high-stakes mandate.
+Here's what we're seeing across SaaS platforms like yours: 88% of AI pilots never reach production (CIO Magazine). Most teams build prototypes, hit scaling challenges, and either stall or restart from scratch - burning months and budget in the process.
+Omnithrive Technologies specializes in turning AI initiatives into production-ready systems within 90 days. For your messaging infrastructure challenge, we've delivered agentic AI solutions using LangChain, LangGraph, and CrewAI that handle exactly what you need - intelligent routing, dynamic templating, and real-time feedback optimization.
+Here's the math: Your posted budget for this hire is approximately $100,000 annually. We can deliver equivalent AI capabilities and infrastructure improvements for roughly 1/10th of that cost - without the 6-month ramp-up or ongoing management overhead.
+Rather than committing to a full-time senior engineer, what if you could validate the opportunity first? We offer a complimentary 2-Day AI Opportunity Audit - no commitment, no cost. We'll map your specific infrastructure gaps and show you exactly what's possible within 90 days.
+If it makes sense, we build. If it doesn't, you walk away with a clear roadmap.
+I'd like to invite you to explore this: cal.com/omnithrivetech-ceo
 Warm regards,
 [Your Name]
 Senior B2B Outreach Specialist
@@ -9948,24 +9958,25 @@
       </c>
       <c r="N110" s="2" t="inlineStr">
         <is>
-          <t>Re: your Senior Software Engineer search</t>
+          <t>A thought on Klipboard's AI build</t>
         </is>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
           <t>Dear Klipboard Team,
-I noticed you're hiring for a Senior Software Engineer with AI/ML expertise to strengthen your cloud ERP capabilities. Building AI-native features into industry-specific software requires both deep technical talent and production-ready execution—both of which come with significant cost and timeline risk.
-Here's the challenge: 88% of AI pilots never reach production (CIO Magazine). Most organizations invest heavily in hiring or contracting AI specialists, only to see prototypes stall or fail to integrate with existing workflows.
-Klipboard's budget for this role is approximately $100,000 annually. At Omnithrive, we deliver equivalent AI capabilities—custom-built agentic systems, LLM integration, and production-ready automation—for roughly one-tenth of that investment. More importantly, we guarantee measurable business outcomes within 90 days, not demos or incomplete pilots.
-Rather than navigate the uncertainty of hiring and onboarding, consider this: What if you could validate your highest-impact AI opportunities, build a working system, and prove ROI—all within two weeks, before committing to a full-time hire?
-Our complimentary 2-Day AI Opportunity Audit identifies where AI creates immediate value in your ERP workflows—without cost or commitment. We'll map your most inefficient processes and show you exactly which AI implementation delivers measurable return.
-I'd welcome a brief conversation about how this could accelerate your AI roadmap.
-You can book directly here: cal.com/omnithrivetech-ceo
+I noticed you are hiring a Senior Software Engineer with AI/ML expertise at approximately $100,000 annually. Before you finalize that search, I want to share a perspective that may save you significant resources.
+88% of AI pilots never reach production according to CIO Magazine. The challenge is rarely technical talent - it is translating AI into measurable business outcomes within your existing workflows.
+Omnithrive Technologies specializes in doing exactly this for SaaS companies like yours. Rather than building custom solutions from scratch, we integrate production-ready AI systems directly into your industry-specific ERP and business software stack. We focus on process automation and value acceleration where inefficiency costs you most.
+Here is what matters: equivalent AI capabilities and implementation cost roughly $10,000 using our High-Impact MVP approach - approximately one-tenth of what you would invest in a full-time hire. You retain flexibility, eliminate long onboarding cycles, and move from concept to production within 90 days.
+For companies operating hybrid teams like yours, this model also reduces coordination overhead while maintaining the collaboration your three-days-on-site policy supports.
+I would like to invite you to a complimentary 2-Day AI Opportunity Audit, completely free and without commitment. We will identify where AI can directly improve your margins and operational efficiency.
+If this interests you, please book a conversation at cal.com/omnithrivetech-ceo.
 Warm regards,
 [Your Name]
 Senior B2B Outreach Specialist
 Omnithrive Technologies
-admin@omnithrivetech.com | +91 97426 09264</t>
+admin@omnithrivetech.com
+WhatsApp: +91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -10055,24 +10066,24 @@
       </c>
       <c r="N111" s="3" t="inlineStr">
         <is>
-          <t>Re: Your Data Scientist (Python) search</t>
+          <t>Re: your Data Scientist (Python) search</t>
         </is>
       </c>
       <c r="O111" s="3" t="inlineStr">
         <is>
           <t>Dear Gary Burnison,
-I noticed Korn Ferry is actively hiring for a Data Scientist to develop statistical models, clean datasets, and translate data insights into actionable recommendations—a critical capability for organizational consulting at your scale.
-Here's a perspective worth considering: 75% of AI projects fail to deliver ROI, and the talent market for skilled Python developers remains intensely competitive. A full-time hire at your €300/day budget represents approximately $100,000 annually, plus onboarding delays and integration overhead.
-Omnithrive Technologies specializes in building production-ready AI systems that deliver measurable value within 90 days—not pilots, not prototypes. We've worked with mid-to-large enterprises across consulting and workforce optimization to automate data analysis workflows, accelerate pattern recognition, and operationalize insights at scale.
-Our approach is straightforward: instead of a 6-month hiring and ramp-up cycle, we can deploy equivalent AI capabilities—including Python-based statistical modeling, data pipeline automation, and stakeholder-ready visualization—for approximately one-tenth of your annual hiring budget. You retain flexibility, avoid long-term fixed costs, and gain immediate access to production-grade systems tailored to your specific workflows.
-We're not asking for a commitment. We offer a complimentary 2-Day AI Opportunity Audit to map where AI can accelerate value in your operations—no cost, no obligation.
-If this resonates, I'd welcome a brief conversation.
-Book your audit here: cal.com/omnithrivetech-ceo
+I noticed Korn Ferry is actively recruiting for a Data Scientist role focused on Python-based statistical modeling and machine learning. The position emphasizes developing algorithms, visualizing insights, and translating data findings into actionable business recommendations - critical capabilities for organizational consulting.
+Here's an observation: recruiting, onboarding, and retaining specialized AI talent at $100,000 annually is a significant investment, particularly when 75% of AI projects fail to deliver ROI according to the IBM CEO Study 2025.
+At Omnithrive Technologies, we've built an alternative approach. Rather than hiring a full-time data scientist, we deliver production-ready AI systems - including Python-based statistical models, predictive algorithms, and data visualization pipelines - at approximately 1/10th of that cost. Our team specializes in building custom AI solutions that integrate directly into your existing workflows and deliver measurable business outcomes within 90 days.
+For Korn Ferry specifically, this means accelerating your capability to build data-driven insights for client engagements without the extended hiring timeline or ongoing infrastructure overhead.
+We offer a complimentary 2-Day AI Opportunity Audit at no commitment or cost. During this audit, we'll assess where AI can generate the highest impact for your consulting practice and outline a concrete path to production within 90 days.
+If this resonates, I'd welcome the conversation. You can schedule directly at cal.com/omnithrivetech-ceo.
 Warm regards,
 [Your Name]
 Senior B2B Outreach Specialist
 Omnithrive Technologies
-admin@omnithrivetech.com | +91 97426 09264</t>
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -10143,22 +10154,23 @@
       </c>
       <c r="N112" s="2" t="inlineStr">
         <is>
-          <t>On Laerdal Medical's AI Engineer hire—a cost-effective alternative</t>
+          <t>A thought on Laerdal Medical's AI build</t>
         </is>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
           <t>Dear Laerdal Medical Team,
-I noticed your search for an AI Engineer to translate business needs into actionable AI solutions and develop LLM-powered prototypes for healthcare training. That's precisely the work we specialize in—and I wanted to share a perspective that might reshape how you approach this.
-Your $100,000 annual budget for a full-time hire is significant. Yet 88% of AI pilots never reach production, according to CIO Magazine. Most organizations struggle not because they lack engineering talent, but because they lack a proven methodology to move from prototype to production-ready systems that actually drive measurable outcomes.
-At Omnithrive Technologies, we've built a different model. Instead of hiring a single engineer, you could engage our expert AI developers—who specialize in LLMs, RAG systems, and responsible AI frameworks—at approximately $10,000 for a complete, production-ready MVP in 2–3 weeks. That's roughly 1/10th of your annual hire budget, with zero fixed overhead and measurable ROI built in from day one.
-We understand healthcare's stakes. Your mission to help save lives demands AI systems that work reliably in time-critical scenarios—not experimental pilots.
-Before you commit to either path, I'd like to offer a complimentary 2-Day AI Opportunity Audit. We'll assess your specific simulation and training workflows, identify where AI creates the highest impact, and provide a clear roadmap—no commitment required.
-You can book directly here: cal.com/omnithrivetech-ceo
-Warm regards,
-**Omnithrive Technologies**
+I noticed your recent search for an AI Engineer to translate business needs into actionable AI solutions and develop prototypes around LLMs, embeddings, and RAGs for your healthcare training platform.
+This is precisely the work we specialize in at Omnithrive Technologies. We build production-ready AI systems that turn failing or stalled initiatives into measurable value within 90 days - and we do it without the 12-18 month hiring and onboarding cycle.
+Here is the reality: 88% of AI pilots never reach production (CIO Magazine). Most organizations spend significant resources building prototypes that remain prototypes. Your $100,000 annual budget for a full-time AI Engineer is substantial, but consider this - Omnithrive delivers equivalent AI capabilities at approximately 1/10th that cost. A senior AI developer working on your LLM and RAG implementations, translating business requirements into production systems, costs roughly $10,000 through our model versus $100,000 annually as a hire.
+More importantly, we bring end-to-end accountability. We don't hand off a prototype and disappear. We embed change management and adoption support directly into deployment, ensuring your team can sustain and scale what we build.
+Rather than hire and hope, we propose a different path: a complimentary 2-Day AI Opportunity Audit. We will analyze your specific use cases around healthcare simulation training, identify high-impact AI opportunities aligned with your mission of saving lives, and present a clear production roadmap.
+No commitment. No cost. Just clarity on what is actually possible.
+Book here: cal.com/omnithrivetech-ceo
+Warm regards,
+Omnithrive Technologies
 AI Value Acceleration Studio
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+admin@omnithrivetech.com | +91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -10233,24 +10245,21 @@
       </c>
       <c r="N113" s="3" t="inlineStr">
         <is>
-          <t>Lanas Healthcare Technology Ltd's AI automation opportunity</t>
+          <t>Automating Lanas Healthcare Technology Ltd's data governance workflows</t>
         </is>
       </c>
       <c r="O113" s="3" t="inlineStr">
         <is>
           <t>Dear Lanas Healthcare Technology Ltd Team,
-I noticed your search for a Senior Software Developer—specifically someone to automate tasks through scripting and maintain your data governance infrastructure across Angular, TypeScript, and Java environments.
-Here's a thought: before investing $100,000 annually in a full-time hire, have you considered what intelligent automation could accomplish within your existing platform?
-We work with healthcare technology companies to embed AI-driven automation directly into their clinical workflows and data pipelines. Rather than hiring another developer, we build production-ready AI systems that handle repetitive documentation, data validation, and integration tasks—capabilities that typically require months of custom development.
-The challenge is real: 88% of AI pilots never reach production (CIO Magazine). Most healthcare organizations struggle to move beyond proof-of-concept. We're different. We deliver production-ready systems in 90 days, custom-built for your RxWeb stack, with measurable ROI—or we don't charge.
-For context, intelligent automation of your data governance workflows and task automation could cost approximately $10,000 through our High-Impact MVP Build—roughly 1/10th of your annual hiring budget—while freeing your existing team to focus on strategic development rather than repetitive scripting.
-We offer a complimentary 2-Day AI Opportunity Audit to identify where automation delivers the highest impact for Lanas Healthcare Technology Ltd. No commitment, no cost.
-Would you be open to a brief conversation?
-Book here: cal.com/omnithrivetech-ceo
-Warm regards,
-[Your Name]
-Senior B2B Outreach Specialist
+I noticed your search for a Senior Software Developer to maintain Angular/TypeScript applications and manage data governance across your hospital platform. That's a critical role-and a significant investment at $100,000 annually.
+I wanted to share a perspective: 75% of AI projects fail to deliver ROI, according to the IBM CEO Study 2025. Healthcare organizations often struggle with the same challenge your JD hints at-automating repetitive tasks like code documentation, data quality checks, and security compliance without adding permanent headcount.
+Omnithrive Technologies specializes in turning those operational bottlenecks into production-ready AI systems. Rather than hiring a full-time developer to handle automation and governance workflows, we build custom AI agents that handle documentation generation, automated code reviews, and data integrity monitoring-typically for one-tenth of a senior hire's cost. Your $100,000 budget translates to approximately $10,000 with us, plus you retain the flexibility to scale without permanent overhead.
+We've delivered results in healthcare, logistics, and manufacturing by focusing on what matters: measurable ROI within 90 days, not pilots that never reach production.
+No obligation to engage further-but I'd like to invite your team to explore this with our complimentary 2-Day AI Opportunity Audit. We'll map your specific workflows, identify where AI can reduce manual effort, and present a clear roadmap for value.
+You can schedule directly at cal.com/omnithrivetech-ceo.
+Warm regards,
 Omnithrive Technologies
+AI Value Acceleration Studio
 admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
         </is>
       </c>
@@ -10328,22 +10337,25 @@
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>Louisville Metro Government's AI hiring — a perspective</t>
+          <t>Louisville Metro's Engineer II search - an AI alternative</t>
         </is>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
           <t>Dear Craig Greenberg,
-I noticed Louisville Metro Government is recruiting an Engineer II with AI/ML capabilities—specifically someone who can compute load requirements, evaluate material adequacy, and analyze traffic patterns and environmental conditions at scale.
-That's a critical hire. But here's the reality: you're budgeting $100,000 annually for one engineer. What if you could deploy production-ready AI systems that automate those exact workflows—material stress analysis, soil evaluation, traffic pattern studies, cost estimation—for approximately one-tenth of that investment?
-According to the IBM CEO Study (2025), 75% of AI projects fail to deliver ROI. Most organizations either build pilots that never reach production, or hire expensive talent that becomes a fixed cost regardless of output. Louisville Metro Government deserves better.
-Omnithrive Technologies specializes in turning stalled AI initiatives into measurable operational value within 90 days. We don't build demos. We deploy production-ready systems custom-built for your municipal workflows—in this case, accelerating your engineering teams' analysis, inspection, and procurement processes through intelligent automation.
-Rather than committing to a full-time hire before you know what's possible, I'd like to offer a complimentary 2-Day AI Opportunity Audit. No cost. No obligation. We'll assess your current engineering workflows, identify where AI can deliver immediate impact, and present a clear roadmap.
-If this resonates, please book a time at cal.com/omnithrivetech-ceo or reach out directly at admin@omnithrivetech.com.
+I noticed Louisville Metro Government is recruiting for an Engineer II role focused on infrastructure design, load calculations, and material specifications. That's a $100,000 annual investment in specialized technical capacity.
+What if you could access equivalent AI capabilities for one-tenth that cost?
+Your engineers currently spend significant time on repetitive tasks: computing load and grade requirements, evaluating soil test data, calculating material cost estimates, and preparing bid proposals. These are precisely the workflows where AI delivers immediate, measurable value - automating data analysis, flagging specification errors, and accelerating feasibility studies.
+The challenge is execution. According to IBM's 2025 CEO Study, 75% of AI projects fail to deliver ROI. Most organizations deploy pilots that never reach production, leaving them with unused tools and frustrated teams.
+Omnithrive Technologies specializes in production-ready AI systems built specifically for government and infrastructure operations. We don't sell generic software - we build custom workflows that integrate directly into your existing processes, with built-in change management to ensure adoption.
+We've helped similar organizations turn stalled AI initiatives into measurable operational gains within 90 days. Before you commit to a full-time hire, it's worth exploring what's actually possible.
+I'd like to offer Louisville Metro Government a complimentary 2-Day AI Opportunity Audit - no cost, no commitment. We'll assess your infrastructure workflows and identify where AI can reduce costs and accelerate project delivery.
+You can book directly at cal.com/omnithrivetech-ceo or reach us at admin@omnithrivetech.com.
 Warm regards,
 Omnithrive Technologies
 AI Value Acceleration Studio
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -10410,16 +10422,20 @@
       <c r="O115" s="3" t="inlineStr">
         <is>
           <t>Dear Luxoft Poland Team,
-I noticed you're hiring for a Semantic AI/ML Engineer to lead ontology design, knowledge graph development, and SPARQL optimization across your enterprise systems. That's a critical role—and a $100,000 annual investment.
-Here's a thought: 75% of AI projects fail to deliver ROI, often because teams lack the production-ready architecture and change management to move beyond pilots into scaled deployment. Building knowledge graphs and semantic systems in-house is complex; recruiting, onboarding, and managing a full-time specialist compounds that cost and risk.
-At Omnithrive Technologies, we deliver equivalent AI capabilities—custom ontologies, enterprise knowledge graphs, optimized semantic querying—for approximately one-tenth of what you'd invest in that hire. Our approach is ROI-first: we build production-ready systems within 90 days, not prototypes. We handle the technical depth (LangGraph, AutoGen, knowledge graph optimization) *and* the change management that ensures adoption.
-Rather than a lengthy hiring cycle, consider this: a free 2-Day AI Opportunity Audit to map your semantic data challenges, quantify the efficiency gains, and validate the business case before committing to either path.
-No obligation. No cost. You'll have a clear picture of what's possible and what it actually costs to move from pilot to production.
-If this resonates, book your audit here: **cal.com/omnithrivetech-ceo**
-Warm regards,
-**Omnithrive Technologies**
-AI Value Acceleration Studio
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+I noticed you are hiring for a Semantic AI/ML Engineer to lead ontology design, knowledge graph development, and SPARQL optimization across your enterprise systems. That is a significant technical investment - and for good reason. These capabilities are critical.
+However, I wanted to share a perspective: 75% of AI projects fail to deliver ROI, according to the IBM CEO Study 2025. Most organizations build teams first, then discover misalignment between engineering effort and actual business value.
+At Omnithrive Technologies, we take the opposite approach. We audit your specific workflows, identify where semantic AI and knowledge graph systems will generate measurable profit, then build production-ready systems - not prototypes - within 90 days.
+The financial reality: a full-time Semantic AI/ML Engineer costs approximately $100,000 annually. We deliver equivalent capabilities, custom-built to your domain and integrated into your existing systems, for roughly one-tenth that cost. More importantly, you only pay when value is proven.
+We have worked with software engineering and digital transformation companies on similar challenges: automating data ontology design, accelerating knowledge graph population, and optimizing semantic querying at scale.
+Rather than hiring immediately, consider a different starting point: a free 2-Day AI Opportunity Audit. No commitment. No cost. We will map your exact use cases, quantify the ROI potential, and show you whether a semantic AI system makes financial sense before you invest in headcount.
+I would welcome the conversation.
+Book your audit here: cal.com/omnithrivetech-ceo
+Warm regards,
+[Your Name]
+Senior B2B Outreach Specialist
+Omnithrive Technologies
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -10471,24 +10487,23 @@
       <c r="M116" s="2" t="inlineStr"/>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>Re: Madison Recruitment's .NET engineer search</t>
+          <t>Madison Recruitment's .NET hiring - an AI angle</t>
         </is>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
           <t>Dear Madison Recruitment Team,
-I noticed you're actively hiring for a .NET Software Engineer with expertise in classification and Gemma—skills that command significant market rates and extended search timelines.
-Here's a perspective worth considering: Rather than investing $100,000 annually in a full-time hire, what if you could deploy custom AI systems to automate candidate screening, CV classification, and interview preparation at approximately 1/10th that cost?
-According to IBM's 2025 CEO Study, 75% of AI projects fail to deliver ROI—primarily because organisations build generic solutions rather than production-ready systems tailored to their exact workflows. At Omnithrive Technologies, we specialise in the opposite approach: AI systems built specifically for your recruitment processes that deliver measurable value within 90 days, not pilot projects that stall.
-For a recruitment platform like Madison, the opportunities are substantial. Imagine automating candidate assessment workflows, intelligently routing applications, and scaling your interview preparation systems without recruiting bottlenecks. We've built production-grade agentic AI systems using LangChain, LangGraph, and custom classification models—the same technologies your engineering teams rely on.
-Rather than a lengthy hiring process, consider this: a complimentary 2-Day AI Opportunity Audit to identify where automation delivers the highest ROI for your operations. No commitment, no cost—simply a concrete roadmap for turning recruitment inefficiency into competitive advantage.
-I'd welcome the chance to explore this with your team.
-Book your audit here: cal.com/omnithrivetech-ceo
-Warm regards,
-[Your Name]
-Senior B2B Outreach Specialist
+I wanted to reach out because I noticed you are actively recruiting for a .NET Software Engineer role - a critical hire that represents significant investment and time-to-productivity risk for your organization.
+Here is the reality: 75% of AI projects fail to deliver ROI, according to the IBM CEO Study (2025). Most organizations either build AI capabilities in-house at enormous cost, or they hire specialized talent at premium salaries. Your budget for this single .NET hire is approximately $100,000 annually - yet you could deploy production-ready AI capabilities that handle classification, workflow automation, and candidate intelligence tasks for roughly one-tenth of that cost.
+At Omnithrive Technologies, we specialize in turning stalled or failing AI initiatives into measurable profit within 90 days. We do not deliver pilots or prototypes. We build custom, production-ready systems tailored to your exact workflows - in your case, automating candidate classification, interview preparation optimization, and employer-candidate matching through intelligent AI agents.
+Rather than waiting months to onboard a new engineer and hoping they deliver ROI, you could have a fully functional AI system operational and generating measurable results in weeks. We only scale when value is proven.
+I would like to invite you to a complimentary 2-Day AI Opportunity Audit, at no cost and with no commitment. We will analyze your current recruitment workflows and identify where AI can deliver immediate impact.
+You can book your audit here: cal.com/omnithrivetech-ceo
+Warm regards,
 Omnithrive Technologies
-admin@omnithrivetech.com | +91 97426 09264</t>
+AI Value Acceleration Studio
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -10572,23 +10587,24 @@
       </c>
       <c r="N117" s="3" t="inlineStr">
         <is>
-          <t>Mastercard's card processing platform — AI acceleration angle</t>
+          <t>A thought on Mastercard's AI build velocity</t>
         </is>
       </c>
       <c r="O117" s="3" t="inlineStr">
         <is>
           <t>Dear Mastercard Team,
-I noticed you're hiring for a Software Engineer II to handle parametrization, configuration, and cross-functional problem resolution on your Way4 issuing platform. That's a critical role — and it typically costs $100,000 annually in salary and overhead.
-Here's what we're seeing across FinTech: 88% of AI pilots never reach production (CIO Magazine), yet the operational complexity of card processing systems like yours demands intelligent automation to reduce manual configuration, accelerate client onboarding, and resolve multi-service dependencies faster.
-Rather than add headcount, many enterprises in your space are deploying production-ready AI systems that handle parametrization logic, configuration workflows, and diagnostic problem-solving — delivering equivalent capabilities for approximately 1/10th of a full-time hire's cost.
-Omnithrive Technologies specializes in turning stalled AI initiatives into measurable profit within 90 days. We've built production systems (not pilots) using LangGraph, LangChain, and enterprise LLMs specifically designed for complex operational workflows like card platform management.
-Before you finalize that hire, I'd like to offer something that costs nothing: a complimentary 2-Day AI Opportunity Audit. We'll map where intelligent automation could reduce manual effort, accelerate platform configuration, and improve resolution cycles — with no commitment required.
-If this interests you, book directly here: cal.com/omnithrivetech-ceo
-Warm regards,
-[Your Name]
-Senior B2B Outreach Specialist
+I noticed your Software Engineer II posting focuses on Way4Cards platform configuration and cross-functional problem resolution across complex card processing systems. That's mission-critical work - but it's also exactly where AI can accelerate capability without extending headcount.
+Here's the reality: 75% of AI projects fail to deliver ROI, according to the IBM CEO Study 2025. Most financial services companies invest heavily in engineering talent to handle parametrization, configuration workflows, and issue diagnosis - only to see those initiatives stall or never reach production.
+At Omnithrive Technologies, we specialize in turning stalled AI initiatives into measurable production systems within 90 days. For Mastercard's payments infrastructure, this means automating the configuration and knowledge-sharing workflows your teams currently handle manually - delivering equivalent capabilities at roughly 1/10th the cost of a full-time Software Engineer II (your $100K annual budget versus our typical engagement cost).
+Rather than hiring another engineer, consider this: what if you could automate the repetitive parametrization, configuration documentation, and cross-service problem diagnosis work using production-ready agentic AI - built specifically for Way4Cards and your issuing platform requirements?
+We offer a complimentary 2-Day AI Opportunity Audit to identify high-impact automation opportunities within your payments infrastructure. No commitment. No cost.
+If you'd like to explore this approach, I'd welcome a brief conversation.
+Book your audit at cal.com/omnithrivetech-ceo
+Warm regards,
 Omnithrive Technologies
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+AI Value Acceleration Studio
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -10679,15 +10695,15 @@
       <c r="O118" s="2" t="inlineStr">
         <is>
           <t>Dear Magda,
-I noticed Mekion Consulting is actively hiring for a Machine Learning Engineer—a role critical to building scalable AI solutions for your clients. Given the complexity of embedding systems and the entrepreneurial pace your startup clients demand, I wanted to share a perspective that might be valuable.
-Here's the reality: 88% of AI pilots never reach production (CIO Magazine). Most organizations struggle not with hiring talent, but with translating that talent into measurable business outcomes. A full-time ML Engineer at $100,000 annually is essential—but what if you could access equivalent AI capabilities for one-tenth that cost, deployed in production within 90 days?
-At Omnithrive Technologies, we specialize in turning stalled AI initiatives into measurable profits. Rather than adding headcount, we build production-ready systems tailored to your clients' exact workflows—whether that's embedding models, Go-based architectures, or machine learning pipelines. We handle everything your clients care about: problem-solving, reducing complexity, and delivering customer value at pace.
-This isn't theoretical. We've helped mid-to-large enterprises bypass the pilot trap entirely, deploying systems that drive real ROI in the first quarter.
-If Mekion's own operations—or your startup clients—are grappling with AI efficiency, I'd like to invite you to a complimentary 2-Day AI Opportunity Audit. No commitment. No cost. Just a clear map of where AI can create immediate value.
-You can book directly here: cal.com/omnithrivetech-ceo
-Warm regards,
-Omnithrive Technologies
-AI Value Acceleration Studio
+I noticed Mekion Consulting is actively hiring for a Machine Learning Engineer with expertise in embeddings and Go - a critical role for scaling your AI capabilities across client engagements.
+Here is a direct observation: building ethical, production-ready AI solutions requires specialized talent, and hiring a full-time ML engineer at your stated budget of $100,000 annually is a significant investment. Yet 88% of AI pilots never reach production, according to CIO Magazine - meaning the risk of that investment failing to deliver measurable value is substantial.
+At Omnithrive Technologies, we deliver equivalent AI capabilities through our expert developer network at approximately $10,000 - effectively 1/10th the cost of a full-time hire. More importantly, we guarantee production-ready systems within 90 days, not prototypes or stalled pilots.
+Your clients need AI solutions that actually work. Your teams need someone who can bridge complex technical concepts with stakeholder requirements - precisely what you've outlined in your JD. Rather than betting on a single hire, consider validating your AI opportunities first.
+This is why we offer a complimentary 2-Day AI Opportunity Audit. No commitment. No cost. We analyze your specific use cases, identify where AI can deliver measurable ROI, and recommend whether a full-time hire, managed developers, or a hybrid approach makes sense for Mekion's growth strategy.
+I would welcome a brief conversation about your AI roadmap.
+Please book your audit here: cal.com/omnithrivetech-ceo
+Warm regards,
+Omnithrive Technologies AI Value Acceleration Studio
 admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
         </is>
       </c>
@@ -10751,22 +10767,24 @@
       </c>
       <c r="N119" s="3" t="inlineStr">
         <is>
-          <t>Ministry of Housing, Communities and Local Government's AI production challenge</t>
+          <t>Ministry of Housing's AI production challenge - an alternative approach</t>
         </is>
       </c>
       <c r="O119" s="3" t="inlineStr">
         <is>
           <t>Dear Ministry of Housing, Communities and Local Government Team,
-I noticed your search for an Associate AI Engineer, and I wanted to share a perspective that may be valuable to your leadership.
-Your job description emphasizes developing AI prototypes and scaling to production while managing stakeholder feedback and AI ethics compliance. This is precisely where most government departments face friction—88% of AI pilots never reach production, according to CIO Magazine. The gap between prototype and operational deployment consumes time, budget, and organizational credibility.
-Here's the practical consideration: hiring a full-time AI Engineer at £100,000 annually locks in a 12-month commitment with no guarantee of production-ready outcomes. At Omnithrive Technologies, we deliver equivalent capabilities—custom AI systems built on modern stacks (LangChain, LangGraph, AutoGen) integrated into your existing workflows—for approximately 1/10th of that investment. More importantly, we guarantee production-ready systems within 90 days, not pilots.
-Your team handles the strategic oversight, stakeholder integration, and policy alignment. We handle the engineering velocity and delivery certainty. You avoid the hiring lead time, onboarding complexity, and fixed overhead while retaining full control over direction.
-Rather than debate this further, I'd like to propose a complimentary 2-Day AI Opportunity Audit. No commitment. We'll map your most pressing AI initiative, identify production pathways, and quantify realistic value within 90 days.
-If this resonates, please book here: cal.com/omnithrivetech-ceo
-Warm regards,
-**Omnithrive Technologies**
+I noticed your search for an Associate AI Engineer to develop and scale AI prototypes into production while managing stakeholder feedback and ensuring policy compliance. That's a critical hire - and it underscores a broader challenge facing government digital teams.
+Here's the reality: 88% of AI pilots never reach production (CIO Magazine). Your team needs not just engineering capacity, but proven capability to move from MVP to working systems quickly, with built-in change management and stakeholder alignment.
+At Omnithrive Technologies, we specialise in exactly this: turning stalled or failing AI initiatives into production-ready systems within 90 days. Rather than waiting months to onboard and train a full-time engineer at £100,000 annually, you could access a production-ready AI capability for approximately one-tenth that cost - deployed in weeks, not quarters.
+We work across the same workflows your brief describes: developing MVPs, iterating with user feedback, integrating across complex stakeholder environments, and embedding AI ethics principles throughout. Our approach is custom-built for government contexts and includes the change management layer most projects miss.
+Before committing to a hire, we recommend exploring what's actually possible in your specific environment. We offer a complimentary 2-Day AI Opportunity Audit - no cost, no obligation - to identify quick wins and scalable opportunities within your operations.
+If this resonates, I'd welcome a brief conversation.
+Book your audit here: cal.com/omnithrivetech-ceo
+Warm regards,
+Omnithrive Technologies
 AI Value Acceleration Studio
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -10838,27 +10856,23 @@
       </c>
       <c r="N120" s="2" t="inlineStr">
         <is>
-          <t>Morgan McKinley's AI Microsoft 365 build — a cost perspective</t>
+          <t>Re: your AI Microsoft 365 Senior Engineer search</t>
         </is>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
           <t>Dear Morgan McKinley Team,
-I noticed you're actively recruiting for an AI Microsoft 365 Senior Engineer with expertise in Copilot Agent design, Microsoft Graph integration, and AI governance—a critical hire at $100,000 annually.
-Here's a perspective worth considering: 75% of AI projects fail to deliver ROI, according to IBM's 2025 CEO Study. Many organizations invest heavily in full-time specialized talent only to struggle with adoption, governance misalignment, and delayed time-to-value.
-At Omnithrive Technologies, we specialize in turning stalled AI initiatives into production-ready systems within 90 days. For recruitment and talent services platforms, we design and deploy custom Copilot Agents integrated with your enterprise data sources and internal APIs—exactly the capabilities your role demands—at approximately 1/10th the cost of a full-time senior engineer.
-Rather than a lengthy hiring and onboarding cycle, you receive:
-- Purpose-built Copilot Agents tailored to your talent workflows
-- Built-in GDPR and EU AI Act compliance from day one
-- Advanced prompt engineering and testing aligned with AI governance standards
-- Cross-functional collaboration without the overhead
-We don't deliver pilots or prototypes. Our systems go live production-ready, with change management included.
-If this aligns with your timeline and budget constraints, I'd welcome a conversation. We offer a complimentary 2-Day AI Opportunity Audit—no commitment, no cost—to identify high-impact use cases specific to Morgan McKinley's platform.
-You can book directly here: cal.com/omnithrivetech-ceo
+I noticed you are actively recruiting for an AI Microsoft 365 Senior Engineer with expertise in designing Copilot Agents, Microsoft Graph integration, and AI governance frameworks aligned with GDPR and the EU AI Act.
+This is precisely the skillset most organizations struggle to find - and the hiring cost reflects that reality. Your budgeted investment of $100,000 annually is substantial for a single full-time role.
+Here is the core challenge: 75% of AI projects fail to deliver measurable ROI, according to the IBM CEO Study 2025. Most organizations hire senior engineers to build custom AI solutions, but without a structured framework for proof-of-value and adoption, those investments sit idle.
+Omnithrive Technologies offers a different path. Rather than committing $100,000 to a full-time hire, we can deliver production-ready Copilot Agent implementations and Microsoft 365 AI integration capabilities for approximately 1/10th of that cost - while eliminating the recruitment risk entirely. Our approach combines expert AI developers, built-in change management, and a guarantee of measurable results within 90 days.
+We have successfully deployed custom AI solutions across recruitment technology, enterprise data integration, and regulatory-compliant governance frameworks. We do not deliver pilots or prototypes - only production-ready systems that scale when value is proven.
+I would like to invite Morgan McKinley to participate in our complimentary 2-Day AI Opportunity Audit. This assessment will identify which AI capabilities would deliver the greatest impact to your talent services operations, with zero commitment or cost.
+Please book your audit at cal.com/omnithrivetech-ceo.
 Warm regards,
 Omnithrive Technologies
 AI Value Acceleration Studio
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+admin@omnithrivetech.com</t>
         </is>
       </c>
     </row>
@@ -10932,28 +10946,24 @@
       </c>
       <c r="N121" s="3" t="inlineStr">
         <is>
-          <t>Re: your CSV Engineer search</t>
+          <t>Re: Your CSV Engineer search</t>
         </is>
       </c>
       <c r="O121" s="3" t="inlineStr">
         <is>
           <t>Dear NES Fircroft Team,
-I noticed you're recruiting for a CSV Engineer to manage GxP laboratory systems, handle data archival, and support validation protocols under strict regulatory compliance (21 CFR Part 11, cGMP).
-This is a critical hire—and at $100,000 annually, it represents a significant investment in infrastructure stability.
-Here's what I want to share: 75% of AI projects fail to deliver ROI, according to the IBM CEO Study 2025. But many organizations don't realize they can deploy production-ready AI systems for a fraction of what they spend on traditional hires.
-At Omnithrive Technologies, we specialize in turning stalled or failing AI initiatives into measurable value within 90 days. For NES Fircroft's use case—automating data management, deviation tracking, CAPA workflows, and system audit coordination—we can build a custom AI solution that handles these repetitive, high-compliance tasks at approximately 1/10th the cost of a full-time engineer ($10,000 versus $100,000).
-Rather than hire, you could deploy an intelligent automation system that:
-- Manages laboratory data archival and backups autonomously
-- Flags regulatory deviations and change controls in real-time
-- Accelerates validation document workflows (IQ/OQ/PQ protocols)
-- Integrates seamlessly with your existing GxP systems
-No pilots. No prototypes. Production-ready systems, built custom to your workflows.
-I'd like to offer NES Fircroft a complimentary 2-Day AI Opportunity Audit—no commitment, no cost. We'll map your exact operational gaps and show you what's possible.
-Book here: cal.com/omnithrivetech-ceo
-Warm regards,
-**Omnithrive Technologies**
-AI Value Acceleration Studio
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+I noticed you're recruiting for a CSV Engineer to manage GxP laboratory systems, validation protocols, and regulatory compliance across your energy sector clients. That's a critical hire - and at $100,000 annually, it represents significant investment for specialized expertise.
+Here's what we've observed: 75% of AI projects fail to deliver ROI because organizations either hire for capability they don't fully utilize, or build systems that never reach production. Your need for data integrity management, change control coordination, and validation documentation is exactly where AI-driven automation delivers measurable value - but only if it's production-ready from day one.
+At Omnithrive Technologies, we turn failing or stalled AI initiatives into measurable profits within 90 days. We specialize in building custom AI systems that handle the exact workflows your clients need - from CAPA automation and deviation tracking to protocol documentation and regulatory audit trails. The result: equivalent capabilities to a full-time CSV Engineer role, delivered at approximately 1/10th the cost.
+Rather than hire and onboard, you could deploy a production-ready AI system in weeks. No pilots. No prototypes. Just measurable ROI.
+We'd like to explore this with you at no cost. Our complimentary 2-Day AI Opportunity Audit will identify exactly where automation creates the biggest impact for your energy clients - with zero commitment required.
+Would you be open to a brief conversation?
+Schedule here: cal.com/omnithrivetech-ceo
+Warm regards,
+[Your Name]
+Senior B2B Outreach Specialist
+Omnithrive Technologies
+AI Value Acceleration Studio</t>
         </is>
       </c>
     </row>
@@ -11026,24 +11036,24 @@
       </c>
       <c r="N122" s="2" t="inlineStr">
         <is>
-          <t>Re: Your OLAN C/C++ Embedded Linux Software Engineer search</t>
+          <t>Re: your OLAN C/C++ Embedded Linux Software Engineer search</t>
         </is>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
           <t>Dear Nokia Team,
-I noticed you're hiring for an OLAN C/C++ Embedded Linux Software Engineer focused on AI Agents and AIOps—a critical role given the complexity of designing software architecture across multiple processor architectures (Arm, MIPS, PPC) while integrating AI-powered network solutions.
-Here's a perspective worth considering: 88% of AI pilots never reach production (CIO Magazine). This statistic reflects a broader challenge many telecom and infrastructure leaders face—building AI capabilities that actually scale into operational systems, not just prototypes.
-At Omnithrive Technologies, we specialize in turning stalled AI initiatives into production-ready systems within 90 days. Rather than hiring a full-time embedded AI engineer at $100,000 annually, organizations can access specialized AI development expertise—including agentic AI frameworks (LangChain, LangGraph, CrewAI), AIOps integration, and cloud-native deployment (Google Cloud)—for approximately one-tenth of that cost.
-For Nokia's use case, this means accelerating your AI-powered network solutions without the long hiring cycle, onboarding delays, or long-term overhead. We build custom systems aligned to your specific workflows and infrastructure requirements, with built-in change management to ensure adoption at scale.
-Rather than another job posting, what if you could validate whether a high-impact AI capability could pay for itself in weeks?
-We offer a complimentary 2-Day AI Opportunity Audit—no commitment, no cost—to identify where AI can create measurable value in your network operations or product roadmap.
-Would you be open to exploring this?
-Schedule here: cal.com/omnithrivetech-ceo
-Warm regards,
-**Omnithrive Technologies**
-AI Value Acceleration Studio
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+I noticed you are actively recruiting for an OLAN C/C++ Embedded Linux Software Engineer - a role that demands deep expertise in AI Agents, AIOps, and multi-architecture systems design across ARM, MIPS, and PPC processors.
+Hiring and onboarding a full-time engineer at $100,000 annually is a significant commitment. What if you could access equivalent AI capabilities - including AI Agent architecture, AIOps automation, and production-ready embedded systems integration - for approximately one-tenth of that cost?
+Here is the challenge: 88% of AI pilots never reach production (CIO Magazine). Nokia's vision for AI-powered network solutions requires more than theoretical frameworks. It demands production-ready systems that integrate seamlessly with your existing embedded Linux infrastructure and can scale across your critical infrastructure clients.
+Omnithrive Technologies specializes in accelerating AI initiatives from concept to measurable value in 90 days. We have built production-grade AI Agents and AIOps systems using LangGraph, CrewAI, and custom automation pipelines - precisely the domain your OLAN initiative requires. Rather than lengthy recruitment cycles or pilot-phase uncertainty, we deliver functional systems that prove value before scaling.
+We would like to offer you a complimentary 2-Day AI Opportunity Audit. This is a no-cost, no-commitment assessment of how AI Agents and AIOps automation can enhance your embedded systems pipeline and reduce time-to-production for your network solutions.
+If this resonates, please book a time that works for your team at cal.com/omnithrivetech-ceo.
+Warm regards,
+[Your Name]
+Senior B2B Outreach Specialist
+Omnithrive Technologies
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
@@ -11091,24 +11101,24 @@
       <c r="M123" s="3" t="inlineStr"/>
       <c r="N123" s="3" t="inlineStr">
         <is>
-          <t>Re: your C&amp;Q Engineer search — an AI alternative</t>
+          <t>AI capabilities for Normec Advipro's compliance workflows</t>
         </is>
       </c>
       <c r="O123" s="3" t="inlineStr">
         <is>
           <t>Dear Normec Advipro Team,
-I noticed you're hiring for a C&amp;Q Engineer at $100,000 annually. I wanted to share a perspective that may be relevant to your process optimization and regulatory compliance work in life sciences.
-88% of AI pilots never reach production (CIO Magazine) — yet your sector desperately needs AI-driven quality management and process automation. The challenge isn't finding talent; it's deploying systems that actually work within your compliance frameworks.
-Rather than a single hire, consider this: Omnithrive Technologies delivers production-ready AI systems tailored to your exact workflows — document intelligence for regulatory submissions, automated QA workflows, predictive compliance monitoring — at approximately 1/10th the cost of a full-time engineer. No pilots. No prototypes. Measurable ROI within 90 days.
-Your C&amp;Q processes generate enormous data. That data can be turned into competitive advantage through intelligent automation, but only if the solution is built specifically for pharmaceutical and food industry constraints — not off-the-shelf tools.
-We've helped consulting and engineering firms like yours eliminate manual compliance checks, accelerate quality audits, and reduce time-to-market for client deliverables.
-The most efficient next step: a complimentary 2-Day AI Opportunity Audit, where we map the exact high-impact automation opportunities within your operations. No commitment. No cost.
-If this resonates, I'd welcome a brief conversation.
-Book here: cal.com/omnithrivetech-ceo
-Warm regards,
-**Omnithrive Technologies**  
-AI Value Acceleration Studio  
-admin@omnithrivetech.com | WhatsApp: +91 97426 09264</t>
+I noticed you are recruiting for a C&amp;Q Engineer with AI/ML expertise. Before you finalize that hire at $100,000 annually, I wanted to share a perspective that may reshape how you approach this.
+Normec Advipro's work in pharmaceutical and food compliance demands precision - process optimization, quality management systems, and regulatory documentation cannot afford delays or errors. An AI-enabled system built specifically for your compliance workflows could accelerate documentation review, streamline audit preparation, and reduce manual QA cycles significantly.
+Here's the gap: 75% of AI projects fail to deliver ROI, according to the IBM CEO Study 2025. Most firms either build generic solutions or hire expensive specialists who lack production-ready deployment expertise. Both approaches drain budget without measurable impact.
+At Omnithrive Technologies, we take a different approach. We build custom, production-ready AI systems tailored to your exact processes - not prototypes or pilots. For approximately 1/10th of what you would spend on a full-time C&amp;Q Engineer ($10,000 versus $100,000), we deliver AI capabilities that integrate directly into your compliance workflows, with built-in change management to ensure adoption.
+We do not charge for exploration. Our complimentary 2-Day AI Opportunity Audit will identify specific high-impact applications within your quality and regulatory processes - with zero commitment.
+If this resonates, I would welcome a brief conversation.
+Book your audit here: cal.com/omnithrivetech-ceo
+Warm regards,
+Omnithrive Technologies
+AI Value Acceleration Studio
+admin@omnithrivetech.com
++91 97426 09264</t>
         </is>
       </c>
     </row>
